--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,67 +39,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,91 +123,391 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,19 +519,331 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,48 +855,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -285,2785 +1053,2017 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,40 +8489,40 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>9.99</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="13">
         <v>13.15</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="8">
         <v>9.95</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="9">
         <v>8.34</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="5">
         <v>9.06</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>5.46</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="6">
         <v>3.94</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="3">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="10">
         <v>0.04</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="11">
         <v>1.19</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="7">
         <v>0.13</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="4">
         <v>-16.67</v>
       </c>
     </row>
@@ -8554,37 +8554,37 @@
       <c r="I3" s="15">
         <v>-8.66</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="16">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="23">
         <v>-15.92</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="20">
         <v>-14.66</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="24">
         <v>-9.78</v>
       </c>
       <c r="N3" s="17">
         <v>-11.59</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="21">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="25">
         <v>-15.36</v>
       </c>
       <c r="Q3" s="18">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="19">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="26">
         <v>-15.92</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="22">
         <v>-29.61</v>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>601008</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 2459.29万</v>
       </c>
       <c r="E4">
@@ -8613,40 +8613,40 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="36">
         <v>8.18</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="32">
         <v>-2.55</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="33">
         <v>-0.36</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="37">
         <v>0.18</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="38">
         <v>-1.64</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="29">
         <v>-7.64</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="39">
         <v>-7.64</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="27">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="30">
         <v>11.82</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="28">
         <v>23.09</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="31">
         <v>35.45</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="34">
         <v>-12.18</v>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,37 +8675,37 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="50">
         <v>11.02</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="46">
         <v>8.91</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="47">
         <v>19.8</v>
       </c>
       <c r="L5" s="40">
         <v>19.08</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="41">
         <v>19.87</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="42">
         <v>13</v>
       </c>
       <c r="O5" s="44">
         <v>12.87</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="43">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="48">
         <v>7.46</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="49">
         <v>5.61</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="45">
         <v>4.49</v>
       </c>
       <c r="T5" s="51">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8737,40 +8737,40 @@
       <c r="H6">
         <v>-1.7</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="58">
         <v>11.92</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="61">
         <v>13.13</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="63">
         <v>17.96</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="64">
         <v>22.02</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="65">
         <v>16.84</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="53">
         <v>9.93</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="54">
         <v>7.43</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="59">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="60">
         <v>9.93</v>
       </c>
       <c r="R6" s="62">
         <v>12.61</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="55">
         <v>23.83</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="56">
         <v>-22.28</v>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="75" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8802,22 +8802,22 @@
       <c r="I7" s="76">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="67">
         <v>-12.07</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="77">
         <v>-10.42</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="78">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="69">
         <v>-14.58</v>
       </c>
       <c r="N7" s="71">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="70">
         <v>-23.59</v>
       </c>
       <c r="P7" s="68">
@@ -8826,13 +8826,13 @@
       <c r="Q7" s="72">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="66">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="73">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="73">
+      <c r="T7" s="74">
         <v>-23.75</v>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>002094</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 3233.09万</v>
       </c>
       <c r="E8">
@@ -8861,28 +8861,28 @@
       <c r="H8">
         <v>-1.1</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="81">
         <v>11.25</v>
       </c>
       <c r="J8" s="88">
         <v>10.01</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="82">
         <v>21.01</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="89">
         <v>18.67</v>
       </c>
       <c r="M8" s="83">
         <v>22.13</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="90">
         <v>21.76</v>
       </c>
       <c r="O8" s="84">
         <v>17.43</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="91">
         <v>16.19</v>
       </c>
       <c r="Q8" s="85">
@@ -8891,7 +8891,7 @@
       <c r="R8" s="86">
         <v>23.73</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="79">
         <v>15.95</v>
       </c>
       <c r="T8" s="87">
@@ -8923,40 +8923,40 @@
       <c r="H9">
         <v>2.78</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="101">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="92">
         <v>5.84</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="93">
         <v>3.78</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="99">
         <v>6.81</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="94">
         <v>6.49</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="102">
         <v>2.7</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="100">
         <v>1.62</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="95">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="96">
         <v>8.22</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="97">
         <v>1.41</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="98">
         <v>0.22</v>
       </c>
-      <c r="T9" s="100">
+      <c r="T9" s="103">
         <v>-31.68</v>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,40 +8985,40 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="110">
         <v>11.08</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="108">
         <v>0</v>
       </c>
       <c r="K10" s="114">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="115">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="116">
         <v>-16.07</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="117">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="111">
         <v>-11.64</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="109">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="105">
         <v>-19.06</v>
       </c>
       <c r="R10" s="112">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="109">
+      <c r="S10" s="113">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="110">
+      <c r="T10" s="106">
         <v>-22.42</v>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="128" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,40 +9047,40 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="129">
         <v>9.97</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="122">
         <v>5.4</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="126">
         <v>3.74</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="130">
         <v>7.89</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="118">
         <v>5.19</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="123">
         <v>1.14</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="120">
         <v>-0.31</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="124">
         <v>-6.65</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="125">
         <v>-3.32</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="127">
         <v>-8.62</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="119">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="123">
+      <c r="T11" s="121">
         <v>-32.92</v>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,40 +9109,40 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="133">
         <v>13</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="131">
         <v>1.73</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="141">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="136">
         <v>1.65</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="132">
         <v>2.69</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="134">
         <v>6.07</v>
       </c>
-      <c r="O12" s="133">
+      <c r="O12" s="135">
         <v>12.39</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="142">
         <v>12.39</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="143">
         <v>11.53</v>
       </c>
       <c r="R12" s="137">
         <v>7.02</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="138">
         <v>5.55</v>
       </c>
-      <c r="T12" s="138">
+      <c r="T12" s="139">
         <v>-35.7</v>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="149" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,40 +9171,40 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="150">
         <v>4.11</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="153">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="146">
         <v>-2.4</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="154">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="155">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="148">
+      <c r="N13" s="156">
         <v>-10.96</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="151">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="149">
+      <c r="P13" s="152">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="144">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="147">
         <v>-17.12</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="148">
         <v>-19.86</v>
       </c>
-      <c r="T13" s="150">
+      <c r="T13" s="145">
         <v>-11.99</v>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="161" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,40 +9233,40 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="167">
         <v>5.15</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="168">
         <v>11.46</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="169">
         <v>22.61</v>
       </c>
-      <c r="L14" s="157">
+      <c r="L14" s="165">
         <v>10.3</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="159">
         <v>3.47</v>
       </c>
       <c r="N14" s="166">
         <v>-0.84</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="160">
         <v>2.52</v>
       </c>
-      <c r="P14" s="160">
+      <c r="P14" s="162">
         <v>2</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="163">
         <v>0.11</v>
       </c>
-      <c r="R14" s="167">
+      <c r="R14" s="157">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="164">
         <v>-2.73</v>
       </c>
-      <c r="T14" s="168">
+      <c r="T14" s="158">
         <v>-0.53</v>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,40 +9295,40 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="176">
         <v>4.02</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="170">
         <v>14.43</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="177">
         <v>2.94</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="171">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="174">
         <v>-7.46</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="180">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="172">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="176">
+      <c r="P15" s="175">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="181">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="178">
         <v>-9.22</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="182">
         <v>-6.58</v>
       </c>
-      <c r="T15" s="180">
+      <c r="T15" s="179">
         <v>-7.16</v>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9357,40 +9357,40 @@
       <c r="H16">
         <v>0.67</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="195">
         <v>9.22</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="183">
         <v>5.78</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="187">
         <v>6.22</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="184">
         <v>2.11</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="194">
         <v>2.67</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="191">
         <v>4.89</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="192">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="193">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="192">
+      <c r="Q16" s="185">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="186">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="188">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="193">
+      <c r="T16" s="189">
         <v>-19.78</v>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600192</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="208" t="str">
         <v>净买: 2508.47万</v>
       </c>
       <c r="E17">
@@ -9419,40 +9419,40 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="196">
         <v>14.66</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="201">
         <v>16.25</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="197">
         <v>13.66</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="198">
         <v>2.29</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="199">
         <v>0.9</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="204">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="205">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="202">
         <v>-6.38</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="203">
         <v>-5.38</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="200">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="196">
+      <c r="S17" s="207">
         <v>-1</v>
       </c>
-      <c r="T17" s="201">
+      <c r="T17" s="206">
         <v>-16.65</v>
       </c>
     </row>
@@ -9481,40 +9481,40 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="221">
         <v>-1.44</v>
       </c>
-      <c r="J18" s="216">
+      <c r="J18" s="217">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="211">
         <v>-13.27</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="209">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="209">
+      <c r="M18" s="210">
         <v>-16.74</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="218">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="219">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="213">
         <v>-19.78</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="214">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="215">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="212">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="212">
+      <c r="T18" s="216">
         <v>-29.33</v>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="233" t="str">
+      <c r="D19" s="222" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9543,25 +9543,25 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="234">
+      <c r="I19" s="223">
         <v>10</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="228">
         <v>8.88</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="229">
         <v>12.24</v>
       </c>
-      <c r="L19" s="222">
+      <c r="L19" s="232">
         <v>11.78</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="230">
         <v>9.28</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="231">
         <v>14.8</v>
       </c>
-      <c r="O19" s="223">
+      <c r="O19" s="233">
         <v>11.38</v>
       </c>
       <c r="P19" s="224">
@@ -9570,13 +9570,13 @@
       <c r="Q19" s="225">
         <v>6.71</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="226">
         <v>7.11</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="234">
         <v>7.37</v>
       </c>
-      <c r="T19" s="226">
+      <c r="T19" s="227">
         <v>-19.28</v>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>002553</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="237" t="str">
         <v>净买: 2010.54万</v>
       </c>
       <c r="E20">
@@ -9605,40 +9605,40 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="238">
         <v>2.6</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="241">
         <v>2.16</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="242">
         <v>3.16</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="243">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="244">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="239">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="245">
         <v>-1</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="236">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="246">
         <v>-0.64</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="247">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="245">
+      <c r="S20" s="240">
         <v>-3.04</v>
       </c>
-      <c r="T20" s="239">
+      <c r="T20" s="235">
         <v>0.96</v>
       </c>
     </row>
@@ -9667,40 +9667,40 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="255">
+      <c r="I21" s="248">
         <v>7.81</v>
       </c>
-      <c r="J21" s="248">
+      <c r="J21" s="256">
         <v>15.57</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="257">
         <v>9.09</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="249">
         <v>15.08</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="250">
         <v>3.57</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="258">
         <v>-2.42</v>
       </c>
-      <c r="O21" s="259">
+      <c r="O21" s="251">
         <v>-4.06</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="255">
         <v>-4.54</v>
       </c>
-      <c r="Q21" s="257">
+      <c r="Q21" s="259">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="252">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="258">
+      <c r="S21" s="253">
         <v>-2</v>
       </c>
-      <c r="T21" s="251">
+      <c r="T21" s="260">
         <v>239.92</v>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>000657</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="273" t="str">
         <v>净买: 6098.44万</v>
       </c>
       <c r="E22">
@@ -9729,40 +9729,40 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="273">
+      <c r="I22" s="266">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="270">
+      <c r="J22" s="261">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="269">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="267">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="261">
+      <c r="M22" s="270">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="262">
         <v>-13.43</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="268">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="272">
         <v>-11.6</v>
       </c>
-      <c r="Q22" s="268">
+      <c r="Q22" s="271">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="263">
         <v>-10.9</v>
       </c>
-      <c r="S22" s="272">
+      <c r="S22" s="264">
         <v>-8.81</v>
       </c>
-      <c r="T22" s="262">
+      <c r="T22" s="265">
         <v>201.4</v>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>600010</v>
       </c>
-      <c r="D23" s="283" t="str">
+      <c r="D23" s="279" t="str">
         <v>净卖: -1.03亿</v>
       </c>
       <c r="E23">
@@ -9791,40 +9791,40 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="284">
+      <c r="I23" s="280">
         <v>6.18</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="281">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="274">
         <v>-8</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="284">
         <v>-8.73</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="275">
         <v>-5.82</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="282">
         <v>-8</v>
       </c>
       <c r="O23" s="285">
         <v>-4.73</v>
       </c>
-      <c r="P23" s="286">
+      <c r="P23" s="276">
         <v>-6.18</v>
       </c>
-      <c r="Q23" s="281">
+      <c r="Q23" s="277">
         <v>-6.55</v>
       </c>
-      <c r="R23" s="274">
+      <c r="R23" s="283">
         <v>-8.73</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="278">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="275">
+      <c r="T23" s="286">
         <v>4</v>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="295" t="str">
+      <c r="D24" s="290" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,40 +9853,40 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="298">
+      <c r="I24" s="293">
         <v>14.91</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="291">
         <v>25.62</v>
       </c>
-      <c r="K24" s="289">
+      <c r="K24" s="287">
         <v>15.37</v>
       </c>
-      <c r="L24" s="290">
+      <c r="L24" s="296">
         <v>11.34</v>
       </c>
-      <c r="M24" s="294">
+      <c r="M24" s="297">
         <v>3.42</v>
       </c>
-      <c r="N24" s="296">
+      <c r="N24" s="298">
         <v>5.9</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="294">
         <v>12.42</v>
       </c>
-      <c r="P24" s="299">
+      <c r="P24" s="288">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="299">
         <v>7.92</v>
       </c>
-      <c r="R24" s="291">
+      <c r="R24" s="289">
         <v>5.59</v>
       </c>
-      <c r="S24" s="292">
+      <c r="S24" s="295">
         <v>11.02</v>
       </c>
-      <c r="T24" s="288">
+      <c r="T24" s="292">
         <v>17.08</v>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="302" t="str">
+      <c r="D25" s="309" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9915,40 +9915,40 @@
       <c r="H25">
         <v>2.57</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="300">
         <v>6.59</v>
       </c>
       <c r="J25" s="310">
         <v>-2.11</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="304">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="307">
+      <c r="L25" s="305">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="303">
+      <c r="M25" s="306">
         <v>-10.14</v>
       </c>
       <c r="N25" s="311">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="312">
+      <c r="O25" s="301">
         <v>-8.17</v>
       </c>
-      <c r="P25" s="308">
+      <c r="P25" s="302">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="304">
+      <c r="Q25" s="307">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="303">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="301">
+      <c r="S25" s="312">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="305">
+      <c r="T25" s="308">
         <v>-0.66</v>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>600117</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="325" t="str">
         <v>净卖: -2617.46万</v>
       </c>
       <c r="E26">
@@ -9977,40 +9977,40 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="315">
+      <c r="I26" s="320">
         <v>-4.81</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="322">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="322">
+      <c r="K26" s="316">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="313">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="325">
+      <c r="M26" s="321">
         <v>-21.44</v>
       </c>
       <c r="N26" s="323">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="316">
+      <c r="O26" s="317">
         <v>-24.05</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="314">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="315">
         <v>-27.45</v>
       </c>
       <c r="R26" s="324">
         <v>-27.25</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="318">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="317">
+      <c r="T26" s="319">
         <v>-48.5</v>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="333" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10039,40 +10039,40 @@
       <c r="H27">
         <v>-2.19</v>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="329">
         <v>7.83</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="330">
         <v>3.08</v>
       </c>
       <c r="K27" s="337">
         <v>1.68</v>
       </c>
-      <c r="L27" s="328">
+      <c r="L27" s="334">
         <v>0.28</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="326">
         <v>0.98</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="335">
         <v>-1.26</v>
       </c>
       <c r="O27" s="327">
         <v>-0.84</v>
       </c>
-      <c r="P27" s="334">
+      <c r="P27" s="331">
         <v>0.14</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="328">
         <v>4.06</v>
       </c>
       <c r="R27" s="338">
         <v>4.76</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="336">
         <v>2.66</v>
       </c>
-      <c r="T27" s="331">
+      <c r="T27" s="332">
         <v>-29.51</v>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="342" t="str">
+      <c r="D28" s="341" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10104,37 +10104,37 @@
       <c r="I28" s="349">
         <v>11.11</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="345">
         <v>22.22</v>
       </c>
-      <c r="K28" s="340">
+      <c r="K28" s="346">
         <v>9.95</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="342">
         <v>1.85</v>
       </c>
-      <c r="M28" s="347">
+      <c r="M28" s="351">
         <v>-5.32</v>
       </c>
-      <c r="N28" s="343">
+      <c r="N28" s="350">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="341">
+      <c r="O28" s="339">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="347">
         <v>-7.87</v>
       </c>
       <c r="Q28" s="348">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="343">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="340">
         <v>-10.19</v>
       </c>
-      <c r="T28" s="351">
+      <c r="T28" s="344">
         <v>-31.94</v>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>002097</v>
       </c>
-      <c r="D29" s="354" t="str">
+      <c r="D29" s="357" t="str">
         <v>净买: 6007.44万</v>
       </c>
       <c r="E29">
@@ -10163,40 +10163,40 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="359">
+      <c r="I29" s="354">
         <v>15.53</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="352">
         <v>19.33</v>
       </c>
-      <c r="K29" s="361">
+      <c r="K29" s="355">
         <v>21.27</v>
       </c>
-      <c r="L29" s="364">
+      <c r="L29" s="356">
         <v>28.8</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="361">
         <v>33.4</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="358">
         <v>28.73</v>
       </c>
-      <c r="O29" s="352">
+      <c r="O29" s="359">
         <v>25.33</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="362">
         <v>17.33</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="360">
         <v>13.93</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="363">
         <v>11.4</v>
       </c>
-      <c r="S29" s="360">
+      <c r="S29" s="364">
         <v>13</v>
       </c>
-      <c r="T29" s="363">
+      <c r="T29" s="353">
         <v>-33.13</v>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>601718</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="375" t="str">
         <v>净卖: -4886.83万</v>
       </c>
       <c r="E30">
@@ -10225,40 +10225,40 @@
       <c r="H30">
         <v>4.17</v>
       </c>
-      <c r="I30" s="365">
+      <c r="I30" s="366">
         <v>5.6</v>
       </c>
-      <c r="J30" s="372">
+      <c r="J30" s="376">
         <v>-5</v>
       </c>
-      <c r="K30" s="373">
+      <c r="K30" s="367">
         <v>-12</v>
       </c>
-      <c r="L30" s="374">
+      <c r="L30" s="370">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="369">
+      <c r="M30" s="371">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="368">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="366">
+      <c r="O30" s="372">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="376">
+      <c r="P30" s="373">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="370">
+      <c r="Q30" s="369">
         <v>-22</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="377">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="365">
         <v>-20.2</v>
       </c>
-      <c r="T30" s="377">
+      <c r="T30" s="374">
         <v>-41.2</v>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="390" t="str">
+      <c r="D31" s="379" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,40 +10287,40 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="382">
         <v>2.72</v>
       </c>
-      <c r="J31" s="379">
+      <c r="J31" s="380">
         <v>1.18</v>
       </c>
       <c r="K31" s="383">
         <v>-3.82</v>
       </c>
-      <c r="L31" s="387">
+      <c r="L31" s="385">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="386">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="381">
+      <c r="N31" s="388">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="388">
+      <c r="O31" s="389">
         <v>-10.28</v>
       </c>
-      <c r="P31" s="384">
+      <c r="P31" s="390">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="385">
+      <c r="Q31" s="384">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="387">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="389">
+      <c r="S31" s="378">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="386">
+      <c r="T31" s="381">
         <v>44.63</v>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600078</v>
       </c>
-      <c r="D32" s="403" t="str">
+      <c r="D32" s="393" t="str">
         <v>净买: 1268.44万</v>
       </c>
       <c r="E32">
@@ -10349,40 +10349,40 @@
       <c r="H32">
         <v>-0.92</v>
       </c>
-      <c r="I32" s="391">
+      <c r="I32" s="394">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="395">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="400">
         <v>-10.08</v>
       </c>
-      <c r="L32" s="392">
+      <c r="L32" s="396">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="393">
+      <c r="M32" s="399">
         <v>-0.93</v>
       </c>
-      <c r="N32" s="394">
+      <c r="N32" s="403">
         <v>-2.26</v>
       </c>
-      <c r="O32" s="400">
+      <c r="O32" s="397">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="401">
+      <c r="P32" s="391">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="402">
+      <c r="Q32" s="398">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="401">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="396">
+      <c r="S32" s="392">
         <v>1.44</v>
       </c>
-      <c r="T32" s="397">
+      <c r="T32" s="402">
         <v>33.85</v>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="411" t="str">
+      <c r="D33" s="410" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,40 +10411,40 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="414">
         <v>8.08</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="405">
         <v>6.62</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="415">
         <v>6.96</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="411">
         <v>7.52</v>
       </c>
-      <c r="M33" s="407">
+      <c r="M33" s="416">
         <v>5.27</v>
       </c>
-      <c r="N33" s="413">
+      <c r="N33" s="406">
         <v>3.03</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="412">
         <v>10.66</v>
       </c>
-      <c r="P33" s="408">
+      <c r="P33" s="407">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="405">
+      <c r="Q33" s="413">
         <v>34.01</v>
       </c>
-      <c r="R33" s="409">
+      <c r="R33" s="404">
         <v>47.36</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="408">
         <v>50.39</v>
       </c>
-      <c r="T33" s="410">
+      <c r="T33" s="409">
         <v>46.02</v>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="426" t="str">
+      <c r="D34" s="428" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10473,40 +10473,40 @@
       <c r="H34">
         <v>-4.48</v>
       </c>
-      <c r="I34" s="422">
+      <c r="I34" s="417">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="423">
+      <c r="J34" s="425">
         <v>0</v>
       </c>
-      <c r="K34" s="419">
+      <c r="K34" s="418">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="429">
+      <c r="L34" s="420">
         <v>4.61</v>
       </c>
-      <c r="M34" s="417">
+      <c r="M34" s="426">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="424">
+      <c r="N34" s="421">
         <v>-1.02</v>
       </c>
-      <c r="O34" s="427">
+      <c r="O34" s="419">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="427">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="422">
         <v>-16.33</v>
       </c>
-      <c r="R34" s="425">
+      <c r="R34" s="423">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="424">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="421">
+      <c r="T34" s="429">
         <v>1.64</v>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="436" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,40 +10535,40 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="436">
+      <c r="I35" s="441">
         <v>4.33</v>
       </c>
-      <c r="J35" s="433">
+      <c r="J35" s="442">
         <v>5.2</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="437">
         <v>-1.91</v>
       </c>
-      <c r="L35" s="437">
+      <c r="L35" s="438">
         <v>-4.85</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="440">
         <v>-6.07</v>
       </c>
-      <c r="N35" s="434">
+      <c r="N35" s="439">
         <v>-7.11</v>
       </c>
-      <c r="O35" s="438">
+      <c r="O35" s="430">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="433">
         <v>-10.4</v>
       </c>
-      <c r="Q35" s="432">
+      <c r="Q35" s="434">
         <v>-10.4</v>
       </c>
-      <c r="R35" s="439">
+      <c r="R35" s="431">
         <v>-8.49</v>
       </c>
       <c r="S35" s="435">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="440">
+      <c r="T35" s="432">
         <v>-8.15</v>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>301348</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="443" t="str">
         <v>净卖: -905.79万</v>
       </c>
       <c r="E36">
@@ -10597,40 +10597,40 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="450">
+      <c r="I36" s="449">
         <v>25.33</v>
       </c>
-      <c r="J36" s="451">
+      <c r="J36" s="444">
         <v>42.26</v>
       </c>
-      <c r="K36" s="445">
+      <c r="K36" s="450">
         <v>32.49</v>
       </c>
-      <c r="L36" s="454">
+      <c r="L36" s="447">
         <v>48.47</v>
       </c>
-      <c r="M36" s="446">
+      <c r="M36" s="451">
         <v>52.11</v>
       </c>
-      <c r="N36" s="455">
+      <c r="N36" s="445">
         <v>37.42</v>
       </c>
-      <c r="O36" s="447">
+      <c r="O36" s="452">
         <v>48.97</v>
       </c>
-      <c r="P36" s="448">
+      <c r="P36" s="446">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="444">
+      <c r="Q36" s="453">
         <v>31.29</v>
       </c>
-      <c r="R36" s="443">
+      <c r="R36" s="454">
         <v>26.08</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="448">
         <v>22.06</v>
       </c>
-      <c r="T36" s="449">
+      <c r="T36" s="455">
         <v>2.36</v>
       </c>
     </row>
@@ -10659,40 +10659,40 @@
       <c r="H37">
         <v>5.98</v>
       </c>
-      <c r="I37" s="464">
+      <c r="I37" s="460">
         <v>7.11</v>
       </c>
-      <c r="J37" s="468">
+      <c r="J37" s="464">
         <v>-0.25</v>
       </c>
       <c r="K37" s="465">
         <v>11.78</v>
       </c>
-      <c r="L37" s="459">
+      <c r="L37" s="468">
         <v>14.52</v>
       </c>
       <c r="M37" s="456">
         <v>3.46</v>
       </c>
-      <c r="N37" s="458">
+      <c r="N37" s="466">
         <v>12.15</v>
       </c>
-      <c r="O37" s="460">
+      <c r="O37" s="458">
         <v>7.42</v>
       </c>
-      <c r="P37" s="461">
+      <c r="P37" s="459">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="462">
+      <c r="Q37" s="457">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="463">
+      <c r="R37" s="461">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="466">
+      <c r="S37" s="462">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="457">
+      <c r="T37" s="463">
         <v>-22.94</v>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>000636</v>
       </c>
-      <c r="D38" s="472" t="str">
+      <c r="D38" s="470" t="str">
         <v>净卖: -226.93万</v>
       </c>
       <c r="E38">
@@ -10721,40 +10721,40 @@
       <c r="H38">
         <v>-1.06</v>
       </c>
-      <c r="I38" s="473">
+      <c r="I38" s="471">
         <v>11.17</v>
       </c>
-      <c r="J38" s="479">
+      <c r="J38" s="469">
         <v>3.8</v>
       </c>
-      <c r="K38" s="476">
+      <c r="K38" s="473">
         <v>2.93</v>
       </c>
-      <c r="L38" s="480">
+      <c r="L38" s="478">
         <v>3.61</v>
       </c>
-      <c r="M38" s="477">
+      <c r="M38" s="479">
         <v>2.73</v>
       </c>
-      <c r="N38" s="471">
+      <c r="N38" s="474">
         <v>9.9</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="472">
         <v>3.76</v>
       </c>
-      <c r="P38" s="481">
+      <c r="P38" s="480">
         <v>14.15</v>
       </c>
-      <c r="Q38" s="469">
+      <c r="Q38" s="475">
         <v>25.56</v>
       </c>
-      <c r="R38" s="478">
+      <c r="R38" s="481">
         <v>25.51</v>
       </c>
-      <c r="S38" s="470">
+      <c r="S38" s="476">
         <v>26.83</v>
       </c>
-      <c r="T38" s="475">
+      <c r="T38" s="477">
         <v>7.27</v>
       </c>
     </row>
@@ -10817,40 +10817,40 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="488">
+      <c r="I40" s="493">
         <v>78.38</v>
       </c>
-      <c r="J40" s="485">
+      <c r="J40" s="490">
         <v>62.16</v>
       </c>
-      <c r="K40" s="489">
+      <c r="K40" s="487">
         <v>56.76</v>
       </c>
-      <c r="L40" s="492">
+      <c r="L40" s="491">
         <v>59.46</v>
       </c>
-      <c r="M40" s="493">
+      <c r="M40" s="482">
         <v>51.35</v>
       </c>
-      <c r="N40" s="486">
+      <c r="N40" s="483">
         <v>40.54</v>
       </c>
-      <c r="O40" s="487">
+      <c r="O40" s="492">
         <v>37.84</v>
       </c>
-      <c r="P40" s="482">
+      <c r="P40" s="484">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="490">
+      <c r="Q40" s="485">
         <v>40.54</v>
       </c>
-      <c r="R40" s="491">
+      <c r="R40" s="488">
         <v>37.84</v>
       </c>
-      <c r="S40" s="483">
+      <c r="S40" s="486">
         <v>40.54</v>
       </c>
-      <c r="T40" s="484">
+      <c r="T40" s="489">
         <v>29.73</v>
       </c>
     </row>
@@ -10865,40 +10865,40 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="500">
+      <c r="I41" s="501">
         <v>5.97</v>
       </c>
-      <c r="J41" s="501">
+      <c r="J41" s="503">
         <v>4.69</v>
       </c>
-      <c r="K41" s="494">
+      <c r="K41" s="497">
         <v>2.99</v>
       </c>
-      <c r="L41" s="495">
+      <c r="L41" s="504">
         <v>2.46</v>
       </c>
-      <c r="M41" s="504">
+      <c r="M41" s="505">
         <v>0.83</v>
       </c>
-      <c r="N41" s="502">
+      <c r="N41" s="498">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="496">
+      <c r="O41" s="502">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="505">
+      <c r="P41" s="499">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="497">
+      <c r="Q41" s="495">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="498">
+      <c r="R41" s="496">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="499">
+      <c r="S41" s="494">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="503">
+      <c r="T41" s="500">
         <v>0.28</v>
       </c>
     </row>

--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,48 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -93,13 +117,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,85 +219,637 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,13 +861,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FFF2B9BE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,13 +897,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,25 +915,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,6 +993,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -291,2779 +1035,2035 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC7E8CE"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDFF2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,40 +8489,40 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>9.99</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="5">
         <v>13.15</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="12">
         <v>9.95</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="13">
         <v>8.34</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="1">
         <v>9.06</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="6">
         <v>5.46</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="7">
         <v>3.94</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="3">
         <v>0.04</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="8">
         <v>1.19</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="4">
         <v>0.13</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="9">
         <v>-16.67</v>
       </c>
     </row>
@@ -8557,34 +8557,34 @@
       <c r="J3" s="16">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="17">
         <v>-15.92</v>
       </c>
       <c r="L3" s="20">
         <v>-14.66</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="18">
         <v>-9.78</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="21">
         <v>-11.59</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="19">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="24">
         <v>-15.36</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="25">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="26">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="22">
         <v>-15.92</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="23">
         <v>-29.61</v>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>601008</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 2459.29万</v>
       </c>
       <c r="E4">
@@ -8613,16 +8613,16 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="28">
         <v>8.18</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="37">
         <v>-2.55</v>
       </c>
       <c r="K4" s="33">
         <v>-0.36</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="34">
         <v>0.18</v>
       </c>
       <c r="M4" s="38">
@@ -8631,22 +8631,22 @@
       <c r="N4" s="29">
         <v>-7.64</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="35">
         <v>-7.64</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="39">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="36">
         <v>11.82</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="30">
         <v>23.09</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="32">
         <v>35.45</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="31">
         <v>-12.18</v>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="48" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,40 +8675,40 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="52">
         <v>11.02</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="40">
         <v>8.91</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="41">
         <v>19.8</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="46">
         <v>19.08</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="49">
         <v>19.87</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="50">
         <v>13</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="42">
         <v>12.87</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="51">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="47">
         <v>7.46</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="43">
         <v>5.61</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="44">
         <v>4.49</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="45">
         <v>-19.01</v>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8737,40 +8737,40 @@
       <c r="H6">
         <v>-1.7</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="62">
         <v>11.92</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="54">
         <v>13.13</v>
       </c>
       <c r="K6" s="63">
         <v>17.96</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="55">
         <v>22.02</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="59">
         <v>16.84</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="56">
         <v>9.93</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="57">
         <v>7.43</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="58">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="64">
         <v>9.93</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="60">
         <v>12.61</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="61">
         <v>23.83</v>
       </c>
-      <c r="T6" s="56">
+      <c r="T6" s="65">
         <v>-22.28</v>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8799,10 +8799,10 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="69">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="76">
         <v>-12.07</v>
       </c>
       <c r="K7" s="77">
@@ -8811,28 +8811,28 @@
       <c r="L7" s="78">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="74">
         <v>-14.58</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="75">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="66">
         <v>-23.59</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="67">
         <v>-22.96</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="68">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="70">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="71">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="74">
+      <c r="T7" s="72">
         <v>-23.75</v>
       </c>
     </row>
@@ -8864,13 +8864,13 @@
       <c r="I8" s="81">
         <v>11.25</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="87">
         <v>10.01</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="88">
         <v>21.01</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="82">
         <v>18.67</v>
       </c>
       <c r="M8" s="83">
@@ -8879,10 +8879,10 @@
       <c r="N8" s="90">
         <v>21.76</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="91">
         <v>17.43</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="84">
         <v>16.19</v>
       </c>
       <c r="Q8" s="85">
@@ -8894,7 +8894,7 @@
       <c r="S8" s="79">
         <v>15.95</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="89">
         <v>-21.88</v>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>002094</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -3419.88万</v>
       </c>
       <c r="E9">
@@ -8923,40 +8923,40 @@
       <c r="H9">
         <v>2.78</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="93">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="98">
         <v>5.84</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="102">
         <v>3.78</v>
       </c>
       <c r="L9" s="99">
         <v>6.81</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="103">
         <v>6.49</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="100">
         <v>2.7</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="104">
         <v>1.62</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="94">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="95">
         <v>8.22</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="96">
         <v>1.41</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="97">
         <v>0.22</v>
       </c>
-      <c r="T9" s="103">
+      <c r="T9" s="92">
         <v>-31.68</v>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,40 +8985,40 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="117">
         <v>11.08</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="105">
         <v>0</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="107">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="111">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="112">
         <v>-16.07</v>
       </c>
-      <c r="N10" s="117">
+      <c r="N10" s="108">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="114">
         <v>-11.64</v>
       </c>
       <c r="P10" s="109">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="115">
         <v>-19.06</v>
       </c>
-      <c r="R10" s="112">
+      <c r="R10" s="116">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="106">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="106">
+      <c r="T10" s="113">
         <v>-22.42</v>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="127" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,40 +9047,40 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="129">
+      <c r="I11" s="120">
         <v>9.97</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="118">
         <v>5.4</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="128">
         <v>3.74</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="124">
         <v>7.89</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="121">
         <v>5.19</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="125">
         <v>1.14</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="126">
         <v>-0.31</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="119">
         <v>-6.65</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="122">
         <v>-3.32</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="123">
         <v>-8.62</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="129">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="121">
+      <c r="T11" s="130">
         <v>-32.92</v>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="132" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,37 +9109,37 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="140">
         <v>13</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="141">
         <v>1.73</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="133">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="137">
         <v>1.65</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="134">
         <v>2.69</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="138">
         <v>6.07</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="142">
         <v>12.39</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="136">
         <v>12.39</v>
       </c>
       <c r="Q12" s="143">
         <v>11.53</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="135">
         <v>7.02</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="131">
         <v>5.55</v>
       </c>
       <c r="T12" s="139">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="149" t="str">
+      <c r="D13" s="146" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,37 +9171,37 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="155">
         <v>4.11</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="152">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="149">
         <v>-2.4</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="156">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="147">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="150">
         <v>-10.96</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="153">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="151">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="148">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="154">
         <v>-17.12</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="144">
         <v>-19.86</v>
       </c>
       <c r="T13" s="145">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="163" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,37 +9233,37 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="164">
         <v>5.15</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="165">
         <v>11.46</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="159">
         <v>22.61</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="166">
         <v>10.3</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="161">
         <v>3.47</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="167">
         <v>-0.84</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="168">
         <v>2.52</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="160">
         <v>2</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="162">
         <v>0.11</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="169">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="157">
         <v>-2.73</v>
       </c>
       <c r="T14" s="158">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="170" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,37 +9295,37 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="171">
         <v>4.02</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="174">
         <v>14.43</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="172">
         <v>2.94</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="175">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="176">
         <v>-7.46</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="177">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="180">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="181">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="178">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="182">
         <v>-9.22</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="173">
         <v>-6.58</v>
       </c>
       <c r="T15" s="179">
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="191" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9357,40 +9357,40 @@
       <c r="H16">
         <v>0.67</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="186">
         <v>9.22</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="192">
         <v>5.78</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="195">
         <v>6.22</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="188">
         <v>2.11</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="189">
         <v>2.67</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="183">
         <v>4.89</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="184">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="190">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="193">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="185">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="187">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="189">
+      <c r="T16" s="194">
         <v>-19.78</v>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600192</v>
       </c>
-      <c r="D17" s="208" t="str">
+      <c r="D17" s="197" t="str">
         <v>净买: 2508.47万</v>
       </c>
       <c r="E17">
@@ -9419,40 +9419,40 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="203">
         <v>14.66</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="198">
         <v>16.25</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="199">
         <v>13.66</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="200">
         <v>2.29</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="205">
         <v>0.9</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="201">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="205">
+      <c r="O17" s="206">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="207">
         <v>-6.38</v>
       </c>
-      <c r="Q17" s="203">
+      <c r="Q17" s="208">
         <v>-5.38</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="196">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="204">
         <v>-1</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="202">
         <v>-16.65</v>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>600192</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="213" t="str">
         <v>净卖: -2805.31万</v>
       </c>
       <c r="E18">
@@ -9481,40 +9481,40 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="221">
+      <c r="I18" s="211">
         <v>-1.44</v>
       </c>
-      <c r="J18" s="217">
+      <c r="J18" s="220">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="216">
         <v>-13.27</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="221">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="210">
+      <c r="M18" s="212">
         <v>-16.74</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="217">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="218">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="209">
         <v>-19.78</v>
       </c>
       <c r="Q18" s="214">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="210">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="219">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="216">
+      <c r="T18" s="215">
         <v>-29.33</v>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="224" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9543,40 +9543,40 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="227">
         <v>10</v>
       </c>
       <c r="J19" s="228">
         <v>8.88</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="225">
         <v>12.24</v>
       </c>
-      <c r="L19" s="232">
+      <c r="L19" s="234">
         <v>11.78</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="229">
         <v>9.28</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="222">
         <v>14.8</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="230">
         <v>11.38</v>
       </c>
-      <c r="P19" s="224">
+      <c r="P19" s="231">
         <v>6.25</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="232">
         <v>6.71</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="233">
         <v>7.11</v>
       </c>
-      <c r="S19" s="234">
+      <c r="S19" s="223">
         <v>7.37</v>
       </c>
-      <c r="T19" s="227">
+      <c r="T19" s="226">
         <v>-19.28</v>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>002553</v>
       </c>
-      <c r="D20" s="237" t="str">
+      <c r="D20" s="240" t="str">
         <v>净买: 2010.54万</v>
       </c>
       <c r="E20">
@@ -9605,40 +9605,40 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="241">
         <v>2.6</v>
       </c>
-      <c r="J20" s="241">
+      <c r="J20" s="242">
         <v>2.16</v>
       </c>
-      <c r="K20" s="242">
+      <c r="K20" s="243">
         <v>3.16</v>
       </c>
-      <c r="L20" s="243">
+      <c r="L20" s="238">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="244">
+      <c r="M20" s="235">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="236">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="245">
+      <c r="O20" s="237">
         <v>-1</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="246">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="246">
+      <c r="Q20" s="244">
         <v>-0.64</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="245">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="247">
         <v>-3.04</v>
       </c>
-      <c r="T20" s="235">
+      <c r="T20" s="239">
         <v>0.96</v>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>000657</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="251" t="str">
         <v>净卖: -1.62亿</v>
       </c>
       <c r="E21">
@@ -9667,40 +9667,40 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="252">
         <v>7.81</v>
       </c>
-      <c r="J21" s="256">
+      <c r="J21" s="253">
         <v>15.57</v>
       </c>
       <c r="K21" s="257">
         <v>9.09</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="258">
         <v>15.08</v>
       </c>
-      <c r="M21" s="250">
+      <c r="M21" s="254">
         <v>3.57</v>
       </c>
-      <c r="N21" s="258">
+      <c r="N21" s="259">
         <v>-2.42</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="249">
         <v>-4.06</v>
       </c>
       <c r="P21" s="255">
         <v>-4.54</v>
       </c>
-      <c r="Q21" s="259">
+      <c r="Q21" s="260">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="248">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="250">
         <v>-2</v>
       </c>
-      <c r="T21" s="260">
+      <c r="T21" s="256">
         <v>239.92</v>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>000657</v>
       </c>
-      <c r="D22" s="273" t="str">
+      <c r="D22" s="269" t="str">
         <v>净买: 6098.44万</v>
       </c>
       <c r="E22">
@@ -9729,40 +9729,40 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="266">
+      <c r="I22" s="270">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="261">
+      <c r="J22" s="265">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="269">
+      <c r="K22" s="271">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="267">
+      <c r="L22" s="272">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="267">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="273">
         <v>-13.43</v>
       </c>
-      <c r="O22" s="268">
+      <c r="O22" s="266">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="262">
         <v>-11.6</v>
       </c>
-      <c r="Q22" s="271">
+      <c r="Q22" s="263">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="264">
         <v>-10.9</v>
       </c>
-      <c r="S22" s="264">
+      <c r="S22" s="261">
         <v>-8.81</v>
       </c>
-      <c r="T22" s="265">
+      <c r="T22" s="268">
         <v>201.4</v>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>600010</v>
       </c>
-      <c r="D23" s="279" t="str">
+      <c r="D23" s="286" t="str">
         <v>净卖: -1.03亿</v>
       </c>
       <c r="E23">
@@ -9791,19 +9791,19 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="280">
+      <c r="I23" s="274">
         <v>6.18</v>
       </c>
-      <c r="J23" s="281">
+      <c r="J23" s="278">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="274">
+      <c r="K23" s="275">
         <v>-8</v>
       </c>
       <c r="L23" s="284">
         <v>-8.73</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="279">
         <v>-5.82</v>
       </c>
       <c r="N23" s="282">
@@ -9815,16 +9815,16 @@
       <c r="P23" s="276">
         <v>-6.18</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="280">
         <v>-6.55</v>
       </c>
       <c r="R23" s="283">
         <v>-8.73</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="281">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="286">
+      <c r="T23" s="277">
         <v>4</v>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="290" t="str">
+      <c r="D24" s="299" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,40 +9853,40 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="293">
+      <c r="I24" s="291">
         <v>14.91</v>
       </c>
-      <c r="J24" s="291">
+      <c r="J24" s="292">
         <v>25.62</v>
       </c>
       <c r="K24" s="287">
         <v>15.37</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="288">
         <v>11.34</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="293">
         <v>3.42</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="296">
         <v>5.9</v>
       </c>
-      <c r="O24" s="294">
+      <c r="O24" s="289">
         <v>12.42</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="297">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="299">
+      <c r="Q24" s="294">
         <v>7.92</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="298">
         <v>5.59</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="290">
         <v>11.02</v>
       </c>
-      <c r="T24" s="292">
+      <c r="T24" s="295">
         <v>17.08</v>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="309" t="str">
+      <c r="D25" s="308" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9915,40 +9915,40 @@
       <c r="H25">
         <v>2.57</v>
       </c>
-      <c r="I25" s="300">
+      <c r="I25" s="309">
         <v>6.59</v>
       </c>
-      <c r="J25" s="310">
+      <c r="J25" s="301">
         <v>-2.11</v>
       </c>
-      <c r="K25" s="304">
+      <c r="K25" s="302">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="305">
+      <c r="L25" s="303">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="304">
         <v>-10.14</v>
       </c>
-      <c r="N25" s="311">
+      <c r="N25" s="310">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="311">
         <v>-8.17</v>
       </c>
-      <c r="P25" s="302">
+      <c r="P25" s="305">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="306">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="303">
+      <c r="R25" s="312">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="300">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="308">
+      <c r="T25" s="307">
         <v>-0.66</v>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>600117</v>
       </c>
-      <c r="D26" s="325" t="str">
+      <c r="D26" s="322" t="str">
         <v>净卖: -2617.46万</v>
       </c>
       <c r="E26">
@@ -9977,40 +9977,40 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="320">
+      <c r="I26" s="323">
         <v>-4.81</v>
       </c>
-      <c r="J26" s="322">
+      <c r="J26" s="314">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="324">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="313">
+      <c r="L26" s="325">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="321">
+      <c r="M26" s="315">
         <v>-21.44</v>
       </c>
-      <c r="N26" s="323">
+      <c r="N26" s="318">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="317">
+      <c r="O26" s="316">
         <v>-24.05</v>
       </c>
-      <c r="P26" s="314">
+      <c r="P26" s="317">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="315">
+      <c r="Q26" s="313">
         <v>-27.45</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="319">
         <v>-27.25</v>
       </c>
-      <c r="S26" s="318">
+      <c r="S26" s="320">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="319">
+      <c r="T26" s="321">
         <v>-48.5</v>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="333" t="str">
+      <c r="D27" s="330" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10039,40 +10039,40 @@
       <c r="H27">
         <v>-2.19</v>
       </c>
-      <c r="I27" s="329">
+      <c r="I27" s="337">
         <v>7.83</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="331">
         <v>3.08</v>
       </c>
-      <c r="K27" s="337">
+      <c r="K27" s="338">
         <v>1.68</v>
       </c>
-      <c r="L27" s="334">
+      <c r="L27" s="327">
         <v>0.28</v>
       </c>
-      <c r="M27" s="326">
+      <c r="M27" s="328">
         <v>0.98</v>
       </c>
-      <c r="N27" s="335">
+      <c r="N27" s="332">
         <v>-1.26</v>
       </c>
-      <c r="O27" s="327">
+      <c r="O27" s="326">
         <v>-0.84</v>
       </c>
-      <c r="P27" s="331">
+      <c r="P27" s="333">
         <v>0.14</v>
       </c>
-      <c r="Q27" s="328">
+      <c r="Q27" s="329">
         <v>4.06</v>
       </c>
-      <c r="R27" s="338">
+      <c r="R27" s="334">
         <v>4.76</v>
       </c>
-      <c r="S27" s="336">
+      <c r="S27" s="335">
         <v>2.66</v>
       </c>
-      <c r="T27" s="332">
+      <c r="T27" s="336">
         <v>-29.51</v>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="351" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10101,37 +10101,37 @@
       <c r="H28">
         <v>-0.92</v>
       </c>
-      <c r="I28" s="349">
+      <c r="I28" s="339">
         <v>11.11</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="348">
         <v>22.22</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="340">
         <v>9.95</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="349">
         <v>1.85</v>
       </c>
-      <c r="M28" s="351">
+      <c r="M28" s="345">
         <v>-5.32</v>
       </c>
-      <c r="N28" s="350">
+      <c r="N28" s="346">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="341">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="347">
+      <c r="P28" s="342">
         <v>-7.87</v>
       </c>
-      <c r="Q28" s="348">
+      <c r="Q28" s="343">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="347">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="340">
+      <c r="S28" s="350">
         <v>-10.19</v>
       </c>
       <c r="T28" s="344">
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>002097</v>
       </c>
-      <c r="D29" s="357" t="str">
+      <c r="D29" s="356" t="str">
         <v>净买: 6007.44万</v>
       </c>
       <c r="E29">
@@ -10163,40 +10163,40 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="354">
+      <c r="I29" s="357">
         <v>15.53</v>
       </c>
-      <c r="J29" s="352">
+      <c r="J29" s="358">
         <v>19.33</v>
       </c>
-      <c r="K29" s="355">
+      <c r="K29" s="361">
         <v>21.27</v>
       </c>
-      <c r="L29" s="356">
+      <c r="L29" s="359">
         <v>28.8</v>
       </c>
-      <c r="M29" s="361">
+      <c r="M29" s="362">
         <v>33.4</v>
       </c>
-      <c r="N29" s="358">
+      <c r="N29" s="360">
         <v>28.73</v>
       </c>
-      <c r="O29" s="359">
+      <c r="O29" s="353">
         <v>25.33</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="363">
         <v>17.33</v>
       </c>
-      <c r="Q29" s="360">
+      <c r="Q29" s="364">
         <v>13.93</v>
       </c>
-      <c r="R29" s="363">
+      <c r="R29" s="352">
         <v>11.4</v>
       </c>
-      <c r="S29" s="364">
+      <c r="S29" s="354">
         <v>13</v>
       </c>
-      <c r="T29" s="353">
+      <c r="T29" s="355">
         <v>-33.13</v>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>601718</v>
       </c>
-      <c r="D30" s="375" t="str">
+      <c r="D30" s="365" t="str">
         <v>净卖: -4886.83万</v>
       </c>
       <c r="E30">
@@ -10228,37 +10228,37 @@
       <c r="I30" s="366">
         <v>5.6</v>
       </c>
-      <c r="J30" s="376">
+      <c r="J30" s="375">
         <v>-5</v>
       </c>
-      <c r="K30" s="367">
+      <c r="K30" s="369">
         <v>-12</v>
       </c>
-      <c r="L30" s="370">
+      <c r="L30" s="373">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="371">
+      <c r="M30" s="376">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="368">
+      <c r="N30" s="370">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="367">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="371">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="369">
+      <c r="Q30" s="377">
         <v>-22</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="374">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="365">
+      <c r="S30" s="368">
         <v>-20.2</v>
       </c>
-      <c r="T30" s="374">
+      <c r="T30" s="372">
         <v>-41.2</v>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="379" t="str">
+      <c r="D31" s="382" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,40 +10287,40 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="379">
         <v>2.72</v>
       </c>
-      <c r="J31" s="380">
+      <c r="J31" s="390">
         <v>1.18</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="378">
         <v>-3.82</v>
       </c>
-      <c r="L31" s="385">
+      <c r="L31" s="380">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="386">
+      <c r="M31" s="388">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="388">
+      <c r="N31" s="383">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="389">
+      <c r="O31" s="384">
         <v>-10.28</v>
       </c>
-      <c r="P31" s="390">
+      <c r="P31" s="389">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="384">
+      <c r="Q31" s="381">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="385">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="378">
+      <c r="S31" s="386">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="381">
+      <c r="T31" s="387">
         <v>44.63</v>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600078</v>
       </c>
-      <c r="D32" s="393" t="str">
+      <c r="D32" s="394" t="str">
         <v>净买: 1268.44万</v>
       </c>
       <c r="E32">
@@ -10349,40 +10349,40 @@
       <c r="H32">
         <v>-0.92</v>
       </c>
-      <c r="I32" s="394">
+      <c r="I32" s="402">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="398">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="400">
+      <c r="K32" s="403">
         <v>-10.08</v>
       </c>
-      <c r="L32" s="396">
+      <c r="L32" s="391">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="399">
+      <c r="M32" s="392">
         <v>-0.93</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="393">
         <v>-2.26</v>
       </c>
-      <c r="O32" s="397">
+      <c r="O32" s="399">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="396">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="398">
+      <c r="Q32" s="397">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="400">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="392">
+      <c r="S32" s="395">
         <v>1.44</v>
       </c>
-      <c r="T32" s="402">
+      <c r="T32" s="401">
         <v>33.85</v>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="415" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,40 +10411,40 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="416">
         <v>8.08</v>
       </c>
-      <c r="J33" s="405">
+      <c r="J33" s="407">
         <v>6.62</v>
       </c>
-      <c r="K33" s="415">
+      <c r="K33" s="404">
         <v>6.96</v>
       </c>
       <c r="L33" s="411">
         <v>7.52</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="408">
         <v>5.27</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="409">
         <v>3.03</v>
       </c>
       <c r="O33" s="412">
         <v>10.66</v>
       </c>
-      <c r="P33" s="407">
+      <c r="P33" s="405">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="413">
+      <c r="Q33" s="406">
         <v>34.01</v>
       </c>
-      <c r="R33" s="404">
+      <c r="R33" s="413">
         <v>47.36</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="410">
         <v>50.39</v>
       </c>
-      <c r="T33" s="409">
+      <c r="T33" s="414">
         <v>46.02</v>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="428" t="str">
+      <c r="D34" s="429" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10476,37 +10476,37 @@
       <c r="I34" s="417">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="425">
+      <c r="J34" s="422">
         <v>0</v>
       </c>
       <c r="K34" s="418">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="420">
+      <c r="L34" s="423">
         <v>4.61</v>
       </c>
-      <c r="M34" s="426">
+      <c r="M34" s="421">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="421">
+      <c r="N34" s="424">
         <v>-1.02</v>
       </c>
       <c r="O34" s="419">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="425">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="422">
+      <c r="Q34" s="426">
         <v>-16.33</v>
       </c>
-      <c r="R34" s="423">
+      <c r="R34" s="427">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="424">
+      <c r="S34" s="420">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="429">
+      <c r="T34" s="428">
         <v>1.64</v>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="430" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,40 +10535,40 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="441">
+      <c r="I35" s="431">
         <v>4.33</v>
       </c>
-      <c r="J35" s="442">
+      <c r="J35" s="437">
         <v>5.2</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="435">
         <v>-1.91</v>
       </c>
       <c r="L35" s="438">
         <v>-4.85</v>
       </c>
-      <c r="M35" s="440">
+      <c r="M35" s="432">
         <v>-6.07</v>
       </c>
-      <c r="N35" s="439">
+      <c r="N35" s="433">
         <v>-7.11</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="441">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="433">
+      <c r="P35" s="439">
         <v>-10.4</v>
       </c>
-      <c r="Q35" s="434">
+      <c r="Q35" s="442">
         <v>-10.4</v>
       </c>
-      <c r="R35" s="431">
+      <c r="R35" s="440">
         <v>-8.49</v>
       </c>
-      <c r="S35" s="435">
+      <c r="S35" s="436">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="432">
+      <c r="T35" s="434">
         <v>-8.15</v>
       </c>
     </row>
@@ -10597,40 +10597,40 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="449">
+      <c r="I36" s="453">
         <v>25.33</v>
       </c>
-      <c r="J36" s="444">
+      <c r="J36" s="448">
         <v>42.26</v>
       </c>
-      <c r="K36" s="450">
+      <c r="K36" s="454">
         <v>32.49</v>
       </c>
-      <c r="L36" s="447">
+      <c r="L36" s="449">
         <v>48.47</v>
       </c>
-      <c r="M36" s="451">
+      <c r="M36" s="446">
         <v>52.11</v>
       </c>
-      <c r="N36" s="445">
+      <c r="N36" s="455">
         <v>37.42</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="444">
         <v>48.97</v>
       </c>
-      <c r="P36" s="446">
+      <c r="P36" s="450">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="453">
+      <c r="Q36" s="451">
         <v>31.29</v>
       </c>
-      <c r="R36" s="454">
+      <c r="R36" s="445">
         <v>26.08</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="452">
         <v>22.06</v>
       </c>
-      <c r="T36" s="455">
+      <c r="T36" s="447">
         <v>2.36</v>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>301348</v>
       </c>
-      <c r="D37" s="467" t="str">
+      <c r="D37" s="468" t="str">
         <v>净卖: -4537.41万</v>
       </c>
       <c r="E37">
@@ -10659,40 +10659,40 @@
       <c r="H37">
         <v>5.98</v>
       </c>
-      <c r="I37" s="460">
+      <c r="I37" s="459">
         <v>7.11</v>
       </c>
-      <c r="J37" s="464">
+      <c r="J37" s="456">
         <v>-0.25</v>
       </c>
-      <c r="K37" s="465">
+      <c r="K37" s="463">
         <v>11.78</v>
       </c>
-      <c r="L37" s="468">
+      <c r="L37" s="457">
         <v>14.52</v>
       </c>
-      <c r="M37" s="456">
+      <c r="M37" s="466">
         <v>3.46</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="460">
         <v>12.15</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="461">
         <v>7.42</v>
       </c>
-      <c r="P37" s="459">
+      <c r="P37" s="464">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="458">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="461">
+      <c r="R37" s="462">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="462">
+      <c r="S37" s="465">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="463">
+      <c r="T37" s="467">
         <v>-22.94</v>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>000636</v>
       </c>
-      <c r="D38" s="470" t="str">
+      <c r="D38" s="477" t="str">
         <v>净卖: -226.93万</v>
       </c>
       <c r="E38">
@@ -10721,40 +10721,40 @@
       <c r="H38">
         <v>-1.06</v>
       </c>
-      <c r="I38" s="471">
+      <c r="I38" s="474">
         <v>11.17</v>
       </c>
-      <c r="J38" s="469">
+      <c r="J38" s="475">
         <v>3.8</v>
       </c>
-      <c r="K38" s="473">
+      <c r="K38" s="478">
         <v>2.93</v>
       </c>
-      <c r="L38" s="478">
+      <c r="L38" s="472">
         <v>3.61</v>
       </c>
-      <c r="M38" s="479">
+      <c r="M38" s="473">
         <v>2.73</v>
       </c>
-      <c r="N38" s="474">
+      <c r="N38" s="481">
         <v>9.9</v>
       </c>
-      <c r="O38" s="472">
+      <c r="O38" s="469">
         <v>3.76</v>
       </c>
-      <c r="P38" s="480">
+      <c r="P38" s="470">
         <v>14.15</v>
       </c>
-      <c r="Q38" s="475">
+      <c r="Q38" s="479">
         <v>25.56</v>
       </c>
-      <c r="R38" s="481">
+      <c r="R38" s="471">
         <v>25.51</v>
       </c>
       <c r="S38" s="476">
         <v>26.83</v>
       </c>
-      <c r="T38" s="477">
+      <c r="T38" s="480">
         <v>7.27</v>
       </c>
     </row>
@@ -10820,37 +10820,37 @@
       <c r="I40" s="493">
         <v>78.38</v>
       </c>
-      <c r="J40" s="490">
+      <c r="J40" s="485">
         <v>62.16</v>
       </c>
-      <c r="K40" s="487">
+      <c r="K40" s="489">
         <v>56.76</v>
       </c>
-      <c r="L40" s="491">
+      <c r="L40" s="486">
         <v>59.46</v>
       </c>
-      <c r="M40" s="482">
+      <c r="M40" s="490">
         <v>51.35</v>
       </c>
-      <c r="N40" s="483">
+      <c r="N40" s="491">
         <v>40.54</v>
       </c>
-      <c r="O40" s="492">
+      <c r="O40" s="483">
         <v>37.84</v>
       </c>
-      <c r="P40" s="484">
+      <c r="P40" s="487">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="485">
+      <c r="Q40" s="482">
         <v>40.54</v>
       </c>
-      <c r="R40" s="488">
+      <c r="R40" s="492">
         <v>37.84</v>
       </c>
-      <c r="S40" s="486">
+      <c r="S40" s="484">
         <v>40.54</v>
       </c>
-      <c r="T40" s="489">
+      <c r="T40" s="488">
         <v>29.73</v>
       </c>
     </row>
@@ -10868,37 +10868,37 @@
       <c r="I41" s="501">
         <v>5.97</v>
       </c>
-      <c r="J41" s="503">
+      <c r="J41" s="502">
         <v>4.69</v>
       </c>
-      <c r="K41" s="497">
+      <c r="K41" s="503">
         <v>2.99</v>
       </c>
-      <c r="L41" s="504">
+      <c r="L41" s="496">
         <v>2.46</v>
       </c>
-      <c r="M41" s="505">
+      <c r="M41" s="499">
         <v>0.83</v>
       </c>
-      <c r="N41" s="498">
+      <c r="N41" s="504">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="502">
+      <c r="O41" s="500">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="499">
+      <c r="P41" s="494">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="495">
+      <c r="Q41" s="497">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="496">
+      <c r="R41" s="498">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="494">
+      <c r="S41" s="505">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="500">
+      <c r="T41" s="495">
         <v>0.28</v>
       </c>
     </row>

--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,25 +39,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0212F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,25 +207,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,6 +225,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -111,7 +405,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,73 +495,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,13 +531,2353 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBA2533"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,7 +2889,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,49 +2913,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,25 +2979,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF56B96C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,883 +3027,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1209,1861 +3063,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,41 +8489,41 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="8">
         <v>9.99</v>
       </c>
       <c r="J2" s="5">
         <v>13.15</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="11">
         <v>9.95</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="6">
         <v>8.34</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="13">
         <v>9.06</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="9">
         <v>5.46</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="1">
         <v>3.94</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="10">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="7">
         <v>0.04</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="12">
         <v>1.19</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="2">
         <v>0.13</v>
       </c>
-      <c r="T2" s="9">
-        <v>-16.67</v>
+      <c r="T2" s="3">
+        <v>-16.07</v>
       </c>
     </row>
     <row r="3">
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002570</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -3219.58万</v>
       </c>
       <c r="E3">
@@ -8551,40 +8551,40 @@
       <c r="H3">
         <v>-1.51</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="22">
         <v>-8.66</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="25">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="18">
         <v>-15.92</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="26">
         <v>-14.66</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="23">
         <v>-9.78</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="20">
         <v>-11.59</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="14">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="15">
         <v>-15.36</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="19">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="16">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="24">
         <v>-15.92</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="21">
         <v>-29.61</v>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>601008</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 2459.29万</v>
       </c>
       <c r="E4">
@@ -8613,41 +8613,41 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="29">
         <v>8.18</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="35">
         <v>-2.55</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="37">
         <v>-0.36</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="36">
         <v>0.18</v>
       </c>
       <c r="M4" s="38">
         <v>-1.64</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="39">
         <v>-7.64</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="27">
         <v>-7.64</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="30">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="28">
         <v>11.82</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="31">
         <v>23.09</v>
       </c>
       <c r="S4" s="32">
         <v>35.45</v>
       </c>
-      <c r="T4" s="31">
-        <v>-12.18</v>
+      <c r="T4" s="33">
+        <v>-12.36</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8675,41 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="42">
         <v>11.02</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="43">
         <v>8.91</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="50">
         <v>19.8</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="51">
         <v>19.08</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="52">
         <v>19.87</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="46">
         <v>13</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="41">
         <v>12.87</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="44">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="40">
         <v>7.46</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="45">
         <v>5.61</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="47">
         <v>4.49</v>
       </c>
-      <c r="T5" s="45">
-        <v>-19.01</v>
+      <c r="T5" s="48">
+        <v>-17.95</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8737,41 +8737,41 @@
       <c r="H6">
         <v>-1.7</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="56">
         <v>11.92</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="63">
         <v>13.13</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="57">
         <v>17.96</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="58">
         <v>22.02</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="53">
         <v>16.84</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="64">
         <v>9.93</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="54">
         <v>7.43</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="65">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="59">
         <v>9.93</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="61">
         <v>12.61</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="55">
         <v>23.83</v>
       </c>
-      <c r="T6" s="65">
-        <v>-22.28</v>
+      <c r="T6" s="62">
+        <v>-24.27</v>
       </c>
     </row>
     <row r="7">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="76" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8802,38 +8802,38 @@
       <c r="I7" s="69">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="70">
         <v>-12.07</v>
       </c>
       <c r="K7" s="77">
         <v>-10.42</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="66">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="71">
         <v>-14.58</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="73">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="67">
         <v>-23.59</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="68">
         <v>-22.96</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="74">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="78">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="72">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="72">
-        <v>-23.75</v>
+      <c r="T7" s="75">
+        <v>-23.35</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>002094</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="82" t="str">
         <v>净买: 3233.09万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8861,41 @@
       <c r="H8">
         <v>-1.1</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="80">
         <v>11.25</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="83">
         <v>10.01</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="90">
         <v>21.01</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="91">
         <v>18.67</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="88">
         <v>22.13</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="79">
         <v>21.76</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8" s="84">
         <v>17.43</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="85">
         <v>16.19</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="86">
         <v>19.65</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="87">
         <v>23.73</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="81">
         <v>15.95</v>
       </c>
       <c r="T8" s="89">
-        <v>-21.88</v>
+        <v>-22.13</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>002094</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -3419.88万</v>
       </c>
       <c r="E9">
@@ -8923,41 +8923,41 @@
       <c r="H9">
         <v>2.78</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="95">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="92">
         <v>5.84</v>
       </c>
-      <c r="K9" s="102">
+      <c r="K9" s="98">
         <v>3.78</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="93">
         <v>6.81</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="101">
         <v>6.49</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="102">
         <v>2.7</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="103">
         <v>1.62</v>
       </c>
       <c r="P9" s="94">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="96">
         <v>8.22</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="104">
         <v>1.41</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="99">
         <v>0.22</v>
       </c>
-      <c r="T9" s="92">
-        <v>-31.68</v>
+      <c r="T9" s="100">
+        <v>-31.89</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="113" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,41 +8985,41 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="117">
+      <c r="I10" s="107">
         <v>11.08</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="109">
         <v>0</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="110">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="114">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="111">
         <v>-16.07</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="115">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="114">
+      <c r="O10" s="116">
         <v>-11.64</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="112">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="108">
         <v>-19.06</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="117">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="105">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="113">
-        <v>-22.42</v>
+      <c r="T10" s="106">
+        <v>-20.49</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="127" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,41 +9047,41 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="127">
         <v>9.97</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="128">
         <v>5.4</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="129">
         <v>3.74</v>
       </c>
-      <c r="L11" s="124">
+      <c r="L11" s="130">
         <v>7.89</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="120">
         <v>5.19</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="121">
         <v>1.14</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="125">
         <v>-0.31</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="118">
         <v>-6.65</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="123">
         <v>-3.32</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="122">
         <v>-8.62</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="119">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="130">
-        <v>-32.92</v>
+      <c r="T11" s="124">
+        <v>-32.29</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="139" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9109,41 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="140">
+      <c r="I12" s="142">
         <v>13</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="135">
         <v>1.73</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="136">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="143">
         <v>1.65</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="132">
         <v>2.69</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="140">
         <v>6.07</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="141">
         <v>12.39</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="133">
         <v>12.39</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="137">
         <v>11.53</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="131">
         <v>7.02</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="134">
         <v>5.55</v>
       </c>
-      <c r="T12" s="139">
-        <v>-35.7</v>
+      <c r="T12" s="138">
+        <v>-34.23</v>
       </c>
     </row>
     <row r="13">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="145" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,41 +9171,41 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="155">
+      <c r="I13" s="149">
         <v>4.11</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="146">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="151">
         <v>-2.4</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="152">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="150">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="153">
         <v>-10.96</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="154">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="155">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="147">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="156">
         <v>-17.12</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="148">
         <v>-19.86</v>
       </c>
-      <c r="T13" s="145">
-        <v>-11.99</v>
+      <c r="T13" s="144">
+        <v>-11.64</v>
       </c>
     </row>
     <row r="14">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="159" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,41 +9233,41 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="164">
+      <c r="I14" s="162">
         <v>5.15</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="163">
         <v>11.46</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="164">
         <v>22.61</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="169">
         <v>10.3</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="160">
         <v>3.47</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="166">
         <v>-0.84</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="161">
         <v>2.52</v>
       </c>
-      <c r="P14" s="160">
+      <c r="P14" s="165">
         <v>2</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="157">
         <v>0.11</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="167">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="158">
         <v>-2.73</v>
       </c>
-      <c r="T14" s="158">
-        <v>-0.53</v>
+      <c r="T14" s="168">
+        <v>1.68</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,41 +9295,41 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="180">
         <v>4.02</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="177">
         <v>14.43</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="174">
         <v>2.94</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="181">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="175">
         <v>-7.46</v>
       </c>
-      <c r="N15" s="177">
+      <c r="N15" s="178">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="182">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="170">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="171">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="172">
         <v>-9.22</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="179">
         <v>-6.58</v>
       </c>
-      <c r="T15" s="179">
-        <v>-7.16</v>
+      <c r="T15" s="176">
+        <v>-5.1</v>
       </c>
     </row>
     <row r="16">
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="193" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9360,38 +9360,38 @@
       <c r="I16" s="186">
         <v>9.22</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="194">
         <v>5.78</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="187">
         <v>6.22</v>
       </c>
       <c r="L16" s="188">
         <v>2.11</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="195">
         <v>2.67</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="184">
         <v>4.89</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="190">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="190">
+      <c r="P16" s="191">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="185">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="185">
+      <c r="R16" s="189">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="183">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="194">
-        <v>-19.78</v>
+      <c r="T16" s="192">
+        <v>-18.22</v>
       </c>
     </row>
     <row r="17">
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600192</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="203" t="str">
         <v>净买: 2508.47万</v>
       </c>
       <c r="E17">
@@ -9419,41 +9419,41 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="204">
         <v>14.66</v>
       </c>
-      <c r="J17" s="198">
+      <c r="J17" s="207">
         <v>16.25</v>
       </c>
       <c r="K17" s="199">
         <v>13.66</v>
       </c>
-      <c r="L17" s="200">
+      <c r="L17" s="205">
         <v>2.29</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="196">
         <v>0.9</v>
       </c>
-      <c r="N17" s="201">
+      <c r="N17" s="197">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="208">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="207">
+      <c r="P17" s="200">
         <v>-6.38</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="206">
         <v>-5.38</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="198">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="204">
+      <c r="S17" s="201">
         <v>-1</v>
       </c>
       <c r="T17" s="202">
-        <v>-16.65</v>
+        <v>-15.75</v>
       </c>
     </row>
     <row r="18">
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>600192</v>
       </c>
-      <c r="D18" s="213" t="str">
+      <c r="D18" s="210" t="str">
         <v>净卖: -2805.31万</v>
       </c>
       <c r="E18">
@@ -9481,41 +9481,41 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="220">
         <v>-1.44</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="211">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="221">
         <v>-13.27</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="209">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="216">
         <v>-16.74</v>
       </c>
       <c r="N18" s="217">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="212">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="209">
+      <c r="P18" s="218">
         <v>-19.78</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="213">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="214">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="219">
+      <c r="S18" s="215">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="215">
-        <v>-29.33</v>
+      <c r="T18" s="219">
+        <v>-28.57</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="226" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9549,35 +9549,35 @@
       <c r="J19" s="228">
         <v>8.88</v>
       </c>
-      <c r="K19" s="225">
+      <c r="K19" s="229">
         <v>12.24</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="230">
         <v>11.78</v>
       </c>
-      <c r="M19" s="229">
+      <c r="M19" s="222">
         <v>9.28</v>
       </c>
-      <c r="N19" s="222">
+      <c r="N19" s="223">
         <v>14.8</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="231">
         <v>11.38</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="232">
         <v>6.25</v>
       </c>
-      <c r="Q19" s="232">
+      <c r="Q19" s="224">
         <v>6.71</v>
       </c>
       <c r="R19" s="233">
         <v>7.11</v>
       </c>
-      <c r="S19" s="223">
+      <c r="S19" s="225">
         <v>7.37</v>
       </c>
-      <c r="T19" s="226">
-        <v>-19.28</v>
+      <c r="T19" s="234">
+        <v>-18.22</v>
       </c>
     </row>
     <row r="20">
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>002553</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="245" t="str">
         <v>净买: 2010.54万</v>
       </c>
       <c r="E20">
@@ -9605,41 +9605,41 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="246">
         <v>2.6</v>
       </c>
       <c r="J20" s="242">
         <v>2.16</v>
       </c>
-      <c r="K20" s="243">
+      <c r="K20" s="238">
         <v>3.16</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="243">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="247">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="236">
+      <c r="N20" s="244">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="240">
         <v>-1</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="241">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="235">
         <v>-0.64</v>
       </c>
-      <c r="R20" s="245">
+      <c r="R20" s="236">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="237">
         <v>-3.04</v>
       </c>
       <c r="T20" s="239">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="21">
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>000657</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="255" t="str">
         <v>净卖: -1.62亿</v>
       </c>
       <c r="E21">
@@ -9667,41 +9667,41 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="252">
+      <c r="I21" s="256">
         <v>7.81</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="249">
         <v>15.57</v>
       </c>
-      <c r="K21" s="257">
+      <c r="K21" s="251">
         <v>9.09</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="252">
         <v>15.08</v>
       </c>
-      <c r="M21" s="254">
+      <c r="M21" s="257">
         <v>3.57</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="258">
         <v>-2.42</v>
       </c>
-      <c r="O21" s="249">
+      <c r="O21" s="250">
         <v>-4.06</v>
       </c>
-      <c r="P21" s="255">
+      <c r="P21" s="259">
         <v>-4.54</v>
       </c>
       <c r="Q21" s="260">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="253">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="248">
         <v>-2</v>
       </c>
-      <c r="T21" s="256">
-        <v>239.92</v>
+      <c r="T21" s="254">
+        <v>254.57</v>
       </c>
     </row>
     <row r="22">
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>000657</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="261" t="str">
         <v>净买: 6098.44万</v>
       </c>
       <c r="E22">
@@ -9729,41 +9729,41 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="270">
+      <c r="I22" s="262">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="265">
+      <c r="J22" s="263">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="268">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="272">
+      <c r="L22" s="264">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="265">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="273">
+      <c r="N22" s="269">
         <v>-13.43</v>
       </c>
-      <c r="O22" s="266">
+      <c r="O22" s="270">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="266">
         <v>-11.6</v>
       </c>
-      <c r="Q22" s="263">
+      <c r="Q22" s="267">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="271">
         <v>-10.9</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="272">
         <v>-8.81</v>
       </c>
-      <c r="T22" s="268">
-        <v>201.4</v>
+      <c r="T22" s="273">
+        <v>214.39</v>
       </c>
     </row>
     <row r="23">
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>600010</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="284" t="str">
         <v>净卖: -1.03亿</v>
       </c>
       <c r="E23">
@@ -9791,41 +9791,41 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="281">
         <v>6.18</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="285">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="276">
         <v>-8</v>
       </c>
-      <c r="L23" s="284">
+      <c r="L23" s="277">
         <v>-8.73</v>
       </c>
       <c r="M23" s="279">
         <v>-5.82</v>
       </c>
-      <c r="N23" s="282">
+      <c r="N23" s="278">
         <v>-8</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="286">
         <v>-4.73</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="280">
         <v>-6.18</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="282">
         <v>-6.55</v>
       </c>
-      <c r="R23" s="283">
+      <c r="R23" s="274">
         <v>-8.73</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="283">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="277">
-        <v>4</v>
+      <c r="T23" s="275">
+        <v>4.73</v>
       </c>
     </row>
     <row r="24">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="298" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,41 +9853,41 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="290">
         <v>14.91</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="291">
         <v>25.62</v>
       </c>
-      <c r="K24" s="287">
+      <c r="K24" s="292">
         <v>15.37</v>
       </c>
-      <c r="L24" s="288">
+      <c r="L24" s="299">
         <v>11.34</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="287">
         <v>3.42</v>
       </c>
-      <c r="N24" s="296">
+      <c r="N24" s="288">
         <v>5.9</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="293">
         <v>12.42</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="295">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="294">
+      <c r="Q24" s="296">
         <v>7.92</v>
       </c>
-      <c r="R24" s="298">
+      <c r="R24" s="294">
         <v>5.59</v>
       </c>
-      <c r="S24" s="290">
+      <c r="S24" s="297">
         <v>11.02</v>
       </c>
-      <c r="T24" s="295">
-        <v>17.08</v>
+      <c r="T24" s="289">
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="306" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9918,38 +9918,38 @@
       <c r="I25" s="309">
         <v>6.59</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="307">
         <v>-2.11</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="310">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="303">
+      <c r="L25" s="311">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="304">
+      <c r="M25" s="312">
         <v>-10.14</v>
       </c>
-      <c r="N25" s="310">
+      <c r="N25" s="303">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="311">
+      <c r="O25" s="304">
         <v>-8.17</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="308">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="306">
+      <c r="Q25" s="300">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="312">
+      <c r="R25" s="301">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="300">
+      <c r="S25" s="302">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="307">
-        <v>-0.66</v>
+      <c r="T25" s="305">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="26">
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>600117</v>
       </c>
-      <c r="D26" s="322" t="str">
+      <c r="D26" s="323" t="str">
         <v>净卖: -2617.46万</v>
       </c>
       <c r="E26">
@@ -9977,41 +9977,41 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="323">
+      <c r="I26" s="324">
         <v>-4.81</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="325">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="313">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="325">
+      <c r="L26" s="316">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="317">
         <v>-21.44</v>
       </c>
       <c r="N26" s="318">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="316">
+      <c r="O26" s="320">
         <v>-24.05</v>
       </c>
-      <c r="P26" s="317">
+      <c r="P26" s="321">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="319">
         <v>-27.45</v>
       </c>
-      <c r="R26" s="319">
+      <c r="R26" s="314">
         <v>-27.25</v>
       </c>
-      <c r="S26" s="320">
+      <c r="S26" s="315">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="321">
-        <v>-48.5</v>
+      <c r="T26" s="322">
+        <v>-47.7</v>
       </c>
     </row>
     <row r="27">
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="335" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10039,40 +10039,40 @@
       <c r="H27">
         <v>-2.19</v>
       </c>
-      <c r="I27" s="337">
+      <c r="I27" s="336">
         <v>7.83</v>
       </c>
-      <c r="J27" s="331">
+      <c r="J27" s="334">
         <v>3.08</v>
       </c>
-      <c r="K27" s="338">
+      <c r="K27" s="328">
         <v>1.68</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="329">
         <v>0.28</v>
       </c>
-      <c r="M27" s="328">
+      <c r="M27" s="330">
         <v>0.98</v>
       </c>
-      <c r="N27" s="332">
+      <c r="N27" s="337">
         <v>-1.26</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="331">
         <v>-0.84</v>
       </c>
-      <c r="P27" s="333">
+      <c r="P27" s="338">
         <v>0.14</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="332">
         <v>4.06</v>
       </c>
-      <c r="R27" s="334">
+      <c r="R27" s="333">
         <v>4.76</v>
       </c>
-      <c r="S27" s="335">
+      <c r="S27" s="326">
         <v>2.66</v>
       </c>
-      <c r="T27" s="336">
+      <c r="T27" s="327">
         <v>-29.51</v>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="344" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10104,38 +10104,38 @@
       <c r="I28" s="339">
         <v>11.11</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="345">
         <v>22.22</v>
       </c>
       <c r="K28" s="340">
         <v>9.95</v>
       </c>
-      <c r="L28" s="349">
+      <c r="L28" s="346">
         <v>1.85</v>
       </c>
-      <c r="M28" s="345">
+      <c r="M28" s="341">
         <v>-5.32</v>
       </c>
-      <c r="N28" s="346">
+      <c r="N28" s="342">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="341">
+      <c r="O28" s="349">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="342">
+      <c r="P28" s="347">
         <v>-7.87</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="348">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="347">
+      <c r="R28" s="350">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="350">
+      <c r="S28" s="343">
         <v>-10.19</v>
       </c>
-      <c r="T28" s="344">
-        <v>-31.94</v>
+      <c r="T28" s="351">
+        <v>-31.02</v>
       </c>
     </row>
     <row r="29">
@@ -10163,41 +10163,41 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="364">
         <v>15.53</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="357">
         <v>19.33</v>
       </c>
-      <c r="K29" s="361">
+      <c r="K29" s="360">
         <v>21.27</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="352">
         <v>28.8</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="358">
         <v>33.4</v>
       </c>
-      <c r="N29" s="360">
+      <c r="N29" s="354">
         <v>28.73</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="361">
         <v>25.33</v>
       </c>
-      <c r="P29" s="363">
+      <c r="P29" s="353">
         <v>17.33</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="359">
         <v>13.93</v>
       </c>
-      <c r="R29" s="352">
+      <c r="R29" s="362">
         <v>11.4</v>
       </c>
-      <c r="S29" s="354">
+      <c r="S29" s="355">
         <v>13</v>
       </c>
-      <c r="T29" s="355">
-        <v>-33.13</v>
+      <c r="T29" s="363">
+        <v>-33</v>
       </c>
     </row>
     <row r="30">
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>601718</v>
       </c>
-      <c r="D30" s="365" t="str">
+      <c r="D30" s="366" t="str">
         <v>净卖: -4886.83万</v>
       </c>
       <c r="E30">
@@ -10225,41 +10225,41 @@
       <c r="H30">
         <v>4.17</v>
       </c>
-      <c r="I30" s="366">
+      <c r="I30" s="373">
         <v>5.6</v>
       </c>
-      <c r="J30" s="375">
+      <c r="J30" s="371">
         <v>-5</v>
       </c>
-      <c r="K30" s="369">
+      <c r="K30" s="374">
         <v>-12</v>
       </c>
-      <c r="L30" s="373">
+      <c r="L30" s="376">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="376">
+      <c r="M30" s="367">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="370">
+      <c r="N30" s="372">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="367">
+      <c r="O30" s="377">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="368">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="365">
         <v>-22</v>
       </c>
-      <c r="R30" s="374">
+      <c r="R30" s="369">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="368">
+      <c r="S30" s="370">
         <v>-20.2</v>
       </c>
-      <c r="T30" s="372">
-        <v>-41.2</v>
+      <c r="T30" s="375">
+        <v>-40.4</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="382" t="str">
+      <c r="D31" s="390" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,10 +10287,10 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="379">
+      <c r="I31" s="384">
         <v>2.72</v>
       </c>
-      <c r="J31" s="390">
+      <c r="J31" s="385">
         <v>1.18</v>
       </c>
       <c r="K31" s="378">
@@ -10299,29 +10299,29 @@
       <c r="L31" s="380">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="386">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="383">
+      <c r="N31" s="381">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="384">
+      <c r="O31" s="382">
         <v>-10.28</v>
       </c>
-      <c r="P31" s="389">
+      <c r="P31" s="388">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="387">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="385">
+      <c r="R31" s="379">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="386">
+      <c r="S31" s="389">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="387">
-        <v>44.63</v>
+      <c r="T31" s="383">
+        <v>52.64</v>
       </c>
     </row>
     <row r="32">
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600078</v>
       </c>
-      <c r="D32" s="394" t="str">
+      <c r="D32" s="395" t="str">
         <v>净买: 1268.44万</v>
       </c>
       <c r="E32">
@@ -10349,19 +10349,19 @@
       <c r="H32">
         <v>-0.92</v>
       </c>
-      <c r="I32" s="402">
+      <c r="I32" s="396">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="403">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="403">
+      <c r="K32" s="391">
         <v>-10.08</v>
       </c>
-      <c r="L32" s="391">
+      <c r="L32" s="392">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="392">
+      <c r="M32" s="397">
         <v>-0.93</v>
       </c>
       <c r="N32" s="393">
@@ -10370,20 +10370,20 @@
       <c r="O32" s="399">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="396">
+      <c r="P32" s="394">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="397">
+      <c r="Q32" s="400">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="401">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="395">
+      <c r="S32" s="398">
         <v>1.44</v>
       </c>
-      <c r="T32" s="401">
-        <v>33.85</v>
+      <c r="T32" s="402">
+        <v>28.19</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="415" t="str">
+      <c r="D33" s="406" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10411,41 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="416">
+      <c r="I33" s="412">
         <v>8.08</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="409">
         <v>6.62</v>
       </c>
-      <c r="K33" s="404">
+      <c r="K33" s="413">
         <v>6.96</v>
       </c>
-      <c r="L33" s="411">
+      <c r="L33" s="410">
         <v>7.52</v>
       </c>
-      <c r="M33" s="408">
+      <c r="M33" s="414">
         <v>5.27</v>
       </c>
-      <c r="N33" s="409">
+      <c r="N33" s="407">
         <v>3.03</v>
       </c>
-      <c r="O33" s="412">
+      <c r="O33" s="415">
         <v>10.66</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="416">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="404">
         <v>34.01</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="405">
         <v>47.36</v>
       </c>
-      <c r="S33" s="410">
+      <c r="S33" s="408">
         <v>50.39</v>
       </c>
-      <c r="T33" s="414">
-        <v>46.02</v>
+      <c r="T33" s="411">
+        <v>39.84</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="418" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10473,41 @@
       <c r="H34">
         <v>-4.48</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="427">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="424">
         <v>0</v>
       </c>
-      <c r="K34" s="418">
+      <c r="K34" s="425">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="421">
         <v>4.61</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="428">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="424">
+      <c r="N34" s="429">
         <v>-1.02</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="422">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="425">
+      <c r="P34" s="419">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="423">
         <v>-16.33</v>
       </c>
-      <c r="R34" s="427">
+      <c r="R34" s="420">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="426">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="428">
-        <v>1.64</v>
+      <c r="T34" s="417">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="430" t="str">
+      <c r="D35" s="442" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,41 +10535,41 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="431">
+      <c r="I35" s="435">
         <v>4.33</v>
       </c>
-      <c r="J35" s="437">
+      <c r="J35" s="436">
         <v>5.2</v>
       </c>
-      <c r="K35" s="435">
+      <c r="K35" s="437">
         <v>-1.91</v>
       </c>
-      <c r="L35" s="438">
+      <c r="L35" s="434">
         <v>-4.85</v>
       </c>
-      <c r="M35" s="432">
+      <c r="M35" s="430">
         <v>-6.07</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="439">
         <v>-7.11</v>
       </c>
-      <c r="O35" s="441">
+      <c r="O35" s="440">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="439">
+      <c r="P35" s="431">
         <v>-10.4</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="441">
         <v>-10.4</v>
       </c>
-      <c r="R35" s="440">
+      <c r="R35" s="438">
         <v>-8.49</v>
       </c>
-      <c r="S35" s="436">
+      <c r="S35" s="432">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="434">
-        <v>-8.15</v>
+      <c r="T35" s="433">
+        <v>-6.59</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>301348</v>
       </c>
-      <c r="D36" s="443" t="str">
+      <c r="D36" s="453" t="str">
         <v>净卖: -905.79万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10597,41 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="454">
         <v>25.33</v>
       </c>
-      <c r="J36" s="448">
+      <c r="J36" s="450">
         <v>42.26</v>
       </c>
-      <c r="K36" s="454">
+      <c r="K36" s="455">
         <v>32.49</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="451">
         <v>48.47</v>
       </c>
-      <c r="M36" s="446">
+      <c r="M36" s="443">
         <v>52.11</v>
       </c>
-      <c r="N36" s="455">
+      <c r="N36" s="444">
         <v>37.42</v>
       </c>
-      <c r="O36" s="444">
+      <c r="O36" s="452">
         <v>48.97</v>
       </c>
-      <c r="P36" s="450">
+      <c r="P36" s="445">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="451">
+      <c r="Q36" s="446">
         <v>31.29</v>
       </c>
-      <c r="R36" s="445">
+      <c r="R36" s="447">
         <v>26.08</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="448">
         <v>22.06</v>
       </c>
-      <c r="T36" s="447">
-        <v>2.36</v>
+      <c r="T36" s="449">
+        <v>2.86</v>
       </c>
     </row>
     <row r="37">
@@ -10659,41 +10659,41 @@
       <c r="H37">
         <v>5.98</v>
       </c>
-      <c r="I37" s="459">
+      <c r="I37" s="462">
         <v>7.11</v>
       </c>
-      <c r="J37" s="456">
+      <c r="J37" s="467">
         <v>-0.25</v>
       </c>
       <c r="K37" s="463">
         <v>11.78</v>
       </c>
-      <c r="L37" s="457">
+      <c r="L37" s="456">
         <v>14.52</v>
       </c>
-      <c r="M37" s="466">
+      <c r="M37" s="457">
         <v>3.46</v>
       </c>
-      <c r="N37" s="460">
+      <c r="N37" s="464">
         <v>12.15</v>
       </c>
-      <c r="O37" s="461">
+      <c r="O37" s="458">
         <v>7.42</v>
       </c>
-      <c r="P37" s="464">
+      <c r="P37" s="465">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="458">
+      <c r="Q37" s="459">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="462">
+      <c r="R37" s="466">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="465">
+      <c r="S37" s="460">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="467">
-        <v>-22.94</v>
+      <c r="T37" s="461">
+        <v>-22.56</v>
       </c>
     </row>
     <row r="38">
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>000636</v>
       </c>
-      <c r="D38" s="477" t="str">
+      <c r="D38" s="472" t="str">
         <v>净卖: -226.93万</v>
       </c>
       <c r="E38">
@@ -10721,16 +10721,16 @@
       <c r="H38">
         <v>-1.06</v>
       </c>
-      <c r="I38" s="474">
+      <c r="I38" s="475">
         <v>11.17</v>
       </c>
-      <c r="J38" s="475">
+      <c r="J38" s="476">
         <v>3.8</v>
       </c>
-      <c r="K38" s="478">
+      <c r="K38" s="474">
         <v>2.93</v>
       </c>
-      <c r="L38" s="472">
+      <c r="L38" s="477">
         <v>3.61</v>
       </c>
       <c r="M38" s="473">
@@ -10739,23 +10739,23 @@
       <c r="N38" s="481">
         <v>9.9</v>
       </c>
-      <c r="O38" s="469">
+      <c r="O38" s="478">
         <v>3.76</v>
       </c>
-      <c r="P38" s="470">
+      <c r="P38" s="469">
         <v>14.15</v>
       </c>
-      <c r="Q38" s="479">
+      <c r="Q38" s="470">
         <v>25.56</v>
       </c>
-      <c r="R38" s="471">
+      <c r="R38" s="479">
         <v>25.51</v>
       </c>
-      <c r="S38" s="476">
+      <c r="S38" s="480">
         <v>26.83</v>
       </c>
-      <c r="T38" s="480">
-        <v>7.27</v>
+      <c r="T38" s="471">
+        <v>8.15</v>
       </c>
     </row>
     <row r="39">
@@ -10817,40 +10817,40 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="493">
+      <c r="I40" s="490">
         <v>78.38</v>
       </c>
-      <c r="J40" s="485">
+      <c r="J40" s="482">
         <v>62.16</v>
       </c>
-      <c r="K40" s="489">
+      <c r="K40" s="483">
         <v>56.76</v>
       </c>
-      <c r="L40" s="486">
+      <c r="L40" s="484">
         <v>59.46</v>
       </c>
-      <c r="M40" s="490">
+      <c r="M40" s="487">
         <v>51.35</v>
       </c>
-      <c r="N40" s="491">
+      <c r="N40" s="488">
         <v>40.54</v>
       </c>
-      <c r="O40" s="483">
+      <c r="O40" s="485">
         <v>37.84</v>
       </c>
-      <c r="P40" s="487">
+      <c r="P40" s="491">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="482">
+      <c r="Q40" s="486">
         <v>40.54</v>
       </c>
       <c r="R40" s="492">
         <v>37.84</v>
       </c>
-      <c r="S40" s="484">
+      <c r="S40" s="493">
         <v>40.54</v>
       </c>
-      <c r="T40" s="488">
+      <c r="T40" s="489">
         <v>29.73</v>
       </c>
     </row>
@@ -10865,41 +10865,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="501">
+      <c r="I41" s="495">
         <v>5.97</v>
       </c>
-      <c r="J41" s="502">
+      <c r="J41" s="497">
         <v>4.69</v>
       </c>
-      <c r="K41" s="503">
+      <c r="K41" s="498">
         <v>2.99</v>
       </c>
-      <c r="L41" s="496">
+      <c r="L41" s="504">
         <v>2.46</v>
       </c>
-      <c r="M41" s="499">
+      <c r="M41" s="501">
         <v>0.83</v>
       </c>
-      <c r="N41" s="504">
+      <c r="N41" s="505">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="500">
+      <c r="O41" s="499">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="494">
+      <c r="P41" s="502">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="497">
+      <c r="Q41" s="496">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="498">
+      <c r="R41" s="500">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="505">
+      <c r="S41" s="503">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="495">
-        <v>0.28</v>
+      <c r="T41" s="494">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,12 +39,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFEF9FA"/>
         <bgColor/>
       </patternFill>
@@ -57,25 +87,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
+        <fgColor rgb="FFEFF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,13 +213,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
+        <fgColor rgb="FFF3BCC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,25 +225,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,61 +417,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FFC22937"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,7 +429,403 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,6 +837,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -237,13 +861,2197 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -255,2815 +3063,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,41 +8489,41 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="3">
         <v>9.99</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="13">
         <v>13.15</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="1">
         <v>9.95</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="9">
         <v>8.34</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="6">
         <v>9.06</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="10">
         <v>5.46</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="4">
         <v>3.94</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="11">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="5">
         <v>0.04</v>
       </c>
       <c r="R2" s="12">
         <v>1.19</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="7">
         <v>0.13</v>
       </c>
-      <c r="T2" s="3">
-        <v>-16.07</v>
+      <c r="T2" s="8">
+        <v>-17.07</v>
       </c>
     </row>
     <row r="3">
@@ -8551,41 +8551,41 @@
       <c r="H3">
         <v>-1.51</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="18">
         <v>-8.66</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="26">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="21">
         <v>-15.92</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="14">
         <v>-14.66</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="22">
         <v>-9.78</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="15">
         <v>-11.59</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="19">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="23">
         <v>-15.36</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="24">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="25">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="20">
         <v>-15.92</v>
       </c>
-      <c r="T3" s="21">
-        <v>-29.61</v>
+      <c r="T3" s="16">
+        <v>-30.73</v>
       </c>
     </row>
     <row r="4">
@@ -8613,41 +8613,41 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="32">
         <v>8.18</v>
       </c>
       <c r="J4" s="35">
         <v>-2.55</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="28">
         <v>-0.36</v>
       </c>
       <c r="L4" s="36">
         <v>0.18</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="37">
         <v>-1.64</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="38">
         <v>-7.64</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="39">
         <v>-7.64</v>
       </c>
       <c r="P4" s="30">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="31">
         <v>11.82</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="27">
         <v>23.09</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="29">
         <v>35.45</v>
       </c>
       <c r="T4" s="33">
-        <v>-12.36</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8675,41 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="46">
         <v>11.02</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="42">
         <v>8.91</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="49">
         <v>19.8</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="43">
         <v>19.08</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="50">
         <v>19.87</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="51">
         <v>13</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="47">
         <v>12.87</v>
       </c>
       <c r="P5" s="44">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="45">
         <v>7.46</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="40">
         <v>5.61</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="52">
         <v>4.49</v>
       </c>
       <c r="T5" s="48">
-        <v>-17.95</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8740,31 +8740,31 @@
       <c r="I6" s="56">
         <v>11.92</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="57">
         <v>13.13</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="58">
         <v>17.96</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="61">
         <v>22.02</v>
       </c>
       <c r="M6" s="53">
         <v>16.84</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="59">
         <v>9.93</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="64">
         <v>7.43</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="60">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="54">
         <v>9.93</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="65">
         <v>12.61</v>
       </c>
       <c r="S6" s="55">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8799,41 +8799,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="75">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="68">
         <v>-12.07</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="69">
         <v>-10.42</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="76">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="77">
         <v>-14.58</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="70">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="66">
         <v>-23.59</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="78">
         <v>-22.96</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="71">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="72">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="67">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="75">
-        <v>-23.35</v>
+      <c r="T7" s="73">
+        <v>-24.92</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>002094</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 3233.09万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8861,41 @@
       <c r="H8">
         <v>-1.1</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="81">
         <v>11.25</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="90">
         <v>10.01</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="87">
         <v>21.01</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="82">
         <v>18.67</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="86">
         <v>22.13</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="83">
         <v>21.76</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="88">
         <v>17.43</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="91">
         <v>16.19</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="84">
         <v>19.65</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="79">
         <v>23.73</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="85">
         <v>15.95</v>
       </c>
-      <c r="T8" s="89">
-        <v>-22.13</v>
+      <c r="T8" s="80">
+        <v>-22.99</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>002094</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -3419.88万</v>
       </c>
       <c r="E9">
@@ -8923,41 +8923,41 @@
       <c r="H9">
         <v>2.78</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="102">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="98">
         <v>5.84</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="96">
         <v>3.78</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="99">
         <v>6.81</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="103">
         <v>6.49</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="104">
         <v>2.7</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="100">
         <v>1.62</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="97">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="92">
         <v>8.22</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="95">
         <v>1.41</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="93">
         <v>0.22</v>
       </c>
-      <c r="T9" s="100">
-        <v>-31.89</v>
+      <c r="T9" s="94">
+        <v>-32.65</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="111" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,41 +8985,41 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="105">
         <v>11.08</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="112">
         <v>0</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="115">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="114">
+      <c r="L10" s="106">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="113">
         <v>-16.07</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="107">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="108">
         <v>-11.64</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="110">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="108">
+      <c r="Q10" s="109">
         <v>-19.06</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="114">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="116">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="106">
-        <v>-20.49</v>
+      <c r="T10" s="117">
+        <v>-21.15</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="128" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,22 +9047,22 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="129">
         <v>9.97</v>
       </c>
-      <c r="J11" s="128">
+      <c r="J11" s="121">
         <v>5.4</v>
       </c>
-      <c r="K11" s="129">
+      <c r="K11" s="130">
         <v>3.74</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="123">
         <v>7.89</v>
       </c>
       <c r="M11" s="120">
         <v>5.19</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="124">
         <v>1.14</v>
       </c>
       <c r="O11" s="125">
@@ -9071,17 +9071,17 @@
       <c r="P11" s="118">
         <v>-6.65</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="126">
         <v>-3.32</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="127">
         <v>-8.62</v>
       </c>
       <c r="S11" s="119">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="124">
-        <v>-32.29</v>
+      <c r="T11" s="122">
+        <v>-33.23</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="141" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9109,41 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="138">
         <v>13</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="142">
         <v>1.73</v>
       </c>
-      <c r="K12" s="136">
+      <c r="K12" s="143">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="133">
         <v>1.65</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="134">
         <v>2.69</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="131">
         <v>6.07</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12" s="132">
         <v>12.39</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="135">
         <v>12.39</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="136">
         <v>11.53</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="139">
         <v>7.02</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="140">
         <v>5.55</v>
       </c>
-      <c r="T12" s="138">
-        <v>-34.23</v>
+      <c r="T12" s="137">
+        <v>-33.97</v>
       </c>
     </row>
     <row r="13">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="155" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,41 +9171,41 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="145">
         <v>4.11</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="156">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="151">
+      <c r="K13" s="146">
         <v>-2.4</v>
       </c>
-      <c r="L13" s="152">
+      <c r="L13" s="150">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="153">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="153">
+      <c r="N13" s="154">
         <v>-10.96</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="147">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="151">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="148">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="156">
+      <c r="R13" s="149">
         <v>-17.12</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="144">
         <v>-19.86</v>
       </c>
-      <c r="T13" s="144">
-        <v>-11.64</v>
+      <c r="T13" s="152">
+        <v>-13.01</v>
       </c>
     </row>
     <row r="14">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="165" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,16 +9233,16 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="163">
         <v>5.15</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="157">
         <v>11.46</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="158">
         <v>22.61</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="159">
         <v>10.3</v>
       </c>
       <c r="M14" s="160">
@@ -9254,20 +9254,20 @@
       <c r="O14" s="161">
         <v>2.52</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="162">
         <v>2</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="167">
         <v>0.11</v>
       </c>
-      <c r="R14" s="167">
+      <c r="R14" s="164">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="168">
         <v>-2.73</v>
       </c>
-      <c r="T14" s="168">
-        <v>1.68</v>
+      <c r="T14" s="169">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="181" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,41 +9295,41 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="171">
         <v>4.02</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="172">
         <v>14.43</v>
       </c>
-      <c r="K15" s="174">
+      <c r="K15" s="182">
         <v>2.94</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="177">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="173">
         <v>-7.46</v>
       </c>
       <c r="N15" s="178">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="182">
+      <c r="O15" s="179">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="170">
+      <c r="P15" s="174">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="171">
+      <c r="Q15" s="180">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="175">
         <v>-9.22</v>
       </c>
-      <c r="S15" s="179">
+      <c r="S15" s="176">
         <v>-6.58</v>
       </c>
-      <c r="T15" s="176">
-        <v>-5.1</v>
+      <c r="T15" s="170">
+        <v>-7.26</v>
       </c>
     </row>
     <row r="16">
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9357,41 +9357,41 @@
       <c r="H16">
         <v>0.67</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="194">
         <v>9.22</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="191">
         <v>5.78</v>
       </c>
       <c r="K16" s="187">
         <v>6.22</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="192">
         <v>2.11</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="188">
         <v>2.67</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="195">
         <v>4.89</v>
       </c>
-      <c r="O16" s="190">
+      <c r="O16" s="183">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="184">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="193">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="185">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="183">
+      <c r="S16" s="189">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="192">
-        <v>-18.22</v>
+      <c r="T16" s="186">
+        <v>-19.56</v>
       </c>
     </row>
     <row r="17">
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600192</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="200" t="str">
         <v>净买: 2508.47万</v>
       </c>
       <c r="E17">
@@ -9419,41 +9419,41 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="201">
         <v>14.66</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="203">
         <v>16.25</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="204">
         <v>13.66</v>
       </c>
       <c r="L17" s="205">
         <v>2.29</v>
       </c>
-      <c r="M17" s="196">
+      <c r="M17" s="198">
         <v>0.9</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="208">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="196">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="206">
         <v>-6.38</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="197">
         <v>-5.38</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="199">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="202">
         <v>-1</v>
       </c>
-      <c r="T17" s="202">
-        <v>-15.75</v>
+      <c r="T17" s="207">
+        <v>-17.05</v>
       </c>
     </row>
     <row r="18">
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>600192</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="214" t="str">
         <v>净卖: -2805.31万</v>
       </c>
       <c r="E18">
@@ -9481,41 +9481,41 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="220">
+      <c r="I18" s="217">
         <v>-1.44</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="219">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="221">
+      <c r="K18" s="220">
         <v>-13.27</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="221">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="216">
+      <c r="M18" s="218">
         <v>-16.74</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="212">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="209">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="218">
+      <c r="P18" s="215">
         <v>-19.78</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="210">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="216">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="211">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="219">
-        <v>-28.57</v>
+      <c r="T18" s="213">
+        <v>-29.67</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="224" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9546,38 +9546,38 @@
       <c r="I19" s="227">
         <v>10</v>
       </c>
-      <c r="J19" s="228">
+      <c r="J19" s="231">
         <v>8.88</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="228">
         <v>12.24</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="232">
         <v>11.78</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="233">
         <v>9.28</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="234">
         <v>14.8</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="222">
         <v>11.38</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="229">
         <v>6.25</v>
       </c>
-      <c r="Q19" s="224">
+      <c r="Q19" s="225">
         <v>6.71</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="230">
         <v>7.11</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="223">
         <v>7.37</v>
       </c>
-      <c r="T19" s="234">
-        <v>-18.22</v>
+      <c r="T19" s="226">
+        <v>-20.46</v>
       </c>
     </row>
     <row r="20">
@@ -9605,41 +9605,41 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="241">
         <v>2.6</v>
       </c>
-      <c r="J20" s="242">
+      <c r="J20" s="246">
         <v>2.16</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="242">
         <v>3.16</v>
       </c>
-      <c r="L20" s="243">
+      <c r="L20" s="247">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="247">
+      <c r="M20" s="237">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="238">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="235">
         <v>-1</v>
       </c>
-      <c r="P20" s="241">
+      <c r="P20" s="239">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="244">
         <v>-0.64</v>
       </c>
       <c r="R20" s="236">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="237">
+      <c r="S20" s="240">
         <v>-3.04</v>
       </c>
-      <c r="T20" s="239">
-        <v>1.08</v>
+      <c r="T20" s="243">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>000657</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="256" t="str">
         <v>净卖: -1.62亿</v>
       </c>
       <c r="E21">
@@ -9667,41 +9667,41 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="260">
         <v>7.81</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="253">
         <v>15.57</v>
       </c>
-      <c r="K21" s="251">
+      <c r="K21" s="257">
         <v>9.09</v>
       </c>
-      <c r="L21" s="252">
+      <c r="L21" s="254">
         <v>15.08</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="248">
         <v>3.57</v>
       </c>
-      <c r="N21" s="258">
+      <c r="N21" s="249">
         <v>-2.42</v>
       </c>
       <c r="O21" s="250">
         <v>-4.06</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="251">
         <v>-4.54</v>
       </c>
-      <c r="Q21" s="260">
+      <c r="Q21" s="258">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="252">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="259">
         <v>-2</v>
       </c>
-      <c r="T21" s="254">
-        <v>254.57</v>
+      <c r="T21" s="255">
+        <v>250.15</v>
       </c>
     </row>
     <row r="22">
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>000657</v>
       </c>
-      <c r="D22" s="261" t="str">
+      <c r="D22" s="262" t="str">
         <v>净买: 6098.44万</v>
       </c>
       <c r="E22">
@@ -9729,41 +9729,41 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="265">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="266">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="263">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="267">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="268">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="270">
         <v>-13.43</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="271">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="266">
+      <c r="P22" s="269">
         <v>-11.6</v>
       </c>
-      <c r="Q22" s="267">
+      <c r="Q22" s="272">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="271">
+      <c r="R22" s="264">
         <v>-10.9</v>
       </c>
-      <c r="S22" s="272">
+      <c r="S22" s="273">
         <v>-8.81</v>
       </c>
-      <c r="T22" s="273">
-        <v>214.39</v>
+      <c r="T22" s="261">
+        <v>210.47</v>
       </c>
     </row>
     <row r="23">
@@ -9791,41 +9791,41 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="275">
         <v>6.18</v>
       </c>
       <c r="J23" s="285">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="278">
         <v>-8</v>
       </c>
-      <c r="L23" s="277">
+      <c r="L23" s="286">
         <v>-8.73</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="282">
         <v>-5.82</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="279">
         <v>-8</v>
       </c>
-      <c r="O23" s="286">
+      <c r="O23" s="276">
         <v>-4.73</v>
       </c>
       <c r="P23" s="280">
         <v>-6.18</v>
       </c>
-      <c r="Q23" s="282">
+      <c r="Q23" s="274">
         <v>-6.55</v>
       </c>
-      <c r="R23" s="274">
+      <c r="R23" s="281">
         <v>-8.73</v>
       </c>
-      <c r="S23" s="283">
+      <c r="S23" s="277">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="275">
-        <v>4.73</v>
+      <c r="T23" s="283">
+        <v>4.36</v>
       </c>
     </row>
     <row r="24">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="291" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,41 +9853,41 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="292">
         <v>14.91</v>
       </c>
-      <c r="J24" s="291">
+      <c r="J24" s="295">
         <v>25.62</v>
       </c>
-      <c r="K24" s="292">
+      <c r="K24" s="296">
         <v>15.37</v>
       </c>
-      <c r="L24" s="299">
+      <c r="L24" s="297">
         <v>11.34</v>
       </c>
-      <c r="M24" s="287">
+      <c r="M24" s="288">
         <v>3.42</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="298">
         <v>5.9</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="299">
         <v>12.42</v>
       </c>
-      <c r="P24" s="295">
+      <c r="P24" s="290">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="296">
+      <c r="Q24" s="289">
         <v>7.92</v>
       </c>
-      <c r="R24" s="294">
+      <c r="R24" s="287">
         <v>5.59</v>
       </c>
-      <c r="S24" s="297">
+      <c r="S24" s="293">
         <v>11.02</v>
       </c>
-      <c r="T24" s="289">
-        <v>14.6</v>
+      <c r="T24" s="294">
+        <v>11.65</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="305" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9915,41 +9915,41 @@
       <c r="H25">
         <v>2.57</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="306">
         <v>6.59</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="303">
         <v>-2.11</v>
       </c>
       <c r="K25" s="310">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="304">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="311">
         <v>-10.14</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="307">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="308">
         <v>-8.17</v>
       </c>
-      <c r="P25" s="308">
+      <c r="P25" s="300">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="300">
+      <c r="Q25" s="301">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="301">
+      <c r="R25" s="302">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="302">
+      <c r="S25" s="312">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="305">
-        <v>-2.77</v>
+      <c r="T25" s="309">
+        <v>-5.27</v>
       </c>
     </row>
     <row r="26">
@@ -9977,41 +9977,41 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="324">
+      <c r="I26" s="318">
         <v>-4.81</v>
       </c>
-      <c r="J26" s="325">
+      <c r="J26" s="319">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="324">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="316">
+      <c r="L26" s="321">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="314">
         <v>-21.44</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="315">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="320">
+      <c r="O26" s="325">
         <v>-24.05</v>
       </c>
-      <c r="P26" s="321">
+      <c r="P26" s="316">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="313">
         <v>-27.45</v>
       </c>
-      <c r="R26" s="314">
+      <c r="R26" s="317">
         <v>-27.25</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="322">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="322">
-        <v>-47.7</v>
+      <c r="T26" s="320">
+        <v>-46.89</v>
       </c>
     </row>
     <row r="27">
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="334" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10039,41 +10039,41 @@
       <c r="H27">
         <v>-2.19</v>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="327">
         <v>7.83</v>
       </c>
-      <c r="J27" s="334">
+      <c r="J27" s="331">
         <v>3.08</v>
       </c>
-      <c r="K27" s="328">
+      <c r="K27" s="332">
         <v>1.68</v>
       </c>
-      <c r="L27" s="329">
+      <c r="L27" s="333">
         <v>0.28</v>
       </c>
-      <c r="M27" s="330">
+      <c r="M27" s="328">
         <v>0.98</v>
       </c>
-      <c r="N27" s="337">
+      <c r="N27" s="329">
         <v>-1.26</v>
       </c>
-      <c r="O27" s="331">
+      <c r="O27" s="335">
         <v>-0.84</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="330">
         <v>0.14</v>
       </c>
-      <c r="Q27" s="332">
+      <c r="Q27" s="336">
         <v>4.06</v>
       </c>
-      <c r="R27" s="333">
+      <c r="R27" s="326">
         <v>4.76</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="337">
         <v>2.66</v>
       </c>
-      <c r="T27" s="327">
-        <v>-29.51</v>
+      <c r="T27" s="338">
+        <v>-30.63</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="350" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10101,16 +10101,16 @@
       <c r="H28">
         <v>-0.92</v>
       </c>
-      <c r="I28" s="339">
+      <c r="I28" s="351">
         <v>11.11</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="346">
         <v>22.22</v>
       </c>
       <c r="K28" s="340">
         <v>9.95</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="347">
         <v>1.85</v>
       </c>
       <c r="M28" s="341">
@@ -10119,23 +10119,23 @@
       <c r="N28" s="342">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="343">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="347">
+      <c r="P28" s="348">
         <v>-7.87</v>
       </c>
-      <c r="Q28" s="348">
+      <c r="Q28" s="349">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="350">
+      <c r="R28" s="344">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="339">
         <v>-10.19</v>
       </c>
-      <c r="T28" s="351">
-        <v>-31.02</v>
+      <c r="T28" s="345">
+        <v>-31.25</v>
       </c>
     </row>
     <row r="29">
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>002097</v>
       </c>
-      <c r="D29" s="356" t="str">
+      <c r="D29" s="355" t="str">
         <v>净买: 6007.44万</v>
       </c>
       <c r="E29">
@@ -10163,41 +10163,41 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="364">
+      <c r="I29" s="360">
         <v>15.53</v>
       </c>
       <c r="J29" s="357">
         <v>19.33</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="358">
         <v>21.27</v>
       </c>
-      <c r="L29" s="352">
+      <c r="L29" s="364">
         <v>28.8</v>
       </c>
-      <c r="M29" s="358">
+      <c r="M29" s="361">
         <v>33.4</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="362">
         <v>28.73</v>
       </c>
-      <c r="O29" s="361">
+      <c r="O29" s="356">
         <v>25.33</v>
       </c>
-      <c r="P29" s="353">
+      <c r="P29" s="352">
         <v>17.33</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="353">
         <v>13.93</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="363">
         <v>11.4</v>
       </c>
-      <c r="S29" s="355">
+      <c r="S29" s="359">
         <v>13</v>
       </c>
-      <c r="T29" s="363">
-        <v>-33</v>
+      <c r="T29" s="354">
+        <v>-33.27</v>
       </c>
     </row>
     <row r="30">
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>601718</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="368" t="str">
         <v>净卖: -4886.83万</v>
       </c>
       <c r="E30">
@@ -10225,41 +10225,41 @@
       <c r="H30">
         <v>4.17</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="369">
         <v>5.6</v>
       </c>
-      <c r="J30" s="371">
+      <c r="J30" s="372">
         <v>-5</v>
       </c>
-      <c r="K30" s="374">
+      <c r="K30" s="370">
         <v>-12</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="375">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="376">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="372">
+      <c r="N30" s="365">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="377">
+      <c r="O30" s="373">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="368">
+      <c r="P30" s="371">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="365">
+      <c r="Q30" s="366">
         <v>-22</v>
       </c>
-      <c r="R30" s="369">
+      <c r="R30" s="374">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="370">
+      <c r="S30" s="367">
         <v>-20.2</v>
       </c>
-      <c r="T30" s="375">
-        <v>-40.4</v>
+      <c r="T30" s="377">
+        <v>-40.6</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="390" t="str">
+      <c r="D31" s="380" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,41 +10287,41 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="384">
+      <c r="I31" s="385">
         <v>2.72</v>
       </c>
-      <c r="J31" s="385">
+      <c r="J31" s="378">
         <v>1.18</v>
       </c>
-      <c r="K31" s="378">
+      <c r="K31" s="379">
         <v>-3.82</v>
       </c>
-      <c r="L31" s="380">
+      <c r="L31" s="381">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="386">
+      <c r="M31" s="388">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="381">
+      <c r="N31" s="389">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="382">
+      <c r="O31" s="390">
         <v>-10.28</v>
       </c>
-      <c r="P31" s="388">
+      <c r="P31" s="386">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="382">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="379">
+      <c r="R31" s="383">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="389">
+      <c r="S31" s="387">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="383">
-        <v>52.64</v>
+      <c r="T31" s="384">
+        <v>54.51</v>
       </c>
     </row>
     <row r="32">
@@ -10349,41 +10349,41 @@
       <c r="H32">
         <v>-0.92</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="402">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="396">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="392">
         <v>-10.08</v>
       </c>
-      <c r="L32" s="392">
+      <c r="L32" s="397">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="397">
+      <c r="M32" s="403">
         <v>-0.93</v>
       </c>
-      <c r="N32" s="393">
+      <c r="N32" s="401">
         <v>-2.26</v>
       </c>
-      <c r="O32" s="399">
+      <c r="O32" s="398">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="394">
+      <c r="P32" s="393">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="400">
+      <c r="Q32" s="391">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="399">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="398">
+      <c r="S32" s="400">
         <v>1.44</v>
       </c>
-      <c r="T32" s="402">
-        <v>28.19</v>
+      <c r="T32" s="394">
+        <v>26.34</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="406" t="str">
+      <c r="D33" s="405" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10411,41 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="412">
+      <c r="I33" s="406">
         <v>8.08</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="407">
         <v>6.62</v>
       </c>
-      <c r="K33" s="413">
+      <c r="K33" s="408">
         <v>6.96</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="412">
         <v>7.52</v>
       </c>
-      <c r="M33" s="414">
+      <c r="M33" s="409">
         <v>5.27</v>
       </c>
-      <c r="N33" s="407">
+      <c r="N33" s="410">
         <v>3.03</v>
       </c>
-      <c r="O33" s="415">
+      <c r="O33" s="411">
         <v>10.66</v>
       </c>
-      <c r="P33" s="416">
+      <c r="P33" s="413">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="414">
         <v>34.01</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="415">
         <v>47.36</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="416">
         <v>50.39</v>
       </c>
-      <c r="T33" s="411">
-        <v>39.84</v>
+      <c r="T33" s="404">
+        <v>37.82</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="418" t="str">
+      <c r="D34" s="427" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10473,41 @@
       <c r="H34">
         <v>-4.48</v>
       </c>
-      <c r="I34" s="427">
+      <c r="I34" s="417">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="424">
+      <c r="J34" s="421">
         <v>0</v>
       </c>
-      <c r="K34" s="425">
+      <c r="K34" s="428">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="421">
+      <c r="L34" s="418">
         <v>4.61</v>
       </c>
-      <c r="M34" s="428">
+      <c r="M34" s="429">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="429">
+      <c r="N34" s="425">
         <v>-1.02</v>
       </c>
-      <c r="O34" s="422">
+      <c r="O34" s="419">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="419">
+      <c r="P34" s="422">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="423">
+      <c r="Q34" s="426">
         <v>-16.33</v>
       </c>
       <c r="R34" s="420">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="426">
+      <c r="S34" s="423">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="417">
-        <v>-2.66</v>
+      <c r="T34" s="424">
+        <v>-4.06</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="442" t="str">
+      <c r="D35" s="437" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,19 +10535,19 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="438">
         <v>4.33</v>
       </c>
-      <c r="J35" s="436">
+      <c r="J35" s="430">
         <v>5.2</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="431">
         <v>-1.91</v>
       </c>
-      <c r="L35" s="434">
+      <c r="L35" s="432">
         <v>-4.85</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="433">
         <v>-6.07</v>
       </c>
       <c r="N35" s="439">
@@ -10556,20 +10556,20 @@
       <c r="O35" s="440">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="441">
         <v>-10.4</v>
       </c>
-      <c r="Q35" s="441">
+      <c r="Q35" s="442">
         <v>-10.4</v>
       </c>
-      <c r="R35" s="438">
+      <c r="R35" s="434">
         <v>-8.49</v>
       </c>
-      <c r="S35" s="432">
+      <c r="S35" s="435">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="433">
-        <v>-6.59</v>
+      <c r="T35" s="436">
+        <v>-8.32</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>301348</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="446" t="str">
         <v>净卖: -905.79万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10597,41 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="454">
+      <c r="I36" s="452">
         <v>25.33</v>
       </c>
-      <c r="J36" s="450">
+      <c r="J36" s="443">
         <v>42.26</v>
       </c>
-      <c r="K36" s="455">
+      <c r="K36" s="447">
         <v>32.49</v>
       </c>
-      <c r="L36" s="451">
+      <c r="L36" s="453">
         <v>48.47</v>
       </c>
-      <c r="M36" s="443">
+      <c r="M36" s="444">
         <v>52.11</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="450">
         <v>37.42</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="445">
         <v>48.97</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="454">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="446">
+      <c r="Q36" s="448">
         <v>31.29</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="449">
         <v>26.08</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="455">
         <v>22.06</v>
       </c>
-      <c r="T36" s="449">
-        <v>2.86</v>
+      <c r="T36" s="451">
+        <v>1.78</v>
       </c>
     </row>
     <row r="37">
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>301348</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="460" t="str">
         <v>净卖: -4537.41万</v>
       </c>
       <c r="E37">
@@ -10659,41 +10659,41 @@
       <c r="H37">
         <v>5.98</v>
       </c>
-      <c r="I37" s="462">
+      <c r="I37" s="464">
         <v>7.11</v>
       </c>
-      <c r="J37" s="467">
+      <c r="J37" s="457">
         <v>-0.25</v>
       </c>
-      <c r="K37" s="463">
+      <c r="K37" s="465">
         <v>11.78</v>
       </c>
-      <c r="L37" s="456">
+      <c r="L37" s="466">
         <v>14.52</v>
       </c>
-      <c r="M37" s="457">
+      <c r="M37" s="461">
         <v>3.46</v>
       </c>
-      <c r="N37" s="464">
+      <c r="N37" s="463">
         <v>12.15</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="467">
         <v>7.42</v>
       </c>
-      <c r="P37" s="465">
+      <c r="P37" s="468">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="456">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="466">
+      <c r="R37" s="458">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="460">
+      <c r="S37" s="459">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="461">
-        <v>-22.56</v>
+      <c r="T37" s="462">
+        <v>-23.37</v>
       </c>
     </row>
     <row r="38">
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>000636</v>
       </c>
-      <c r="D38" s="472" t="str">
+      <c r="D38" s="471" t="str">
         <v>净卖: -226.93万</v>
       </c>
       <c r="E38">
@@ -10727,35 +10727,35 @@
       <c r="J38" s="476">
         <v>3.8</v>
       </c>
-      <c r="K38" s="474">
+      <c r="K38" s="481">
         <v>2.93</v>
       </c>
-      <c r="L38" s="477">
+      <c r="L38" s="469">
         <v>3.61</v>
       </c>
-      <c r="M38" s="473">
+      <c r="M38" s="477">
         <v>2.73</v>
       </c>
-      <c r="N38" s="481">
+      <c r="N38" s="472">
         <v>9.9</v>
       </c>
       <c r="O38" s="478">
         <v>3.76</v>
       </c>
-      <c r="P38" s="469">
+      <c r="P38" s="479">
         <v>14.15</v>
       </c>
-      <c r="Q38" s="470">
+      <c r="Q38" s="473">
         <v>25.56</v>
       </c>
-      <c r="R38" s="479">
+      <c r="R38" s="480">
         <v>25.51</v>
       </c>
-      <c r="S38" s="480">
+      <c r="S38" s="474">
         <v>26.83</v>
       </c>
-      <c r="T38" s="471">
-        <v>8.15</v>
+      <c r="T38" s="470">
+        <v>8.24</v>
       </c>
     </row>
     <row r="39">
@@ -10817,10 +10817,10 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="490">
+      <c r="I40" s="489">
         <v>78.38</v>
       </c>
-      <c r="J40" s="482">
+      <c r="J40" s="486">
         <v>62.16</v>
       </c>
       <c r="K40" s="483">
@@ -10829,29 +10829,29 @@
       <c r="L40" s="484">
         <v>59.46</v>
       </c>
-      <c r="M40" s="487">
+      <c r="M40" s="490">
         <v>51.35</v>
       </c>
-      <c r="N40" s="488">
+      <c r="N40" s="491">
         <v>40.54</v>
       </c>
-      <c r="O40" s="485">
+      <c r="O40" s="487">
         <v>37.84</v>
       </c>
-      <c r="P40" s="491">
+      <c r="P40" s="492">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="486">
+      <c r="Q40" s="493">
         <v>40.54</v>
       </c>
-      <c r="R40" s="492">
+      <c r="R40" s="485">
         <v>37.84</v>
       </c>
-      <c r="S40" s="493">
+      <c r="S40" s="488">
         <v>40.54</v>
       </c>
-      <c r="T40" s="489">
-        <v>29.73</v>
+      <c r="T40" s="482">
+        <v>27.03</v>
       </c>
     </row>
     <row r="41">
@@ -10865,41 +10865,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="495">
+      <c r="I41" s="505">
         <v>5.97</v>
       </c>
-      <c r="J41" s="497">
+      <c r="J41" s="494">
         <v>4.69</v>
       </c>
-      <c r="K41" s="498">
+      <c r="K41" s="495">
         <v>2.99</v>
       </c>
-      <c r="L41" s="504">
+      <c r="L41" s="496">
         <v>2.46</v>
       </c>
-      <c r="M41" s="501">
+      <c r="M41" s="499">
         <v>0.83</v>
       </c>
-      <c r="N41" s="505">
+      <c r="N41" s="500">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="499">
+      <c r="O41" s="501">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="502">
+      <c r="P41" s="497">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="496">
+      <c r="Q41" s="502">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="500">
+      <c r="R41" s="503">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="503">
+      <c r="S41" s="498">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="494">
-        <v>1.2</v>
+      <c r="T41" s="504">
+        <v>0.07</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -57,19 +63,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFEFDFD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
+        <fgColor rgb="FFF6CED2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,25 +117,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,13 +213,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,79 +357,1447 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEFF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,7 +1809,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,31 +2007,271 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,13 +2283,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,7 +2475,571 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E6CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B96C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,2761 +3051,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
+        <fgColor rgb="FFA7DBB3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,41 +8489,41 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>9.99</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="4">
         <v>13.15</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="5">
         <v>9.95</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="6">
         <v>8.34</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="7">
         <v>9.06</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="1">
         <v>5.46</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="8">
         <v>3.94</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="10">
         <v>0.04</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="11">
         <v>1.19</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="12">
         <v>0.13</v>
       </c>
-      <c r="T2" s="8">
-        <v>-17.07</v>
+      <c r="T2" s="13">
+        <v>-17.82</v>
       </c>
     </row>
     <row r="3">
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002570</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -3219.58万</v>
       </c>
       <c r="E3">
@@ -8551,41 +8551,41 @@
       <c r="H3">
         <v>-1.51</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="17">
         <v>-8.66</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="22">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="20">
         <v>-15.92</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="23">
         <v>-14.66</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="18">
         <v>-9.78</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="14">
         <v>-11.59</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="24">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="25">
         <v>-15.36</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="26">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="19">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="15">
         <v>-15.92</v>
       </c>
       <c r="T3" s="16">
-        <v>-30.73</v>
+        <v>-31.98</v>
       </c>
     </row>
     <row r="4">
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>601008</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 2459.29万</v>
       </c>
       <c r="E4">
@@ -8613,41 +8613,41 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="30">
         <v>8.18</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="37">
         <v>-2.55</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="34">
         <v>-0.36</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="38">
         <v>0.18</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="39">
         <v>-1.64</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="27">
         <v>-7.64</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="35">
         <v>-7.64</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="33">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="36">
         <v>11.82</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="28">
         <v>23.09</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="31">
         <v>35.45</v>
       </c>
-      <c r="T4" s="33">
-        <v>-12.18</v>
+      <c r="T4" s="29">
+        <v>-13.82</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="48" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8675,41 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="40">
         <v>11.02</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="41">
         <v>8.91</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="45">
         <v>19.8</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="49">
         <v>19.08</v>
       </c>
       <c r="M5" s="50">
         <v>19.87</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="47">
         <v>13</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="51">
         <v>12.87</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="42">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="46">
         <v>7.46</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="43">
         <v>5.61</v>
       </c>
       <c r="S5" s="52">
         <v>4.49</v>
       </c>
-      <c r="T5" s="48">
-        <v>-20.2</v>
+      <c r="T5" s="44">
+        <v>-22.51</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8743,35 +8743,35 @@
       <c r="J6" s="57">
         <v>13.13</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="64">
         <v>17.96</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="54">
         <v>22.02</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="58">
         <v>16.84</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="65">
         <v>9.93</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="60">
         <v>7.43</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="61">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="62">
         <v>9.93</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="63">
         <v>12.61</v>
       </c>
       <c r="S6" s="55">
         <v>23.83</v>
       </c>
-      <c r="T6" s="62">
-        <v>-24.27</v>
+      <c r="T6" s="59">
+        <v>-30.05</v>
       </c>
     </row>
     <row r="7">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8799,41 +8799,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="67">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="75">
         <v>-12.07</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="68">
         <v>-10.42</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="69">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="72">
         <v>-14.58</v>
       </c>
       <c r="N7" s="70">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="76">
         <v>-23.59</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="71">
         <v>-22.96</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="73">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="74">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="78">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="73">
-        <v>-24.92</v>
+      <c r="T7" s="77">
+        <v>-28.76</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>002094</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="90" t="str">
         <v>净买: 3233.09万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8861,41 @@
       <c r="H8">
         <v>-1.1</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="85">
         <v>11.25</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="86">
         <v>10.01</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="91">
         <v>21.01</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="87">
         <v>18.67</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="81">
         <v>22.13</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="79">
         <v>21.76</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="82">
         <v>17.43</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="88">
         <v>16.19</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="89">
         <v>19.65</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="83">
         <v>23.73</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="80">
         <v>15.95</v>
       </c>
-      <c r="T8" s="80">
-        <v>-22.99</v>
+      <c r="T8" s="84">
+        <v>-26.58</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>002094</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -3419.88万</v>
       </c>
       <c r="E9">
@@ -8923,41 +8923,41 @@
       <c r="H9">
         <v>2.78</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="96">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="93">
         <v>5.84</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="100">
         <v>3.78</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="97">
         <v>6.81</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="94">
         <v>6.49</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="95">
         <v>2.7</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="103">
         <v>1.62</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="98">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="104">
         <v>8.22</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="101">
         <v>1.41</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="102">
         <v>0.22</v>
       </c>
-      <c r="T9" s="94">
-        <v>-32.65</v>
+      <c r="T9" s="92">
+        <v>-35.78</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="108" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,41 +8985,41 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="114">
         <v>11.08</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="109">
         <v>0</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="106">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="110">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="111">
         <v>-16.07</v>
       </c>
       <c r="N10" s="107">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="112">
         <v>-11.64</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="115">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="116">
         <v>-19.06</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="117">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="113">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="117">
-        <v>-21.15</v>
+      <c r="T10" s="105">
+        <v>-25.47</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="130" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,41 +9047,41 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="129">
+      <c r="I11" s="128">
         <v>9.97</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="122">
         <v>5.4</v>
       </c>
-      <c r="K11" s="130">
+      <c r="K11" s="124">
         <v>3.74</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="125">
         <v>7.89</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="118">
         <v>5.19</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="119">
         <v>1.14</v>
       </c>
-      <c r="O11" s="125">
+      <c r="O11" s="129">
         <v>-0.31</v>
       </c>
-      <c r="P11" s="118">
+      <c r="P11" s="126">
         <v>-6.65</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="120">
         <v>-3.32</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="121">
         <v>-8.62</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="123">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="122">
-        <v>-33.23</v>
+      <c r="T11" s="127">
+        <v>-35.31</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="141" t="str">
+      <c r="D12" s="132" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9109,41 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="137">
         <v>13</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="133">
         <v>1.73</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="140">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="138">
         <v>1.65</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="142">
         <v>2.69</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="143">
         <v>6.07</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="139">
         <v>12.39</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="141">
         <v>12.39</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="131">
         <v>11.53</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="134">
         <v>7.02</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="135">
         <v>5.55</v>
       </c>
-      <c r="T12" s="137">
-        <v>-33.97</v>
+      <c r="T12" s="136">
+        <v>-35.18</v>
       </c>
     </row>
     <row r="13">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="155" t="str">
+      <c r="D13" s="150" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,41 +9171,41 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="151">
         <v>4.11</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="154">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="155">
         <v>-2.4</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="156">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="153">
+      <c r="M13" s="144">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="146">
         <v>-10.96</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="145">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="147">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="152">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="153">
         <v>-17.12</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="148">
         <v>-19.86</v>
       </c>
-      <c r="T13" s="152">
-        <v>-13.01</v>
+      <c r="T13" s="149">
+        <v>-17.12</v>
       </c>
     </row>
     <row r="14">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="158" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,41 +9233,41 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="165">
         <v>5.15</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="163">
         <v>11.46</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="166">
         <v>22.61</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="167">
         <v>10.3</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="159">
         <v>3.47</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="168">
         <v>-0.84</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="169">
         <v>2.52</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="164">
         <v>2</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="160">
         <v>0.11</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="161">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="162">
         <v>-2.73</v>
       </c>
-      <c r="T14" s="169">
-        <v>-0.63</v>
+      <c r="T14" s="157">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="179" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,41 +9295,41 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="180">
         <v>4.02</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="170">
         <v>14.43</v>
       </c>
-      <c r="K15" s="182">
+      <c r="K15" s="171">
         <v>2.94</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="175">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="178">
         <v>-7.46</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="172">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="176">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="177">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="181">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="175">
+      <c r="R15" s="173">
         <v>-9.22</v>
       </c>
-      <c r="S15" s="176">
+      <c r="S15" s="174">
         <v>-6.58</v>
       </c>
-      <c r="T15" s="170">
-        <v>-7.26</v>
+      <c r="T15" s="182">
+        <v>-7.46</v>
       </c>
     </row>
     <row r="16">
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="184" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9357,41 +9357,41 @@
       <c r="H16">
         <v>0.67</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="192">
         <v>9.22</v>
       </c>
-      <c r="J16" s="191">
+      <c r="J16" s="185">
         <v>5.78</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="188">
         <v>6.22</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="187">
         <v>2.11</v>
       </c>
-      <c r="M16" s="188">
+      <c r="M16" s="189">
         <v>2.67</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="190">
         <v>4.89</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="193">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="194">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="195">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="185">
+      <c r="R16" s="183">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="186">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="186">
-        <v>-19.56</v>
+      <c r="T16" s="191">
+        <v>-22.33</v>
       </c>
     </row>
     <row r="17">
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600192</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="199" t="str">
         <v>净买: 2508.47万</v>
       </c>
       <c r="E17">
@@ -9419,41 +9419,41 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="202">
         <v>14.66</v>
       </c>
       <c r="J17" s="203">
         <v>16.25</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="205">
         <v>13.66</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="204">
         <v>2.29</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="206">
         <v>0.9</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="196">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="200">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="201">
         <v>-6.38</v>
       </c>
       <c r="Q17" s="197">
         <v>-5.38</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="207">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="202">
+      <c r="S17" s="198">
         <v>-1</v>
       </c>
-      <c r="T17" s="207">
-        <v>-17.05</v>
+      <c r="T17" s="208">
+        <v>-18.54</v>
       </c>
     </row>
     <row r="18">
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>600192</v>
       </c>
-      <c r="D18" s="214" t="str">
+      <c r="D18" s="219" t="str">
         <v>净卖: -2805.31万</v>
       </c>
       <c r="E18">
@@ -9481,41 +9481,41 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="209">
         <v>-1.44</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="220">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="213">
         <v>-13.27</v>
       </c>
       <c r="L18" s="221">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="218">
+      <c r="M18" s="214">
         <v>-16.74</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="217">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="210">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="218">
         <v>-19.78</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="215">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="216">
+      <c r="R18" s="211">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="216">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="213">
-        <v>-29.67</v>
+      <c r="T18" s="212">
+        <v>-30.94</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="232" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9543,41 +9543,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="222">
         <v>10</v>
       </c>
-      <c r="J19" s="231">
+      <c r="J19" s="224">
         <v>8.88</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="223">
         <v>12.24</v>
       </c>
-      <c r="L19" s="232">
+      <c r="L19" s="225">
         <v>11.78</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="226">
         <v>9.28</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="228">
         <v>14.8</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="229">
         <v>11.38</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="227">
         <v>6.25</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="233">
         <v>6.71</v>
       </c>
       <c r="R19" s="230">
         <v>7.11</v>
       </c>
-      <c r="S19" s="223">
+      <c r="S19" s="231">
         <v>7.37</v>
       </c>
-      <c r="T19" s="226">
-        <v>-20.46</v>
+      <c r="T19" s="234">
+        <v>-22.76</v>
       </c>
     </row>
     <row r="20">
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>002553</v>
       </c>
-      <c r="D20" s="245" t="str">
+      <c r="D20" s="237" t="str">
         <v>净买: 2010.54万</v>
       </c>
       <c r="E20">
@@ -9605,41 +9605,41 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="238">
         <v>2.6</v>
       </c>
-      <c r="J20" s="246">
+      <c r="J20" s="243">
         <v>2.16</v>
       </c>
-      <c r="K20" s="242">
+      <c r="K20" s="247">
         <v>3.16</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="244">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="235">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="245">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="239">
         <v>-1</v>
       </c>
-      <c r="P20" s="239">
+      <c r="P20" s="236">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="240">
         <v>-0.64</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="246">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="241">
         <v>-3.04</v>
       </c>
-      <c r="T20" s="243">
-        <v>2</v>
+      <c r="T20" s="242">
+        <v>-4.36</v>
       </c>
     </row>
     <row r="21">
@@ -9667,41 +9667,41 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="260">
+      <c r="I21" s="250">
         <v>7.81</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="251">
         <v>15.57</v>
       </c>
-      <c r="K21" s="257">
+      <c r="K21" s="248">
         <v>9.09</v>
       </c>
-      <c r="L21" s="254">
+      <c r="L21" s="257">
         <v>15.08</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="258">
         <v>3.57</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="259">
         <v>-2.42</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="254">
         <v>-4.06</v>
       </c>
-      <c r="P21" s="251">
+      <c r="P21" s="255">
         <v>-4.54</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="252">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="260">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="253">
         <v>-2</v>
       </c>
-      <c r="T21" s="255">
-        <v>250.15</v>
+      <c r="T21" s="249">
+        <v>234.22</v>
       </c>
     </row>
     <row r="22">
@@ -9729,41 +9729,41 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="265">
+      <c r="I22" s="268">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="266">
+      <c r="J22" s="263">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="272">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="267">
+      <c r="L22" s="269">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="268">
+      <c r="M22" s="264">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="270">
+      <c r="N22" s="273">
         <v>-13.43</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="270">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="269">
+      <c r="P22" s="271">
         <v>-11.6</v>
       </c>
-      <c r="Q22" s="272">
+      <c r="Q22" s="265">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="266">
         <v>-10.9</v>
       </c>
-      <c r="S22" s="273">
+      <c r="S22" s="267">
         <v>-8.81</v>
       </c>
       <c r="T22" s="261">
-        <v>210.47</v>
+        <v>196.35</v>
       </c>
     </row>
     <row r="23">
@@ -9791,41 +9791,41 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="275">
+      <c r="I23" s="285">
         <v>6.18</v>
       </c>
-      <c r="J23" s="285">
+      <c r="J23" s="286">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="278">
+      <c r="K23" s="276">
         <v>-8</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="280">
         <v>-8.73</v>
       </c>
-      <c r="M23" s="282">
+      <c r="M23" s="274">
         <v>-5.82</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="277">
         <v>-8</v>
       </c>
-      <c r="O23" s="276">
+      <c r="O23" s="281">
         <v>-4.73</v>
       </c>
-      <c r="P23" s="280">
+      <c r="P23" s="275">
         <v>-6.18</v>
       </c>
-      <c r="Q23" s="274">
+      <c r="Q23" s="282">
         <v>-6.55</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="278">
         <v>-8.73</v>
       </c>
-      <c r="S23" s="277">
+      <c r="S23" s="283">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="283">
-        <v>4.36</v>
+      <c r="T23" s="279">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="24">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="291" t="str">
+      <c r="D24" s="289" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,41 +9853,41 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="297">
         <v>14.91</v>
       </c>
       <c r="J24" s="295">
         <v>25.62</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="290">
         <v>15.37</v>
       </c>
-      <c r="L24" s="297">
+      <c r="L24" s="298">
         <v>11.34</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="287">
         <v>3.42</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="291">
         <v>5.9</v>
       </c>
       <c r="O24" s="299">
         <v>12.42</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="292">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="288">
         <v>7.92</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="293">
         <v>5.59</v>
       </c>
-      <c r="S24" s="293">
+      <c r="S24" s="296">
         <v>11.02</v>
       </c>
       <c r="T24" s="294">
-        <v>11.65</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="307" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9915,41 +9915,41 @@
       <c r="H25">
         <v>2.57</v>
       </c>
-      <c r="I25" s="306">
+      <c r="I25" s="308">
         <v>6.59</v>
       </c>
-      <c r="J25" s="303">
+      <c r="J25" s="302">
         <v>-2.11</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="311">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="304">
+      <c r="L25" s="303">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="311">
+      <c r="M25" s="309">
         <v>-10.14</v>
       </c>
-      <c r="N25" s="307">
+      <c r="N25" s="310">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="304">
         <v>-8.17</v>
       </c>
       <c r="P25" s="300">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="301">
+      <c r="Q25" s="312">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="302">
+      <c r="R25" s="305">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="306">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="309">
-        <v>-5.27</v>
+      <c r="T25" s="301">
+        <v>-8.3</v>
       </c>
     </row>
     <row r="26">
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>600117</v>
       </c>
-      <c r="D26" s="323" t="str">
+      <c r="D26" s="318" t="str">
         <v>净卖: -2617.46万</v>
       </c>
       <c r="E26">
@@ -9977,41 +9977,41 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="318">
+      <c r="I26" s="323">
         <v>-4.81</v>
       </c>
-      <c r="J26" s="319">
+      <c r="J26" s="324">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="325">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="321">
+      <c r="L26" s="319">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="314">
+      <c r="M26" s="313">
         <v>-21.44</v>
       </c>
-      <c r="N26" s="315">
+      <c r="N26" s="320">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="325">
+      <c r="O26" s="315">
         <v>-24.05</v>
       </c>
       <c r="P26" s="316">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="317">
         <v>-27.45</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="314">
         <v>-27.25</v>
       </c>
       <c r="S26" s="322">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="320">
-        <v>-46.89</v>
+      <c r="T26" s="321">
+        <v>-47.9</v>
       </c>
     </row>
     <row r="27">
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="328" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10039,41 +10039,41 @@
       <c r="H27">
         <v>-2.19</v>
       </c>
-      <c r="I27" s="327">
+      <c r="I27" s="329">
         <v>7.83</v>
       </c>
-      <c r="J27" s="331">
+      <c r="J27" s="337">
         <v>3.08</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="330">
         <v>1.68</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="331">
         <v>0.28</v>
       </c>
-      <c r="M27" s="328">
+      <c r="M27" s="332">
         <v>0.98</v>
       </c>
-      <c r="N27" s="329">
+      <c r="N27" s="335">
         <v>-1.26</v>
       </c>
-      <c r="O27" s="335">
+      <c r="O27" s="338">
         <v>-0.84</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="326">
         <v>0.14</v>
       </c>
       <c r="Q27" s="336">
         <v>4.06</v>
       </c>
-      <c r="R27" s="326">
+      <c r="R27" s="334">
         <v>4.76</v>
       </c>
-      <c r="S27" s="337">
+      <c r="S27" s="333">
         <v>2.66</v>
       </c>
-      <c r="T27" s="338">
-        <v>-30.63</v>
+      <c r="T27" s="327">
+        <v>-31.89</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="350" t="str">
+      <c r="D28" s="346" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10101,16 +10101,16 @@
       <c r="H28">
         <v>-0.92</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="339">
         <v>11.11</v>
       </c>
-      <c r="J28" s="346">
+      <c r="J28" s="347">
         <v>22.22</v>
       </c>
-      <c r="K28" s="340">
+      <c r="K28" s="348">
         <v>9.95</v>
       </c>
-      <c r="L28" s="347">
+      <c r="L28" s="340">
         <v>1.85</v>
       </c>
       <c r="M28" s="341">
@@ -10119,23 +10119,23 @@
       <c r="N28" s="342">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="343">
+      <c r="O28" s="349">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="348">
+      <c r="P28" s="343">
         <v>-7.87</v>
       </c>
-      <c r="Q28" s="349">
+      <c r="Q28" s="350">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="351">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="339">
+      <c r="S28" s="344">
         <v>-10.19</v>
       </c>
       <c r="T28" s="345">
-        <v>-31.25</v>
+        <v>-34.03</v>
       </c>
     </row>
     <row r="29">
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>002097</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="364" t="str">
         <v>净买: 6007.44万</v>
       </c>
       <c r="E29">
@@ -10163,41 +10163,41 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="355">
         <v>15.53</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="362">
         <v>19.33</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="363">
         <v>21.27</v>
       </c>
-      <c r="L29" s="364">
+      <c r="L29" s="356">
         <v>28.8</v>
       </c>
-      <c r="M29" s="361">
+      <c r="M29" s="357">
         <v>33.4</v>
       </c>
-      <c r="N29" s="362">
+      <c r="N29" s="352">
         <v>28.73</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="358">
         <v>25.33</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="359">
         <v>17.33</v>
       </c>
       <c r="Q29" s="353">
         <v>13.93</v>
       </c>
-      <c r="R29" s="363">
+      <c r="R29" s="354">
         <v>11.4</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="360">
         <v>13</v>
       </c>
-      <c r="T29" s="354">
-        <v>-33.27</v>
+      <c r="T29" s="361">
+        <v>-34.33</v>
       </c>
     </row>
     <row r="30">
@@ -10225,41 +10225,41 @@
       <c r="H30">
         <v>4.17</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="374">
         <v>5.6</v>
       </c>
-      <c r="J30" s="372">
+      <c r="J30" s="369">
         <v>-5</v>
       </c>
       <c r="K30" s="370">
         <v>-12</v>
       </c>
-      <c r="L30" s="375">
+      <c r="L30" s="373">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="376">
+      <c r="M30" s="365">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="365">
+      <c r="N30" s="366">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="371">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="372">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="375">
         <v>-22</v>
       </c>
-      <c r="R30" s="374">
+      <c r="R30" s="376">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="377">
         <v>-20.2</v>
       </c>
-      <c r="T30" s="377">
-        <v>-40.6</v>
+      <c r="T30" s="367">
+        <v>-43</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="380" t="str">
+      <c r="D31" s="379" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,41 +10287,41 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="385">
+      <c r="I31" s="380">
         <v>2.72</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="389">
         <v>1.18</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="390">
         <v>-3.82</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="383">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="381">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="389">
+      <c r="N31" s="384">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="390">
+      <c r="O31" s="385">
         <v>-10.28</v>
       </c>
       <c r="P31" s="386">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="378">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="387">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="388">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="384">
-        <v>54.51</v>
+      <c r="T31" s="382">
+        <v>54.23</v>
       </c>
     </row>
     <row r="32">
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600078</v>
       </c>
-      <c r="D32" s="395" t="str">
+      <c r="D32" s="394" t="str">
         <v>净买: 1268.44万</v>
       </c>
       <c r="E32">
@@ -10352,38 +10352,38 @@
       <c r="I32" s="402">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="396">
+      <c r="J32" s="395">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="392">
+      <c r="K32" s="396">
         <v>-10.08</v>
       </c>
       <c r="L32" s="397">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="403">
+      <c r="M32" s="399">
         <v>-0.93</v>
       </c>
-      <c r="N32" s="401">
+      <c r="N32" s="398">
         <v>-2.26</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="403">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="391">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="392">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="399">
+      <c r="R32" s="400">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="401">
         <v>1.44</v>
       </c>
-      <c r="T32" s="394">
-        <v>26.34</v>
+      <c r="T32" s="393">
+        <v>37.35</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="405" t="str">
+      <c r="D33" s="408" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10411,41 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="406">
+      <c r="I33" s="409">
         <v>8.08</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="416">
         <v>6.62</v>
       </c>
-      <c r="K33" s="408">
+      <c r="K33" s="404">
         <v>6.96</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="407">
         <v>7.52</v>
       </c>
-      <c r="M33" s="409">
+      <c r="M33" s="405">
         <v>5.27</v>
       </c>
       <c r="N33" s="410">
         <v>3.03</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="413">
         <v>10.66</v>
       </c>
-      <c r="P33" s="413">
+      <c r="P33" s="411">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="414">
+      <c r="Q33" s="412">
         <v>34.01</v>
       </c>
-      <c r="R33" s="415">
+      <c r="R33" s="406">
         <v>47.36</v>
       </c>
-      <c r="S33" s="416">
+      <c r="S33" s="414">
         <v>50.39</v>
       </c>
-      <c r="T33" s="404">
-        <v>37.82</v>
+      <c r="T33" s="415">
+        <v>49.83</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="425" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10473,41 @@
       <c r="H34">
         <v>-4.48</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="423">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="419">
         <v>0</v>
       </c>
-      <c r="K34" s="428">
+      <c r="K34" s="420">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="418">
+      <c r="L34" s="421">
         <v>4.61</v>
       </c>
-      <c r="M34" s="429">
+      <c r="M34" s="424">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="425">
+      <c r="N34" s="426">
         <v>-1.02</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="417">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="422">
+      <c r="P34" s="427">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="428">
         <v>-16.33</v>
       </c>
-      <c r="R34" s="420">
+      <c r="R34" s="418">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="423">
+      <c r="S34" s="429">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="424">
-        <v>-4.06</v>
+      <c r="T34" s="422">
+        <v>4.3</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="437" t="str">
+      <c r="D35" s="438" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,41 +10535,41 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="438">
+      <c r="I35" s="439">
         <v>4.33</v>
       </c>
-      <c r="J35" s="430">
+      <c r="J35" s="442">
         <v>5.2</v>
       </c>
-      <c r="K35" s="431">
+      <c r="K35" s="435">
         <v>-1.91</v>
       </c>
-      <c r="L35" s="432">
+      <c r="L35" s="433">
         <v>-4.85</v>
       </c>
-      <c r="M35" s="433">
+      <c r="M35" s="430">
         <v>-6.07</v>
       </c>
-      <c r="N35" s="439">
+      <c r="N35" s="436">
         <v>-7.11</v>
       </c>
-      <c r="O35" s="440">
+      <c r="O35" s="431">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="441">
+      <c r="P35" s="440">
         <v>-10.4</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="441">
         <v>-10.4</v>
       </c>
       <c r="R35" s="434">
         <v>-8.49</v>
       </c>
-      <c r="S35" s="435">
+      <c r="S35" s="432">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="436">
-        <v>-8.32</v>
+      <c r="T35" s="437">
+        <v>-10.23</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>301348</v>
       </c>
-      <c r="D36" s="446" t="str">
+      <c r="D36" s="449" t="str">
         <v>净卖: -905.79万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10597,41 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="452">
+      <c r="I36" s="450">
         <v>25.33</v>
       </c>
-      <c r="J36" s="443">
+      <c r="J36" s="454">
         <v>42.26</v>
       </c>
-      <c r="K36" s="447">
+      <c r="K36" s="448">
         <v>32.49</v>
       </c>
-      <c r="L36" s="453">
+      <c r="L36" s="444">
         <v>48.47</v>
       </c>
-      <c r="M36" s="444">
+      <c r="M36" s="445">
         <v>52.11</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="455">
         <v>37.42</v>
       </c>
-      <c r="O36" s="445">
+      <c r="O36" s="446">
         <v>48.97</v>
       </c>
-      <c r="P36" s="454">
+      <c r="P36" s="443">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="448">
+      <c r="Q36" s="447">
         <v>31.29</v>
       </c>
-      <c r="R36" s="449">
+      <c r="R36" s="451">
         <v>26.08</v>
       </c>
-      <c r="S36" s="455">
+      <c r="S36" s="452">
         <v>22.06</v>
       </c>
-      <c r="T36" s="451">
-        <v>1.78</v>
+      <c r="T36" s="453">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="37">
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>301348</v>
       </c>
-      <c r="D37" s="460" t="str">
+      <c r="D37" s="468" t="str">
         <v>净卖: -4537.41万</v>
       </c>
       <c r="E37">
@@ -10659,41 +10659,41 @@
       <c r="H37">
         <v>5.98</v>
       </c>
-      <c r="I37" s="464">
+      <c r="I37" s="460">
         <v>7.11</v>
       </c>
-      <c r="J37" s="457">
+      <c r="J37" s="463">
         <v>-0.25</v>
       </c>
-      <c r="K37" s="465">
+      <c r="K37" s="456">
         <v>11.78</v>
       </c>
-      <c r="L37" s="466">
+      <c r="L37" s="464">
         <v>14.52</v>
       </c>
-      <c r="M37" s="461">
+      <c r="M37" s="465">
         <v>3.46</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="457">
         <v>12.15</v>
       </c>
-      <c r="O37" s="467">
+      <c r="O37" s="458">
         <v>7.42</v>
       </c>
-      <c r="P37" s="468">
+      <c r="P37" s="462">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="456">
+      <c r="Q37" s="459">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="458">
+      <c r="R37" s="466">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="459">
+      <c r="S37" s="467">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="462">
-        <v>-23.37</v>
+      <c r="T37" s="461">
+        <v>-25.74</v>
       </c>
     </row>
     <row r="38">
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>000636</v>
       </c>
-      <c r="D38" s="471" t="str">
+      <c r="D38" s="469" t="str">
         <v>净卖: -226.93万</v>
       </c>
       <c r="E38">
@@ -10721,41 +10721,41 @@
       <c r="H38">
         <v>-1.06</v>
       </c>
-      <c r="I38" s="475">
+      <c r="I38" s="479">
         <v>11.17</v>
       </c>
-      <c r="J38" s="476">
+      <c r="J38" s="474">
         <v>3.8</v>
       </c>
-      <c r="K38" s="481">
+      <c r="K38" s="472">
         <v>2.93</v>
       </c>
-      <c r="L38" s="469">
+      <c r="L38" s="470">
         <v>3.61</v>
       </c>
-      <c r="M38" s="477">
+      <c r="M38" s="480">
         <v>2.73</v>
       </c>
-      <c r="N38" s="472">
+      <c r="N38" s="475">
         <v>9.9</v>
       </c>
-      <c r="O38" s="478">
+      <c r="O38" s="476">
         <v>3.76</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="481">
         <v>14.15</v>
       </c>
       <c r="Q38" s="473">
         <v>25.56</v>
       </c>
-      <c r="R38" s="480">
+      <c r="R38" s="471">
         <v>25.51</v>
       </c>
-      <c r="S38" s="474">
+      <c r="S38" s="477">
         <v>26.83</v>
       </c>
-      <c r="T38" s="470">
-        <v>8.24</v>
+      <c r="T38" s="478">
+        <v>10.88</v>
       </c>
     </row>
     <row r="39">
@@ -10817,41 +10817,41 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="489">
+      <c r="I40" s="486">
         <v>78.38</v>
       </c>
-      <c r="J40" s="486">
+      <c r="J40" s="485">
         <v>62.16</v>
       </c>
-      <c r="K40" s="483">
+      <c r="K40" s="487">
         <v>56.76</v>
       </c>
-      <c r="L40" s="484">
+      <c r="L40" s="488">
         <v>59.46</v>
       </c>
-      <c r="M40" s="490">
+      <c r="M40" s="483">
         <v>51.35</v>
       </c>
-      <c r="N40" s="491">
+      <c r="N40" s="490">
         <v>40.54</v>
       </c>
-      <c r="O40" s="487">
+      <c r="O40" s="489">
         <v>37.84</v>
       </c>
-      <c r="P40" s="492">
+      <c r="P40" s="491">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="493">
+      <c r="Q40" s="492">
         <v>40.54</v>
       </c>
-      <c r="R40" s="485">
+      <c r="R40" s="493">
         <v>37.84</v>
       </c>
-      <c r="S40" s="488">
+      <c r="S40" s="482">
         <v>40.54</v>
       </c>
-      <c r="T40" s="482">
-        <v>27.03</v>
+      <c r="T40" s="484">
+        <v>21.62</v>
       </c>
     </row>
     <row r="41">
@@ -10865,41 +10865,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="505">
+      <c r="I41" s="500">
         <v>5.97</v>
       </c>
-      <c r="J41" s="494">
+      <c r="J41" s="496">
         <v>4.69</v>
       </c>
-      <c r="K41" s="495">
+      <c r="K41" s="502">
         <v>2.99</v>
       </c>
-      <c r="L41" s="496">
+      <c r="L41" s="503">
         <v>2.46</v>
       </c>
-      <c r="M41" s="499">
+      <c r="M41" s="497">
         <v>0.83</v>
       </c>
-      <c r="N41" s="500">
+      <c r="N41" s="498">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="501">
+      <c r="O41" s="504">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="497">
+      <c r="P41" s="499">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="502">
+      <c r="Q41" s="501">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="503">
+      <c r="R41" s="505">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="498">
+      <c r="S41" s="494">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="504">
-        <v>0.07</v>
+      <c r="T41" s="495">
+        <v>-1.88</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,121 +39,325 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD73242"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,85 +369,523 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BCC1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -255,19 +897,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,7 +1023,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,13 +1209,577 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD53241"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDE4251"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,2761 +1791,1279 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E6CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,41 +8489,41 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="11">
         <v>9.99</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="12">
         <v>13.15</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="13">
         <v>9.95</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>8.34</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="2">
         <v>9.06</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="7">
         <v>5.46</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="5">
         <v>3.94</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="8">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="6">
         <v>0.04</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="9">
         <v>1.19</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="3">
         <v>0.13</v>
       </c>
-      <c r="T2" s="13">
-        <v>-17.82</v>
+      <c r="T2" s="10">
+        <v>-17.55</v>
       </c>
     </row>
     <row r="3">
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002570</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -3219.58万</v>
       </c>
       <c r="E3">
@@ -8551,41 +8551,41 @@
       <c r="H3">
         <v>-1.51</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="16">
         <v>-8.66</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="25">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="19">
         <v>-15.92</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="17">
         <v>-14.66</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="26">
         <v>-9.78</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="23">
         <v>-11.59</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="18">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="14">
         <v>-15.36</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="15">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="20">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="21">
         <v>-15.92</v>
       </c>
-      <c r="T3" s="16">
-        <v>-31.98</v>
+      <c r="T3" s="22">
+        <v>-31.42</v>
       </c>
     </row>
     <row r="4">
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>601008</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 2459.29万</v>
       </c>
       <c r="E4">
@@ -8613,41 +8613,41 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="32">
         <v>8.18</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="27">
         <v>-2.55</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="33">
         <v>-0.36</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="34">
         <v>0.18</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="30">
         <v>-1.64</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="36">
         <v>-7.64</v>
       </c>
       <c r="O4" s="35">
         <v>-7.64</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="28">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="29">
         <v>11.82</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="37">
         <v>23.09</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="38">
         <v>35.45</v>
       </c>
-      <c r="T4" s="29">
-        <v>-13.82</v>
+      <c r="T4" s="39">
+        <v>-14</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8675,41 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="48">
         <v>11.02</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="51">
         <v>8.91</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="49">
         <v>19.8</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="44">
         <v>19.08</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="45">
         <v>19.87</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="52">
         <v>13</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="50">
         <v>12.87</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="46">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="40">
         <v>7.46</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="41">
         <v>5.61</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="47">
         <v>4.49</v>
       </c>
-      <c r="T5" s="44">
-        <v>-22.51</v>
+      <c r="T5" s="42">
+        <v>-22.31</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8743,35 +8743,35 @@
       <c r="J6" s="57">
         <v>13.13</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="58">
         <v>17.96</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="63">
         <v>22.02</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="59">
         <v>16.84</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="54">
         <v>9.93</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="64">
         <v>7.43</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="65">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="53">
         <v>9.93</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="60">
         <v>12.61</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="61">
         <v>23.83</v>
       </c>
-      <c r="T6" s="59">
-        <v>-30.05</v>
+      <c r="T6" s="62">
+        <v>-27.98</v>
       </c>
     </row>
     <row r="7">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8799,41 +8799,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="68">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="72">
         <v>-12.07</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="69">
         <v>-10.42</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="77">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="73">
         <v>-14.58</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="78">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="66">
         <v>-23.59</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="67">
         <v>-22.96</v>
       </c>
-      <c r="Q7" s="73">
+      <c r="Q7" s="74">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="74">
+      <c r="R7" s="70">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="75">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="77">
-        <v>-28.76</v>
+      <c r="T7" s="76">
+        <v>-31.27</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>002094</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="81" t="str">
         <v>净买: 3233.09万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8861,41 @@
       <c r="H8">
         <v>-1.1</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="82">
         <v>11.25</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="85">
         <v>10.01</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="86">
         <v>21.01</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="79">
         <v>18.67</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="87">
         <v>22.13</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="80">
         <v>21.76</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="83">
         <v>17.43</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="84">
         <v>16.19</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="88">
         <v>19.65</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="89">
         <v>23.73</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="90">
         <v>15.95</v>
       </c>
-      <c r="T8" s="84">
-        <v>-26.58</v>
+      <c r="T8" s="91">
+        <v>-26.33</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>002094</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -3419.88万</v>
       </c>
       <c r="E9">
@@ -8926,38 +8926,38 @@
       <c r="I9" s="96">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="97">
         <v>5.84</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="102">
         <v>3.78</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="103">
         <v>6.81</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="104">
         <v>6.49</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="98">
         <v>2.7</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="100">
         <v>1.62</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="99">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="92">
         <v>8.22</v>
       </c>
       <c r="R9" s="101">
         <v>1.41</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="93">
         <v>0.22</v>
       </c>
-      <c r="T9" s="92">
-        <v>-35.78</v>
+      <c r="T9" s="94">
+        <v>-35.57</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,41 +8985,41 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="105">
         <v>11.08</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="108">
         <v>0</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="111">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="106">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="112">
         <v>-16.07</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="116">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="107">
         <v>-11.64</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="113">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="109">
         <v>-19.06</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="114">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="117">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="105">
-        <v>-25.47</v>
+      <c r="T10" s="115">
+        <v>-24.45</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="118" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,28 +9047,28 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="125">
         <v>9.97</v>
       </c>
       <c r="J11" s="122">
         <v>5.4</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="119">
         <v>3.74</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="126">
         <v>7.89</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="127">
         <v>5.19</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="123">
         <v>1.14</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="128">
         <v>-0.31</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="124">
         <v>-6.65</v>
       </c>
       <c r="Q11" s="120">
@@ -9077,11 +9077,11 @@
       <c r="R11" s="121">
         <v>-8.62</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="130">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="127">
-        <v>-35.31</v>
+      <c r="T11" s="129">
+        <v>-34.48</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="137" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9109,41 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="135">
         <v>13</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="138">
         <v>1.73</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="132">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="140">
         <v>1.65</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="141">
         <v>2.69</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="142">
         <v>6.07</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="143">
         <v>12.39</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="136">
         <v>12.39</v>
       </c>
       <c r="Q12" s="131">
         <v>11.53</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="133">
         <v>7.02</v>
       </c>
-      <c r="S12" s="135">
+      <c r="S12" s="134">
         <v>5.55</v>
       </c>
-      <c r="T12" s="136">
-        <v>-35.18</v>
+      <c r="T12" s="139">
+        <v>-33.62</v>
       </c>
     </row>
     <row r="13">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="154" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,34 +9171,34 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="150">
         <v>4.11</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="151">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="152">
         <v>-2.4</v>
       </c>
       <c r="L13" s="156">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="155">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="153">
         <v>-10.96</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="144">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="145">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="146">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="147">
         <v>-17.12</v>
       </c>
       <c r="S13" s="148">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="167" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,41 +9233,41 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="163">
         <v>5.15</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="168">
         <v>11.46</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="164">
         <v>22.61</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="169">
         <v>10.3</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="161">
         <v>3.47</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="165">
         <v>-0.84</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="157">
         <v>2.52</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="158">
         <v>2</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="162">
         <v>0.11</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="159">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="166">
         <v>-2.73</v>
       </c>
-      <c r="T14" s="157">
-        <v>-0.84</v>
+      <c r="T14" s="160">
+        <v>2.73</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="180" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,41 +9295,41 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="181">
         <v>4.02</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="176">
         <v>14.43</v>
       </c>
       <c r="K15" s="171">
         <v>2.94</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="182">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="177">
         <v>-7.46</v>
       </c>
       <c r="N15" s="172">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="176">
+      <c r="O15" s="173">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="178">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="170">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="179">
         <v>-9.22</v>
       </c>
       <c r="S15" s="174">
         <v>-6.58</v>
       </c>
-      <c r="T15" s="182">
-        <v>-7.46</v>
+      <c r="T15" s="175">
+        <v>-4.12</v>
       </c>
     </row>
     <row r="16">
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="184" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9360,38 +9360,38 @@
       <c r="I16" s="192">
         <v>9.22</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="189">
         <v>5.78</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="186">
         <v>6.22</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="194">
         <v>2.11</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="193">
         <v>2.67</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="195">
         <v>4.89</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="187">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="194">
+      <c r="P16" s="190">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="183">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="191">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="186">
+      <c r="S16" s="188">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="191">
-        <v>-22.33</v>
+      <c r="T16" s="184">
+        <v>-18.22</v>
       </c>
     </row>
     <row r="17">
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600192</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="202" t="str">
         <v>净买: 2508.47万</v>
       </c>
       <c r="E17">
@@ -9419,41 +9419,41 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="203">
         <v>14.66</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="199">
         <v>16.25</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="204">
         <v>13.66</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="205">
         <v>2.29</v>
       </c>
       <c r="M17" s="206">
         <v>0.9</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="200">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="201">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="208">
         <v>-6.38</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="196">
         <v>-5.38</v>
       </c>
       <c r="R17" s="207">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="198">
+      <c r="S17" s="197">
         <v>-1</v>
       </c>
-      <c r="T17" s="208">
-        <v>-18.54</v>
+      <c r="T17" s="198">
+        <v>-17.85</v>
       </c>
     </row>
     <row r="18">
@@ -9481,41 +9481,41 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="213">
         <v>-1.44</v>
       </c>
       <c r="J18" s="220">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="221">
         <v>-13.27</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="214">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="210">
         <v>-16.74</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="211">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="218">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="218">
+      <c r="P18" s="215">
         <v>-19.78</v>
       </c>
-      <c r="Q18" s="215">
+      <c r="Q18" s="216">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="211">
+      <c r="R18" s="217">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="212">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="212">
-        <v>-30.94</v>
+      <c r="T18" s="209">
+        <v>-30.35</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="232" t="str">
+      <c r="D19" s="222" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9543,41 +9543,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="223">
         <v>10</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="232">
         <v>8.88</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="228">
         <v>12.24</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="233">
         <v>11.78</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="229">
         <v>9.28</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="230">
         <v>14.8</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="224">
         <v>11.38</v>
       </c>
-      <c r="P19" s="227">
+      <c r="P19" s="231">
         <v>6.25</v>
       </c>
-      <c r="Q19" s="233">
+      <c r="Q19" s="225">
         <v>6.71</v>
       </c>
-      <c r="R19" s="230">
+      <c r="R19" s="234">
         <v>7.11</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="226">
         <v>7.37</v>
       </c>
-      <c r="T19" s="234">
-        <v>-22.76</v>
+      <c r="T19" s="227">
+        <v>-22.57</v>
       </c>
     </row>
     <row r="20">
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>002553</v>
       </c>
-      <c r="D20" s="237" t="str">
+      <c r="D20" s="246" t="str">
         <v>净买: 2010.54万</v>
       </c>
       <c r="E20">
@@ -9605,41 +9605,41 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="247">
         <v>2.6</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="235">
         <v>2.16</v>
       </c>
-      <c r="K20" s="247">
+      <c r="K20" s="242">
         <v>3.16</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="236">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="243">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="238">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="239">
+      <c r="O20" s="244">
         <v>-1</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="237">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="240">
+      <c r="Q20" s="245">
         <v>-0.64</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="239">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="240">
         <v>-3.04</v>
       </c>
-      <c r="T20" s="242">
-        <v>-4.36</v>
+      <c r="T20" s="241">
+        <v>-3.84</v>
       </c>
     </row>
     <row r="21">
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>000657</v>
       </c>
-      <c r="D21" s="256" t="str">
+      <c r="D21" s="252" t="str">
         <v>净卖: -1.62亿</v>
       </c>
       <c r="E21">
@@ -9667,41 +9667,41 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="253">
         <v>7.81</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="254">
         <v>15.57</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="260">
         <v>9.09</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="259">
         <v>15.08</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="248">
         <v>3.57</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="249">
         <v>-2.42</v>
       </c>
-      <c r="O21" s="254">
+      <c r="O21" s="250">
         <v>-4.06</v>
       </c>
-      <c r="P21" s="255">
+      <c r="P21" s="257">
         <v>-4.54</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="255">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="260">
+      <c r="R21" s="251">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="258">
         <v>-2</v>
       </c>
-      <c r="T21" s="249">
-        <v>234.22</v>
+      <c r="T21" s="256">
+        <v>226.04</v>
       </c>
     </row>
     <row r="22">
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>000657</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="263" t="str">
         <v>净买: 6098.44万</v>
       </c>
       <c r="E22">
@@ -9729,41 +9729,41 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="264">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="268">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="271">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="273">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="269">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="273">
+      <c r="N22" s="270">
         <v>-13.43</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="265">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="271">
+      <c r="P22" s="272">
         <v>-11.6</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="266">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="261">
         <v>-10.9</v>
       </c>
       <c r="S22" s="267">
         <v>-8.81</v>
       </c>
-      <c r="T22" s="261">
-        <v>196.35</v>
+      <c r="T22" s="262">
+        <v>189.1</v>
       </c>
     </row>
     <row r="23">
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>600010</v>
       </c>
-      <c r="D23" s="284" t="str">
+      <c r="D23" s="277" t="str">
         <v>净卖: -1.03亿</v>
       </c>
       <c r="E23">
@@ -9791,41 +9791,41 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="279">
         <v>6.18</v>
       </c>
-      <c r="J23" s="286">
+      <c r="J23" s="278">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="280">
         <v>-8</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="275">
         <v>-8.73</v>
       </c>
-      <c r="M23" s="274">
+      <c r="M23" s="281">
         <v>-5.82</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="284">
         <v>-8</v>
       </c>
-      <c r="O23" s="281">
+      <c r="O23" s="285">
         <v>-4.73</v>
       </c>
-      <c r="P23" s="275">
+      <c r="P23" s="286">
         <v>-6.18</v>
       </c>
       <c r="Q23" s="282">
         <v>-6.55</v>
       </c>
-      <c r="R23" s="278">
+      <c r="R23" s="276">
         <v>-8.73</v>
       </c>
       <c r="S23" s="283">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="279">
-        <v>-0.36</v>
+      <c r="T23" s="274">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="24">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="289" t="str">
+      <c r="D24" s="287" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,41 +9853,41 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="288">
         <v>14.91</v>
       </c>
-      <c r="J24" s="295">
+      <c r="J24" s="297">
         <v>25.62</v>
       </c>
-      <c r="K24" s="290">
+      <c r="K24" s="296">
         <v>15.37</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="292">
         <v>11.34</v>
       </c>
-      <c r="M24" s="287">
+      <c r="M24" s="293">
         <v>3.42</v>
       </c>
-      <c r="N24" s="291">
+      <c r="N24" s="294">
         <v>5.9</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="289">
         <v>12.42</v>
       </c>
-      <c r="P24" s="292">
+      <c r="P24" s="295">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="288">
+      <c r="Q24" s="298">
         <v>7.92</v>
       </c>
-      <c r="R24" s="293">
+      <c r="R24" s="290">
         <v>5.59</v>
       </c>
-      <c r="S24" s="296">
+      <c r="S24" s="299">
         <v>11.02</v>
       </c>
-      <c r="T24" s="294">
-        <v>8.07</v>
+      <c r="T24" s="291">
+        <v>4.66</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="307" t="str">
+      <c r="D25" s="304" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9915,41 +9915,41 @@
       <c r="H25">
         <v>2.57</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="311">
         <v>6.59</v>
       </c>
-      <c r="J25" s="302">
+      <c r="J25" s="305">
         <v>-2.11</v>
       </c>
-      <c r="K25" s="311">
+      <c r="K25" s="312">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="303">
+      <c r="L25" s="306">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="309">
+      <c r="M25" s="307">
         <v>-10.14</v>
       </c>
-      <c r="N25" s="310">
+      <c r="N25" s="300">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="308">
         <v>-8.17</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="309">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="312">
+      <c r="Q25" s="301">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="305">
+      <c r="R25" s="302">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="306">
+      <c r="S25" s="310">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="301">
-        <v>-8.3</v>
+      <c r="T25" s="303">
+        <v>-11.2</v>
       </c>
     </row>
     <row r="26">
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>600117</v>
       </c>
-      <c r="D26" s="318" t="str">
+      <c r="D26" s="313" t="str">
         <v>净卖: -2617.46万</v>
       </c>
       <c r="E26">
@@ -9977,41 +9977,41 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="323">
+      <c r="I26" s="314">
         <v>-4.81</v>
       </c>
-      <c r="J26" s="324">
+      <c r="J26" s="315">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="325">
+      <c r="K26" s="324">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="320">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="313">
+      <c r="M26" s="316">
         <v>-21.44</v>
       </c>
-      <c r="N26" s="320">
+      <c r="N26" s="321">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="315">
+      <c r="O26" s="322">
         <v>-24.05</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="317">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="317">
+      <c r="Q26" s="325">
         <v>-27.45</v>
       </c>
-      <c r="R26" s="314">
+      <c r="R26" s="318">
         <v>-27.25</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="323">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="321">
-        <v>-47.9</v>
+      <c r="T26" s="319">
+        <v>-48.7</v>
       </c>
     </row>
     <row r="27">
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="328" t="str">
+      <c r="D27" s="337" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10042,38 +10042,38 @@
       <c r="I27" s="329">
         <v>7.83</v>
       </c>
-      <c r="J27" s="337">
+      <c r="J27" s="335">
         <v>3.08</v>
       </c>
-      <c r="K27" s="330">
+      <c r="K27" s="331">
         <v>1.68</v>
       </c>
-      <c r="L27" s="331">
+      <c r="L27" s="332">
         <v>0.28</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="333">
         <v>0.98</v>
       </c>
-      <c r="N27" s="335">
+      <c r="N27" s="338">
         <v>-1.26</v>
       </c>
-      <c r="O27" s="338">
+      <c r="O27" s="326">
         <v>-0.84</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="334">
         <v>0.14</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="327">
         <v>4.06</v>
       </c>
-      <c r="R27" s="334">
+      <c r="R27" s="336">
         <v>4.76</v>
       </c>
-      <c r="S27" s="333">
+      <c r="S27" s="328">
         <v>2.66</v>
       </c>
-      <c r="T27" s="327">
-        <v>-31.89</v>
+      <c r="T27" s="330">
+        <v>-31.33</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="346" t="str">
+      <c r="D28" s="351" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10104,38 +10104,38 @@
       <c r="I28" s="339">
         <v>11.11</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="348">
         <v>22.22</v>
       </c>
-      <c r="K28" s="348">
+      <c r="K28" s="345">
         <v>9.95</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="349">
         <v>1.85</v>
       </c>
-      <c r="M28" s="341">
+      <c r="M28" s="340">
         <v>-5.32</v>
       </c>
-      <c r="N28" s="342">
+      <c r="N28" s="341">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="342">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="350">
         <v>-7.87</v>
       </c>
-      <c r="Q28" s="350">
+      <c r="Q28" s="346">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="343">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="344">
+      <c r="S28" s="347">
         <v>-10.19</v>
       </c>
-      <c r="T28" s="345">
-        <v>-34.03</v>
+      <c r="T28" s="344">
+        <v>-31.94</v>
       </c>
     </row>
     <row r="29">
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>002097</v>
       </c>
-      <c r="D29" s="364" t="str">
+      <c r="D29" s="355" t="str">
         <v>净买: 6007.44万</v>
       </c>
       <c r="E29">
@@ -10163,41 +10163,41 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="355">
+      <c r="I29" s="352">
         <v>15.53</v>
       </c>
-      <c r="J29" s="362">
+      <c r="J29" s="356">
         <v>19.33</v>
       </c>
-      <c r="K29" s="363">
+      <c r="K29" s="353">
         <v>21.27</v>
       </c>
-      <c r="L29" s="356">
+      <c r="L29" s="360">
         <v>28.8</v>
       </c>
-      <c r="M29" s="357">
+      <c r="M29" s="362">
         <v>33.4</v>
       </c>
-      <c r="N29" s="352">
+      <c r="N29" s="357">
         <v>28.73</v>
       </c>
-      <c r="O29" s="358">
+      <c r="O29" s="363">
         <v>25.33</v>
       </c>
-      <c r="P29" s="359">
+      <c r="P29" s="361">
         <v>17.33</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="358">
         <v>13.93</v>
       </c>
-      <c r="R29" s="354">
+      <c r="R29" s="359">
         <v>11.4</v>
       </c>
-      <c r="S29" s="360">
+      <c r="S29" s="354">
         <v>13</v>
       </c>
-      <c r="T29" s="361">
-        <v>-34.33</v>
+      <c r="T29" s="364">
+        <v>-33.67</v>
       </c>
     </row>
     <row r="30">
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>601718</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="376" t="str">
         <v>净卖: -4886.83万</v>
       </c>
       <c r="E30">
@@ -10225,41 +10225,41 @@
       <c r="H30">
         <v>4.17</v>
       </c>
-      <c r="I30" s="374">
+      <c r="I30" s="370">
         <v>5.6</v>
       </c>
-      <c r="J30" s="369">
+      <c r="J30" s="377">
         <v>-5</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="365">
         <v>-12</v>
       </c>
-      <c r="L30" s="373">
+      <c r="L30" s="372">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="371">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="366">
+      <c r="N30" s="373">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="371">
+      <c r="O30" s="374">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="372">
+      <c r="P30" s="375">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="368">
         <v>-22</v>
       </c>
-      <c r="R30" s="376">
+      <c r="R30" s="366">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="377">
+      <c r="S30" s="369">
         <v>-20.2</v>
       </c>
       <c r="T30" s="367">
-        <v>-43</v>
+        <v>-41.2</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="379" t="str">
+      <c r="D31" s="383" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,41 +10287,41 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="380">
+      <c r="I31" s="378">
         <v>2.72</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="387">
         <v>1.18</v>
       </c>
-      <c r="K31" s="390">
+      <c r="K31" s="384">
         <v>-3.82</v>
       </c>
-      <c r="L31" s="383">
+      <c r="L31" s="389">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="381">
+      <c r="M31" s="390">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="385">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="385">
+      <c r="O31" s="379">
         <v>-10.28</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="380">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="381">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="388">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="388">
+      <c r="S31" s="382">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="382">
-        <v>54.23</v>
+      <c r="T31" s="386">
+        <v>55.24</v>
       </c>
     </row>
     <row r="32">
@@ -10349,41 +10349,41 @@
       <c r="H32">
         <v>-0.92</v>
       </c>
-      <c r="I32" s="402">
+      <c r="I32" s="401">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="402">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="395">
         <v>-10.08</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="399">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="399">
+      <c r="M32" s="403">
         <v>-0.93</v>
       </c>
-      <c r="N32" s="398">
+      <c r="N32" s="391">
         <v>-2.26</v>
       </c>
-      <c r="O32" s="403">
+      <c r="O32" s="392">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="396">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="392">
+      <c r="Q32" s="393">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="397">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="401">
+      <c r="S32" s="398">
         <v>1.44</v>
       </c>
-      <c r="T32" s="393">
-        <v>37.35</v>
+      <c r="T32" s="400">
+        <v>33.74</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="410" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10411,41 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="409">
+      <c r="I33" s="407">
         <v>8.08</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="411">
         <v>6.62</v>
       </c>
-      <c r="K33" s="404">
+      <c r="K33" s="412">
         <v>6.96</v>
       </c>
-      <c r="L33" s="407">
+      <c r="L33" s="408">
         <v>7.52</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="413">
         <v>5.27</v>
       </c>
-      <c r="N33" s="410">
+      <c r="N33" s="414">
         <v>3.03</v>
       </c>
-      <c r="O33" s="413">
+      <c r="O33" s="415">
         <v>10.66</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="404">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="416">
         <v>34.01</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="405">
         <v>47.36</v>
       </c>
-      <c r="S33" s="414">
+      <c r="S33" s="409">
         <v>50.39</v>
       </c>
-      <c r="T33" s="415">
-        <v>49.83</v>
+      <c r="T33" s="406">
+        <v>45.9</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="425" t="str">
+      <c r="D34" s="429" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10473,41 @@
       <c r="H34">
         <v>-4.48</v>
       </c>
-      <c r="I34" s="423">
+      <c r="I34" s="422">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="419">
+      <c r="J34" s="423">
         <v>0</v>
       </c>
-      <c r="K34" s="420">
+      <c r="K34" s="424">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="421">
+      <c r="L34" s="417">
         <v>4.61</v>
       </c>
-      <c r="M34" s="424">
+      <c r="M34" s="418">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="419">
         <v>-1.02</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="425">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="420">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="426">
         <v>-16.33</v>
       </c>
-      <c r="R34" s="418">
+      <c r="R34" s="421">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="429">
+      <c r="S34" s="427">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="422">
-        <v>4.3</v>
+      <c r="T34" s="428">
+        <v>1.56</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="438" t="str">
+      <c r="D35" s="434" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,41 +10535,41 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="439">
+      <c r="I35" s="435">
         <v>4.33</v>
       </c>
-      <c r="J35" s="442">
+      <c r="J35" s="436">
         <v>5.2</v>
       </c>
-      <c r="K35" s="435">
+      <c r="K35" s="431">
         <v>-1.91</v>
       </c>
-      <c r="L35" s="433">
+      <c r="L35" s="439">
         <v>-4.85</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="437">
         <v>-6.07</v>
       </c>
-      <c r="N35" s="436">
+      <c r="N35" s="440">
         <v>-7.11</v>
       </c>
-      <c r="O35" s="431">
+      <c r="O35" s="441">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="440">
+      <c r="P35" s="432">
         <v>-10.4</v>
       </c>
-      <c r="Q35" s="441">
+      <c r="Q35" s="433">
         <v>-10.4</v>
       </c>
-      <c r="R35" s="434">
+      <c r="R35" s="442">
         <v>-8.49</v>
       </c>
-      <c r="S35" s="432">
+      <c r="S35" s="430">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="437">
-        <v>-10.23</v>
+      <c r="T35" s="438">
+        <v>-10.05</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>301348</v>
       </c>
-      <c r="D36" s="449" t="str">
+      <c r="D36" s="452" t="str">
         <v>净卖: -905.79万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10597,41 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="450">
+      <c r="I36" s="454">
         <v>25.33</v>
       </c>
-      <c r="J36" s="454">
+      <c r="J36" s="455">
         <v>42.26</v>
       </c>
       <c r="K36" s="448">
         <v>32.49</v>
       </c>
-      <c r="L36" s="444">
+      <c r="L36" s="453">
         <v>48.47</v>
       </c>
-      <c r="M36" s="445">
+      <c r="M36" s="449">
         <v>52.11</v>
       </c>
-      <c r="N36" s="455">
+      <c r="N36" s="450">
         <v>37.42</v>
       </c>
-      <c r="O36" s="446">
+      <c r="O36" s="444">
         <v>48.97</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="445">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="447">
+      <c r="Q36" s="443">
         <v>31.29</v>
       </c>
       <c r="R36" s="451">
         <v>26.08</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="446">
         <v>22.06</v>
       </c>
-      <c r="T36" s="453">
-        <v>-1.37</v>
+      <c r="T36" s="447">
+        <v>0.7</v>
       </c>
     </row>
     <row r="37">
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>301348</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="459" t="str">
         <v>净卖: -4537.41万</v>
       </c>
       <c r="E37">
@@ -10662,38 +10662,38 @@
       <c r="I37" s="460">
         <v>7.11</v>
       </c>
-      <c r="J37" s="463">
+      <c r="J37" s="461">
         <v>-0.25</v>
       </c>
-      <c r="K37" s="456">
+      <c r="K37" s="462">
         <v>11.78</v>
       </c>
-      <c r="L37" s="464">
+      <c r="L37" s="463">
         <v>14.52</v>
       </c>
-      <c r="M37" s="465">
+      <c r="M37" s="467">
         <v>3.46</v>
       </c>
       <c r="N37" s="457">
         <v>12.15</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="464">
         <v>7.42</v>
       </c>
-      <c r="P37" s="462">
+      <c r="P37" s="465">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="468">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="466">
+      <c r="R37" s="458">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="467">
+      <c r="S37" s="456">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="461">
-        <v>-25.74</v>
+      <c r="T37" s="466">
+        <v>-24.18</v>
       </c>
     </row>
     <row r="38">
@@ -10721,41 +10721,41 @@
       <c r="H38">
         <v>-1.06</v>
       </c>
-      <c r="I38" s="479">
+      <c r="I38" s="470">
         <v>11.17</v>
       </c>
-      <c r="J38" s="474">
+      <c r="J38" s="478">
         <v>3.8</v>
       </c>
-      <c r="K38" s="472">
+      <c r="K38" s="477">
         <v>2.93</v>
       </c>
-      <c r="L38" s="470">
+      <c r="L38" s="475">
         <v>3.61</v>
       </c>
-      <c r="M38" s="480">
+      <c r="M38" s="479">
         <v>2.73</v>
       </c>
-      <c r="N38" s="475">
+      <c r="N38" s="480">
         <v>9.9</v>
       </c>
-      <c r="O38" s="476">
+      <c r="O38" s="471">
         <v>3.76</v>
       </c>
       <c r="P38" s="481">
         <v>14.15</v>
       </c>
-      <c r="Q38" s="473">
+      <c r="Q38" s="472">
         <v>25.56</v>
       </c>
-      <c r="R38" s="471">
+      <c r="R38" s="476">
         <v>25.51</v>
       </c>
-      <c r="S38" s="477">
+      <c r="S38" s="473">
         <v>26.83</v>
       </c>
-      <c r="T38" s="478">
-        <v>10.88</v>
+      <c r="T38" s="474">
+        <v>13.61</v>
       </c>
     </row>
     <row r="39">
@@ -10817,41 +10817,41 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="486">
+      <c r="I40" s="484">
         <v>78.38</v>
       </c>
-      <c r="J40" s="485">
+      <c r="J40" s="490">
         <v>62.16</v>
       </c>
-      <c r="K40" s="487">
+      <c r="K40" s="493">
         <v>56.76</v>
       </c>
       <c r="L40" s="488">
         <v>59.46</v>
       </c>
-      <c r="M40" s="483">
+      <c r="M40" s="485">
         <v>51.35</v>
       </c>
-      <c r="N40" s="490">
+      <c r="N40" s="491">
         <v>40.54</v>
       </c>
-      <c r="O40" s="489">
+      <c r="O40" s="486">
         <v>37.84</v>
       </c>
-      <c r="P40" s="491">
+      <c r="P40" s="492">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="492">
+      <c r="Q40" s="482">
         <v>40.54</v>
       </c>
-      <c r="R40" s="493">
+      <c r="R40" s="489">
         <v>37.84</v>
       </c>
-      <c r="S40" s="482">
+      <c r="S40" s="487">
         <v>40.54</v>
       </c>
-      <c r="T40" s="484">
-        <v>21.62</v>
+      <c r="T40" s="483">
+        <v>27.03</v>
       </c>
     </row>
     <row r="41">
@@ -10865,41 +10865,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="500">
+      <c r="I41" s="494">
         <v>5.97</v>
       </c>
-      <c r="J41" s="496">
+      <c r="J41" s="504">
         <v>4.69</v>
       </c>
-      <c r="K41" s="502">
+      <c r="K41" s="498">
         <v>2.99</v>
       </c>
-      <c r="L41" s="503">
+      <c r="L41" s="495">
         <v>2.46</v>
       </c>
-      <c r="M41" s="497">
+      <c r="M41" s="499">
         <v>0.83</v>
       </c>
-      <c r="N41" s="498">
+      <c r="N41" s="505">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="504">
+      <c r="O41" s="500">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="499">
+      <c r="P41" s="501">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="501">
+      <c r="Q41" s="496">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="505">
+      <c r="R41" s="502">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="494">
+      <c r="S41" s="503">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="495">
-        <v>-1.88</v>
+      <c r="T41" s="497">
+        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/真爱坤/index.xlsx
+++ b/youzi/真爱坤/index.xlsx
@@ -39,19 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
+        <fgColor rgb="FFD73242"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,7 +117,1687 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,18 +1809,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -117,55 +1827,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4D9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,25 +1887,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3E4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,7 +2073,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C1"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,31 +2127,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,7 +2157,877 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,2791 +3039,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4D9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF56B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>600536</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -5905.46万</v>
       </c>
       <c r="E2">
@@ -8489,41 +8489,41 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="8">
         <v>9.99</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="1">
         <v>13.15</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="2">
         <v>9.95</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>8.34</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="3">
         <v>9.06</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="12">
         <v>5.46</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="9">
         <v>3.94</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="6">
         <v>2.81</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="13">
         <v>0.04</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="10">
         <v>1.19</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="4">
         <v>0.13</v>
       </c>
-      <c r="T2" s="10">
-        <v>-17.55</v>
+      <c r="T2" s="7">
+        <v>-19.06</v>
       </c>
     </row>
     <row r="3">
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002570</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -3219.58万</v>
       </c>
       <c r="E3">
@@ -8551,13 +8551,13 @@
       <c r="H3">
         <v>-1.51</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="22">
         <v>-8.66</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="14">
         <v>-17.74</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="25">
         <v>-15.92</v>
       </c>
       <c r="L3" s="17">
@@ -8566,26 +8566,26 @@
       <c r="M3" s="26">
         <v>-9.78</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="15">
         <v>-11.59</v>
       </c>
       <c r="O3" s="18">
         <v>-10.75</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="19">
         <v>-15.36</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="23">
         <v>-15.22</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="16">
         <v>-17.32</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="24">
         <v>-15.92</v>
       </c>
-      <c r="T3" s="22">
-        <v>-31.42</v>
+      <c r="T3" s="20">
+        <v>-32.4</v>
       </c>
     </row>
     <row r="4">
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>601008</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 2459.29万</v>
       </c>
       <c r="E4">
@@ -8613,41 +8613,41 @@
       <c r="H4">
         <v>-5.34</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="29">
         <v>8.18</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="38">
         <v>-2.55</v>
       </c>
       <c r="K4" s="33">
         <v>-0.36</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="39">
         <v>0.18</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="34">
         <v>-1.64</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="30">
         <v>-7.64</v>
       </c>
       <c r="O4" s="35">
         <v>-7.64</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="37">
         <v>1.64</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="27">
         <v>11.82</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="36">
         <v>23.09</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="28">
         <v>35.45</v>
       </c>
-      <c r="T4" s="39">
-        <v>-14</v>
+      <c r="T4" s="31">
+        <v>-14.55</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>000678</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="40" t="str">
         <v>净买: 2360.07万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8675,41 @@
       <c r="H5">
         <v>-0.92</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="45">
         <v>11.02</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="50">
         <v>8.91</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="46">
         <v>19.8</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="51">
         <v>19.08</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="47">
         <v>19.87</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="48">
         <v>13</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="41">
         <v>12.87</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="44">
         <v>4.88</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="42">
         <v>7.46</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="43">
         <v>5.61</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="49">
         <v>4.49</v>
       </c>
-      <c r="T5" s="42">
-        <v>-22.31</v>
+      <c r="T5" s="52">
+        <v>-24.62</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>601086</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -1890.32万</v>
       </c>
       <c r="E6">
@@ -8737,41 +8737,41 @@
       <c r="H6">
         <v>-1.7</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <v>11.92</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="61">
         <v>13.13</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="65">
         <v>17.96</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="53">
         <v>22.02</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="58">
         <v>16.84</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="59">
         <v>9.93</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="62">
         <v>7.43</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="54">
         <v>1.73</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="55">
         <v>9.93</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="56">
         <v>12.61</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="63">
         <v>23.83</v>
       </c>
-      <c r="T6" s="62">
-        <v>-27.98</v>
+      <c r="T6" s="60">
+        <v>-29.88</v>
       </c>
     </row>
     <row r="7">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -5224.14万</v>
       </c>
       <c r="E7">
@@ -8799,41 +8799,41 @@
       <c r="H7">
         <v>-0.23</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="75">
         <v>-8.39</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="76">
         <v>-12.07</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="67">
         <v>-10.42</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="72">
         <v>-9.95</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="68">
         <v>-14.58</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="77">
         <v>-17.01</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="69">
         <v>-23.59</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="70">
         <v>-22.96</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="78">
         <v>-20.22</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="71">
         <v>-23.35</v>
       </c>
-      <c r="S7" s="75">
+      <c r="S7" s="73">
         <v>-24.06</v>
       </c>
-      <c r="T7" s="76">
-        <v>-31.27</v>
+      <c r="T7" s="74">
+        <v>-31.74</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>002094</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="83" t="str">
         <v>净买: 3233.09万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8861,41 @@
       <c r="H8">
         <v>-1.1</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="87">
         <v>11.25</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="88">
         <v>10.01</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="79">
         <v>21.01</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="89">
         <v>18.67</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="90">
         <v>22.13</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="84">
         <v>21.76</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="85">
         <v>17.43</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="86">
         <v>16.19</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="80">
         <v>19.65</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="91">
         <v>23.73</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="81">
         <v>15.95</v>
       </c>
-      <c r="T8" s="91">
-        <v>-26.33</v>
+      <c r="T8" s="82">
+        <v>-27.56</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>002094</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -3419.88万</v>
       </c>
       <c r="E9">
@@ -8923,41 +8923,41 @@
       <c r="H9">
         <v>2.78</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="97">
         <v>-3.78</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="94">
         <v>5.84</v>
       </c>
-      <c r="K9" s="102">
+      <c r="K9" s="98">
         <v>3.78</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="99">
         <v>6.81</v>
       </c>
-      <c r="M9" s="104">
+      <c r="M9" s="100">
         <v>6.49</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="101">
         <v>2.7</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="92">
         <v>1.62</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="95">
         <v>4.65</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="102">
         <v>8.22</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="93">
         <v>1.41</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="103">
         <v>0.22</v>
       </c>
-      <c r="T9" s="94">
-        <v>-35.57</v>
+      <c r="T9" s="96">
+        <v>-36.65</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002735</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="117" t="str">
         <v>净买: 4713.73万</v>
       </c>
       <c r="E10">
@@ -8985,41 +8985,41 @@
       <c r="H10">
         <v>-0.96</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="113">
         <v>11.08</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="114">
         <v>0</v>
       </c>
-      <c r="K10" s="111">
+      <c r="K10" s="108">
         <v>-10.02</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="105">
         <v>-13.57</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="109">
         <v>-16.07</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="115">
         <v>-15.25</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="110">
         <v>-11.64</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="111">
         <v>-15.56</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="106">
         <v>-19.06</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="107">
         <v>-16.88</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="112">
         <v>-14.49</v>
       </c>
-      <c r="T10" s="115">
-        <v>-24.45</v>
+      <c r="T10" s="116">
+        <v>-27.4</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>002427</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -2198.04万</v>
       </c>
       <c r="E11">
@@ -9047,41 +9047,41 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="123">
         <v>9.97</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="121">
         <v>5.4</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="127">
         <v>3.74</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="124">
         <v>7.89</v>
       </c>
-      <c r="M11" s="127">
+      <c r="M11" s="128">
         <v>5.19</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="125">
         <v>1.14</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="129">
         <v>-0.31</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="130">
         <v>-6.65</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="119">
         <v>-3.32</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="120">
         <v>-8.62</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="118">
         <v>-6.75</v>
       </c>
-      <c r="T11" s="129">
-        <v>-34.48</v>
+      <c r="T11" s="122">
+        <v>-35.2</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603900</v>
       </c>
-      <c r="D12" s="137" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 1483.20万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9109,41 @@
       <c r="H12">
         <v>-2.62</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="141">
         <v>13</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="132">
         <v>1.73</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="133">
         <v>-3.81</v>
       </c>
-      <c r="L12" s="140">
+      <c r="L12" s="138">
         <v>1.65</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="142">
         <v>2.69</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="139">
         <v>6.07</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="135">
         <v>12.39</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="143">
         <v>12.39</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="134">
         <v>11.53</v>
       </c>
-      <c r="R12" s="133">
+      <c r="R12" s="131">
         <v>7.02</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="136">
         <v>5.55</v>
       </c>
-      <c r="T12" s="139">
-        <v>-33.62</v>
+      <c r="T12" s="137">
+        <v>-33.88</v>
       </c>
     </row>
     <row r="13">
@@ -9151,12 +9151,12 @@
         <v>2025-06-05</v>
       </c>
       <c r="B13" t="str">
-        <v>棕榈股份</v>
+        <v>ST棕榈</v>
       </c>
       <c r="C13" t="str">
         <v>002431</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="152" t="str">
         <v>净买: 2379.07万</v>
       </c>
       <c r="E13">
@@ -9171,41 +9171,41 @@
       <c r="H13">
         <v>-2.67</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="153">
         <v>4.11</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="154">
         <v>-3.08</v>
       </c>
-      <c r="K13" s="152">
+      <c r="K13" s="150">
         <v>-2.4</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="155">
         <v>-6.51</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="156">
         <v>-7.88</v>
       </c>
-      <c r="N13" s="153">
+      <c r="N13" s="151">
         <v>-10.96</v>
       </c>
       <c r="O13" s="144">
         <v>-15.41</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="146">
         <v>-15.75</v>
       </c>
-      <c r="Q13" s="146">
+      <c r="Q13" s="147">
         <v>-15.75</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="145">
         <v>-17.12</v>
       </c>
       <c r="S13" s="148">
         <v>-19.86</v>
       </c>
       <c r="T13" s="149">
-        <v>-17.12</v>
+        <v>-21.23</v>
       </c>
     </row>
     <row r="14">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>002235</v>
       </c>
-      <c r="D14" s="167" t="str">
+      <c r="D14" s="157" t="str">
         <v>净买: 4504.36万</v>
       </c>
       <c r="E14">
@@ -9233,41 +9233,41 @@
       <c r="H14">
         <v>-3.94</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="162">
         <v>5.15</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="158">
         <v>11.46</v>
       </c>
       <c r="K14" s="164">
         <v>22.61</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="165">
         <v>10.3</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="159">
         <v>3.47</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="166">
         <v>-0.84</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="160">
         <v>2.52</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="161">
         <v>2</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="167">
         <v>0.11</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="168">
         <v>-5.26</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="163">
         <v>-2.73</v>
       </c>
-      <c r="T14" s="160">
-        <v>2.73</v>
+      <c r="T14" s="169">
+        <v>3.47</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>002235</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="179" t="str">
         <v>净卖: -4379.59万</v>
       </c>
       <c r="E15">
@@ -9295,41 +9295,41 @@
       <c r="H15">
         <v>1.9</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="176">
         <v>4.02</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="173">
         <v>14.43</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="174">
         <v>2.94</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="177">
         <v>-3.43</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="175">
         <v>-7.46</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="182">
         <v>-4.32</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="180">
         <v>-4.81</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="170">
         <v>-6.58</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="171">
         <v>-11.58</v>
       </c>
-      <c r="R15" s="179">
+      <c r="R15" s="172">
         <v>-9.22</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="178">
         <v>-6.58</v>
       </c>
-      <c r="T15" s="175">
-        <v>-4.12</v>
+      <c r="T15" s="181">
+        <v>-3.43</v>
       </c>
     </row>
     <row r="16">
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>002366</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="183" t="str">
         <v>净买: 4590.15万</v>
       </c>
       <c r="E16">
@@ -9357,41 +9357,41 @@
       <c r="H16">
         <v>0.67</v>
       </c>
-      <c r="I16" s="192">
+      <c r="I16" s="184">
         <v>9.22</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="185">
         <v>5.78</v>
       </c>
       <c r="K16" s="186">
         <v>6.22</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="192">
         <v>2.11</v>
       </c>
       <c r="M16" s="193">
         <v>2.67</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="189">
         <v>4.89</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="190">
         <v>-0.89</v>
       </c>
-      <c r="P16" s="190">
+      <c r="P16" s="194">
         <v>-5.56</v>
       </c>
-      <c r="Q16" s="183">
+      <c r="Q16" s="195">
         <v>-3.22</v>
       </c>
-      <c r="R16" s="191">
+      <c r="R16" s="187">
         <v>-4.11</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="191">
         <v>-3.67</v>
       </c>
-      <c r="T16" s="184">
-        <v>-18.22</v>
+      <c r="T16" s="188">
+        <v>-17.67</v>
       </c>
     </row>
     <row r="17">
@@ -9419,41 +9419,41 @@
       <c r="H17">
         <v>-4.02</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="200">
         <v>14.66</v>
       </c>
-      <c r="J17" s="199">
+      <c r="J17" s="206">
         <v>16.25</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="207">
         <v>13.66</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="208">
         <v>2.29</v>
       </c>
-      <c r="M17" s="206">
+      <c r="M17" s="196">
         <v>0.9</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="203">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="197">
         <v>-5.38</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="198">
         <v>-6.38</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="204">
         <v>-5.38</v>
       </c>
-      <c r="R17" s="207">
+      <c r="R17" s="205">
         <v>-6.68</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="199">
         <v>-1</v>
       </c>
-      <c r="T17" s="198">
-        <v>-17.85</v>
+      <c r="T17" s="201">
+        <v>-19.04</v>
       </c>
     </row>
     <row r="18">
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>600192</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="221" t="str">
         <v>净卖: -2805.31万</v>
       </c>
       <c r="E18">
@@ -9481,41 +9481,41 @@
       <c r="H18">
         <v>2.87</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="220">
         <v>-1.44</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="215">
         <v>-3.63</v>
       </c>
-      <c r="K18" s="221">
+      <c r="K18" s="216">
         <v>-13.27</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="209">
         <v>-14.45</v>
       </c>
-      <c r="M18" s="210">
+      <c r="M18" s="217">
         <v>-16.74</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="212">
         <v>-19.78</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="213">
         <v>-20.63</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="218">
         <v>-19.78</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="210">
         <v>-20.88</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="219">
         <v>-16.06</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="211">
         <v>-14.88</v>
       </c>
-      <c r="T18" s="209">
-        <v>-30.35</v>
+      <c r="T18" s="214">
+        <v>-31.36</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>000678</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="230" t="str">
         <v>净买: 2962.57万</v>
       </c>
       <c r="E19">
@@ -9543,41 +9543,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="226">
         <v>10</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="227">
         <v>8.88</v>
       </c>
       <c r="K19" s="228">
         <v>12.24</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="231">
         <v>11.78</v>
       </c>
-      <c r="M19" s="229">
+      <c r="M19" s="232">
         <v>9.28</v>
       </c>
-      <c r="N19" s="230">
+      <c r="N19" s="223">
         <v>14.8</v>
       </c>
       <c r="O19" s="224">
         <v>11.38</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="233">
         <v>6.25</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="229">
         <v>6.71</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="225">
         <v>7.11</v>
       </c>
-      <c r="S19" s="226">
+      <c r="S19" s="234">
         <v>7.37</v>
       </c>
-      <c r="T19" s="227">
-        <v>-22.57</v>
+      <c r="T19" s="222">
+        <v>-24.87</v>
       </c>
     </row>
     <row r="20">
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>002553</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="235" t="str">
         <v>净买: 2010.54万</v>
       </c>
       <c r="E20">
@@ -9605,41 +9605,41 @@
       <c r="H20">
         <v>-0.64</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="246">
         <v>2.6</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="238">
         <v>2.16</v>
       </c>
-      <c r="K20" s="242">
+      <c r="K20" s="239">
         <v>3.16</v>
       </c>
       <c r="L20" s="236">
         <v>-1.4</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="240">
         <v>-1.24</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="242">
         <v>-1.24</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="247">
         <v>-1</v>
       </c>
       <c r="P20" s="237">
         <v>0.16</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="241">
         <v>-0.64</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="243">
         <v>-0.28</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="244">
         <v>-3.04</v>
       </c>
-      <c r="T20" s="241">
-        <v>-3.84</v>
+      <c r="T20" s="245">
+        <v>-6.4</v>
       </c>
     </row>
     <row r="21">
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>000657</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="248" t="str">
         <v>净卖: -1.62亿</v>
       </c>
       <c r="E21">
@@ -9667,41 +9667,41 @@
       <c r="H21">
         <v>2.04</v>
       </c>
-      <c r="I21" s="253">
+      <c r="I21" s="249">
         <v>7.81</v>
       </c>
-      <c r="J21" s="254">
+      <c r="J21" s="257">
         <v>15.57</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="255">
         <v>9.09</v>
       </c>
-      <c r="L21" s="259">
+      <c r="L21" s="258">
         <v>15.08</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="259">
         <v>3.57</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="250">
         <v>-2.42</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="251">
         <v>-4.06</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="252">
         <v>-4.54</v>
       </c>
-      <c r="Q21" s="255">
+      <c r="Q21" s="253">
         <v>-4.36</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="256">
         <v>-2.36</v>
       </c>
-      <c r="S21" s="258">
+      <c r="S21" s="254">
         <v>-2</v>
       </c>
-      <c r="T21" s="256">
-        <v>226.04</v>
+      <c r="T21" s="260">
+        <v>215.57</v>
       </c>
     </row>
     <row r="22">
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>000657</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="273" t="str">
         <v>净买: 6098.44万</v>
       </c>
       <c r="E22">
@@ -9729,41 +9729,41 @@
       <c r="H22">
         <v>-2</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="261">
         <v>-8.16</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="269">
         <v>-13.48</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="270">
         <v>-14.93</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="268">
         <v>-15.36</v>
       </c>
-      <c r="M22" s="269">
+      <c r="M22" s="262">
         <v>-15.2</v>
       </c>
-      <c r="N22" s="270">
+      <c r="N22" s="271">
         <v>-13.43</v>
       </c>
       <c r="O22" s="265">
         <v>-13.1</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="263">
         <v>-11.6</v>
       </c>
       <c r="Q22" s="266">
         <v>-10.74</v>
       </c>
-      <c r="R22" s="261">
+      <c r="R22" s="267">
         <v>-10.9</v>
       </c>
-      <c r="S22" s="267">
+      <c r="S22" s="272">
         <v>-8.81</v>
       </c>
-      <c r="T22" s="262">
-        <v>189.1</v>
+      <c r="T22" s="264">
+        <v>179.81</v>
       </c>
     </row>
     <row r="23">
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>600010</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="283" t="str">
         <v>净卖: -1.03亿</v>
       </c>
       <c r="E23">
@@ -9791,41 +9791,41 @@
       <c r="H23">
         <v>3.77</v>
       </c>
-      <c r="I23" s="279">
+      <c r="I23" s="274">
         <v>6.18</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="275">
         <v>-2.18</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="282">
         <v>-8</v>
       </c>
-      <c r="L23" s="275">
+      <c r="L23" s="284">
         <v>-8.73</v>
       </c>
-      <c r="M23" s="281">
+      <c r="M23" s="276">
         <v>-5.82</v>
       </c>
-      <c r="N23" s="284">
+      <c r="N23" s="280">
         <v>-8</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="277">
         <v>-4.73</v>
       </c>
-      <c r="P23" s="286">
+      <c r="P23" s="278">
         <v>-6.18</v>
       </c>
-      <c r="Q23" s="282">
+      <c r="Q23" s="281">
         <v>-6.55</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="279">
         <v>-8.73</v>
       </c>
-      <c r="S23" s="283">
+      <c r="S23" s="285">
         <v>-8.73</v>
       </c>
-      <c r="T23" s="274">
-        <v>-1.82</v>
+      <c r="T23" s="286">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="24">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>002370</v>
       </c>
-      <c r="D24" s="287" t="str">
+      <c r="D24" s="299" t="str">
         <v>净买: 3721.90万</v>
       </c>
       <c r="E24">
@@ -9853,41 +9853,41 @@
       <c r="H24">
         <v>-4.31</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="297">
         <v>14.91</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="287">
         <v>25.62</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="298">
         <v>15.37</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="296">
         <v>11.34</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="288">
         <v>3.42</v>
       </c>
-      <c r="N24" s="294">
+      <c r="N24" s="289">
         <v>5.9</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="290">
         <v>12.42</v>
       </c>
-      <c r="P24" s="295">
+      <c r="P24" s="291">
         <v>8.23</v>
       </c>
-      <c r="Q24" s="298">
+      <c r="Q24" s="294">
         <v>7.92</v>
       </c>
-      <c r="R24" s="290">
+      <c r="R24" s="292">
         <v>5.59</v>
       </c>
-      <c r="S24" s="299">
+      <c r="S24" s="293">
         <v>11.02</v>
       </c>
-      <c r="T24" s="291">
-        <v>4.66</v>
+      <c r="T24" s="295">
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>002370</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="308" t="str">
         <v>净卖: -3910.43万</v>
       </c>
       <c r="E25">
@@ -9915,41 +9915,41 @@
       <c r="H25">
         <v>2.57</v>
       </c>
-      <c r="I25" s="311">
+      <c r="I25" s="309">
         <v>6.59</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="300">
         <v>-2.11</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="310">
         <v>-5.53</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="303">
         <v>-12.25</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="304">
         <v>-10.14</v>
       </c>
-      <c r="N25" s="300">
+      <c r="N25" s="301">
         <v>-4.61</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="311">
         <v>-8.17</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="302">
         <v>-8.43</v>
       </c>
-      <c r="Q25" s="301">
+      <c r="Q25" s="305">
         <v>-10.41</v>
       </c>
-      <c r="R25" s="302">
+      <c r="R25" s="306">
         <v>-5.8</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="312">
         <v>-4.08</v>
       </c>
-      <c r="T25" s="303">
-        <v>-11.2</v>
+      <c r="T25" s="307">
+        <v>-12.78</v>
       </c>
     </row>
     <row r="26">
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>600117</v>
       </c>
-      <c r="D26" s="313" t="str">
+      <c r="D26" s="314" t="str">
         <v>净卖: -2617.46万</v>
       </c>
       <c r="E26">
@@ -9977,41 +9977,41 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="322">
         <v>-4.81</v>
       </c>
       <c r="J26" s="315">
         <v>-14.23</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="323">
         <v>-22.65</v>
       </c>
-      <c r="L26" s="320">
+      <c r="L26" s="318">
         <v>-18.44</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="325">
         <v>-21.44</v>
       </c>
-      <c r="N26" s="321">
+      <c r="N26" s="313">
         <v>-23.85</v>
       </c>
-      <c r="O26" s="322">
+      <c r="O26" s="324">
         <v>-24.05</v>
       </c>
-      <c r="P26" s="317">
+      <c r="P26" s="319">
         <v>-27.86</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="320">
         <v>-27.45</v>
       </c>
-      <c r="R26" s="318">
+      <c r="R26" s="316">
         <v>-27.25</v>
       </c>
-      <c r="S26" s="323">
+      <c r="S26" s="321">
         <v>-28.06</v>
       </c>
-      <c r="T26" s="319">
-        <v>-48.7</v>
+      <c r="T26" s="317">
+        <v>-48.9</v>
       </c>
     </row>
     <row r="27">
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>002570</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="332" t="str">
         <v>净买: 4416.07万</v>
       </c>
       <c r="E27">
@@ -10039,41 +10039,41 @@
       <c r="H27">
         <v>-2.19</v>
       </c>
-      <c r="I27" s="329">
+      <c r="I27" s="337">
         <v>7.83</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="333">
         <v>3.08</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="326">
         <v>1.68</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="338">
         <v>0.28</v>
       </c>
-      <c r="M27" s="333">
+      <c r="M27" s="327">
         <v>0.98</v>
       </c>
-      <c r="N27" s="338">
+      <c r="N27" s="329">
         <v>-1.26</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="328">
         <v>-0.84</v>
       </c>
       <c r="P27" s="334">
         <v>0.14</v>
       </c>
-      <c r="Q27" s="327">
+      <c r="Q27" s="330">
         <v>4.06</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="331">
         <v>4.76</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="335">
         <v>2.66</v>
       </c>
-      <c r="T27" s="330">
-        <v>-31.33</v>
+      <c r="T27" s="336">
+        <v>-32.31</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>601718</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="348" t="str">
         <v>净买: 4197.69万</v>
       </c>
       <c r="E28">
@@ -10101,41 +10101,41 @@
       <c r="H28">
         <v>-0.92</v>
       </c>
-      <c r="I28" s="339">
+      <c r="I28" s="344">
         <v>11.11</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="339">
         <v>22.22</v>
       </c>
-      <c r="K28" s="345">
+      <c r="K28" s="340">
         <v>9.95</v>
       </c>
       <c r="L28" s="349">
         <v>1.85</v>
       </c>
-      <c r="M28" s="340">
+      <c r="M28" s="346">
         <v>-5.32</v>
       </c>
-      <c r="N28" s="341">
+      <c r="N28" s="350">
         <v>-10.19</v>
       </c>
-      <c r="O28" s="342">
+      <c r="O28" s="345">
         <v>-9.26</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="341">
         <v>-7.87</v>
       </c>
-      <c r="Q28" s="346">
+      <c r="Q28" s="342">
         <v>-9.49</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="347">
         <v>-9.72</v>
       </c>
-      <c r="S28" s="347">
+      <c r="S28" s="351">
         <v>-10.19</v>
       </c>
-      <c r="T28" s="344">
-        <v>-31.94</v>
+      <c r="T28" s="343">
+        <v>-32.87</v>
       </c>
     </row>
     <row r="29">
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>002097</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="363" t="str">
         <v>净买: 6007.44万</v>
       </c>
       <c r="E29">
@@ -10163,41 +10163,41 @@
       <c r="H29">
         <v>-4.76</v>
       </c>
-      <c r="I29" s="352">
+      <c r="I29" s="364">
         <v>15.53</v>
       </c>
-      <c r="J29" s="356">
+      <c r="J29" s="352">
         <v>19.33</v>
       </c>
-      <c r="K29" s="353">
+      <c r="K29" s="358">
         <v>21.27</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="359">
         <v>28.8</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="360">
         <v>33.4</v>
       </c>
-      <c r="N29" s="357">
+      <c r="N29" s="361">
         <v>28.73</v>
       </c>
-      <c r="O29" s="363">
+      <c r="O29" s="353">
         <v>25.33</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="354">
         <v>17.33</v>
       </c>
-      <c r="Q29" s="358">
+      <c r="Q29" s="355">
         <v>13.93</v>
       </c>
-      <c r="R29" s="359">
+      <c r="R29" s="362">
         <v>11.4</v>
       </c>
-      <c r="S29" s="354">
+      <c r="S29" s="356">
         <v>13</v>
       </c>
-      <c r="T29" s="364">
-        <v>-33.67</v>
+      <c r="T29" s="357">
+        <v>-33.13</v>
       </c>
     </row>
     <row r="30">
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>601718</v>
       </c>
-      <c r="D30" s="376" t="str">
+      <c r="D30" s="377" t="str">
         <v>净卖: -4886.83万</v>
       </c>
       <c r="E30">
@@ -10225,41 +10225,41 @@
       <c r="H30">
         <v>4.17</v>
       </c>
-      <c r="I30" s="370">
+      <c r="I30" s="365">
         <v>5.6</v>
       </c>
-      <c r="J30" s="377">
+      <c r="J30" s="373">
         <v>-5</v>
       </c>
-      <c r="K30" s="365">
+      <c r="K30" s="366">
         <v>-12</v>
       </c>
-      <c r="L30" s="372">
+      <c r="L30" s="370">
         <v>-18.2</v>
       </c>
-      <c r="M30" s="371">
+      <c r="M30" s="368">
         <v>-22.4</v>
       </c>
-      <c r="N30" s="373">
+      <c r="N30" s="374">
         <v>-21.6</v>
       </c>
-      <c r="O30" s="374">
+      <c r="O30" s="371">
         <v>-20.4</v>
       </c>
-      <c r="P30" s="375">
+      <c r="P30" s="369">
         <v>-21.8</v>
       </c>
-      <c r="Q30" s="368">
+      <c r="Q30" s="375">
         <v>-22</v>
       </c>
-      <c r="R30" s="366">
+      <c r="R30" s="367">
         <v>-22.4</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="376">
         <v>-20.2</v>
       </c>
-      <c r="T30" s="367">
-        <v>-41.2</v>
+      <c r="T30" s="372">
+        <v>-42</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>000960</v>
       </c>
-      <c r="D31" s="383" t="str">
+      <c r="D31" s="388" t="str">
         <v>净卖: -2.27亿</v>
       </c>
       <c r="E31">
@@ -10287,41 +10287,41 @@
       <c r="H31">
         <v>-2.11</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="389">
         <v>2.72</v>
       </c>
-      <c r="J31" s="387">
+      <c r="J31" s="384">
         <v>1.18</v>
       </c>
-      <c r="K31" s="384">
+      <c r="K31" s="382">
         <v>-3.82</v>
       </c>
-      <c r="L31" s="389">
+      <c r="L31" s="390">
         <v>-4.27</v>
       </c>
-      <c r="M31" s="390">
+      <c r="M31" s="385">
         <v>-6.46</v>
       </c>
-      <c r="N31" s="385">
+      <c r="N31" s="378">
         <v>-9.92</v>
       </c>
-      <c r="O31" s="379">
+      <c r="O31" s="383">
         <v>-10.28</v>
       </c>
-      <c r="P31" s="380">
+      <c r="P31" s="379">
         <v>-8.01</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="380">
         <v>-8.74</v>
       </c>
-      <c r="R31" s="388">
+      <c r="R31" s="381">
         <v>-7.93</v>
       </c>
-      <c r="S31" s="382">
+      <c r="S31" s="386">
         <v>-6.02</v>
       </c>
-      <c r="T31" s="386">
-        <v>55.24</v>
+      <c r="T31" s="387">
+        <v>41.99</v>
       </c>
     </row>
     <row r="32">
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600078</v>
       </c>
-      <c r="D32" s="394" t="str">
+      <c r="D32" s="391" t="str">
         <v>净买: 1268.44万</v>
       </c>
       <c r="E32">
@@ -10349,41 +10349,41 @@
       <c r="H32">
         <v>-0.92</v>
       </c>
-      <c r="I32" s="401">
+      <c r="I32" s="395">
         <v>-8.64</v>
       </c>
-      <c r="J32" s="402">
+      <c r="J32" s="396">
         <v>-12.04</v>
       </c>
-      <c r="K32" s="395">
+      <c r="K32" s="399">
         <v>-10.08</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="397">
         <v>-9.98</v>
       </c>
-      <c r="M32" s="403">
+      <c r="M32" s="400">
         <v>-0.93</v>
       </c>
-      <c r="N32" s="391">
+      <c r="N32" s="401">
         <v>-2.26</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="402">
         <v>-1.95</v>
       </c>
-      <c r="P32" s="396">
+      <c r="P32" s="393">
         <v>-1.44</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="398">
         <v>-3.5</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="403">
         <v>-5.56</v>
       </c>
-      <c r="S32" s="398">
+      <c r="S32" s="392">
         <v>1.44</v>
       </c>
-      <c r="T32" s="400">
-        <v>33.74</v>
+      <c r="T32" s="394">
+        <v>30.97</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600078</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="416" t="str">
         <v>净卖: -996.24万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10411,41 @@
       <c r="H33">
         <v>1.83</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="411">
         <v>8.08</v>
       </c>
-      <c r="J33" s="411">
+      <c r="J33" s="413">
         <v>6.62</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="414">
         <v>6.96</v>
       </c>
       <c r="L33" s="408">
         <v>7.52</v>
       </c>
-      <c r="M33" s="413">
+      <c r="M33" s="404">
         <v>5.27</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="409">
         <v>3.03</v>
       </c>
-      <c r="O33" s="415">
+      <c r="O33" s="405">
         <v>10.66</v>
       </c>
-      <c r="P33" s="404">
+      <c r="P33" s="410">
         <v>21.77</v>
       </c>
-      <c r="Q33" s="416">
+      <c r="Q33" s="406">
         <v>34.01</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="412">
         <v>47.36</v>
       </c>
-      <c r="S33" s="409">
+      <c r="S33" s="407">
         <v>50.39</v>
       </c>
-      <c r="T33" s="406">
-        <v>45.9</v>
+      <c r="T33" s="415">
+        <v>42.87</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600078</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="420" t="str">
         <v>净买: 1376.02万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10473,41 @@
       <c r="H34">
         <v>-4.48</v>
       </c>
-      <c r="I34" s="422">
+      <c r="I34" s="417">
         <v>-5.78</v>
       </c>
-      <c r="J34" s="423">
+      <c r="J34" s="421">
         <v>0</v>
       </c>
-      <c r="K34" s="424">
+      <c r="K34" s="426">
         <v>-2.73</v>
       </c>
-      <c r="L34" s="417">
+      <c r="L34" s="418">
         <v>4.61</v>
       </c>
-      <c r="M34" s="418">
+      <c r="M34" s="427">
         <v>-3.59</v>
       </c>
-      <c r="N34" s="419">
+      <c r="N34" s="428">
         <v>-1.02</v>
       </c>
-      <c r="O34" s="425">
+      <c r="O34" s="422">
         <v>-0.86</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="423">
         <v>-10.78</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="429">
         <v>-16.33</v>
       </c>
-      <c r="R34" s="421">
+      <c r="R34" s="419">
         <v>-13.44</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="424">
         <v>-15.23</v>
       </c>
-      <c r="T34" s="428">
-        <v>1.56</v>
+      <c r="T34" s="425">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002044</v>
       </c>
-      <c r="D35" s="434" t="str">
+      <c r="D35" s="436" t="str">
         <v>净买: 8129.11万</v>
       </c>
       <c r="E35">
@@ -10535,41 +10535,41 @@
       <c r="H35">
         <v>5.48</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="431">
         <v>4.33</v>
       </c>
-      <c r="J35" s="436">
+      <c r="J35" s="434">
         <v>5.2</v>
       </c>
-      <c r="K35" s="431">
+      <c r="K35" s="432">
         <v>-1.91</v>
       </c>
-      <c r="L35" s="439">
+      <c r="L35" s="435">
         <v>-4.85</v>
       </c>
       <c r="M35" s="437">
         <v>-6.07</v>
       </c>
-      <c r="N35" s="440">
+      <c r="N35" s="442">
         <v>-7.11</v>
       </c>
-      <c r="O35" s="441">
+      <c r="O35" s="438">
         <v>-8.32</v>
       </c>
-      <c r="P35" s="432">
+      <c r="P35" s="439">
         <v>-10.4</v>
       </c>
       <c r="Q35" s="433">
         <v>-10.4</v>
       </c>
-      <c r="R35" s="442">
+      <c r="R35" s="430">
         <v>-8.49</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="440">
         <v>-5.37</v>
       </c>
-      <c r="T35" s="438">
-        <v>-10.05</v>
+      <c r="T35" s="441">
+        <v>-10.23</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>301348</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="449" t="str">
         <v>净卖: -905.79万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10597,41 @@
       <c r="H36">
         <v>-4.24</v>
       </c>
-      <c r="I36" s="454">
+      <c r="I36" s="455">
         <v>25.33</v>
       </c>
-      <c r="J36" s="455">
+      <c r="J36" s="443">
         <v>42.26</v>
       </c>
-      <c r="K36" s="448">
+      <c r="K36" s="444">
         <v>32.49</v>
       </c>
-      <c r="L36" s="453">
+      <c r="L36" s="451">
         <v>48.47</v>
       </c>
-      <c r="M36" s="449">
+      <c r="M36" s="450">
         <v>52.11</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="452">
         <v>37.42</v>
       </c>
-      <c r="O36" s="444">
+      <c r="O36" s="453">
         <v>48.97</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="454">
         <v>42.67</v>
       </c>
-      <c r="Q36" s="443">
+      <c r="Q36" s="445">
         <v>31.29</v>
       </c>
-      <c r="R36" s="451">
+      <c r="R36" s="448">
         <v>26.08</v>
       </c>
       <c r="S36" s="446">
         <v>22.06</v>
       </c>
       <c r="T36" s="447">
-        <v>0.7</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="37">
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>301348</v>
       </c>
-      <c r="D37" s="459" t="str">
+      <c r="D37" s="466" t="str">
         <v>净卖: -4537.41万</v>
       </c>
       <c r="E37">
@@ -10659,41 +10659,41 @@
       <c r="H37">
         <v>5.98</v>
       </c>
-      <c r="I37" s="460">
+      <c r="I37" s="463">
         <v>7.11</v>
       </c>
-      <c r="J37" s="461">
+      <c r="J37" s="456">
         <v>-0.25</v>
       </c>
-      <c r="K37" s="462">
+      <c r="K37" s="457">
         <v>11.78</v>
       </c>
-      <c r="L37" s="463">
+      <c r="L37" s="459">
         <v>14.52</v>
       </c>
-      <c r="M37" s="467">
+      <c r="M37" s="464">
         <v>3.46</v>
       </c>
-      <c r="N37" s="457">
+      <c r="N37" s="460">
         <v>12.15</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="467">
         <v>7.42</v>
       </c>
-      <c r="P37" s="465">
+      <c r="P37" s="461">
         <v>-1.15</v>
       </c>
-      <c r="Q37" s="468">
+      <c r="Q37" s="458">
         <v>-5.08</v>
       </c>
-      <c r="R37" s="458">
+      <c r="R37" s="465">
         <v>-8.1</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="462">
         <v>-9.57</v>
       </c>
-      <c r="T37" s="466">
-        <v>-24.18</v>
+      <c r="T37" s="468">
+        <v>-24.59</v>
       </c>
     </row>
     <row r="38">
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>000636</v>
       </c>
-      <c r="D38" s="469" t="str">
+      <c r="D38" s="476" t="str">
         <v>净卖: -226.93万</v>
       </c>
       <c r="E38">
@@ -10721,41 +10721,41 @@
       <c r="H38">
         <v>-1.06</v>
       </c>
-      <c r="I38" s="470">
+      <c r="I38" s="472">
         <v>11.17</v>
       </c>
-      <c r="J38" s="478">
+      <c r="J38" s="477">
         <v>3.8</v>
       </c>
-      <c r="K38" s="477">
+      <c r="K38" s="473">
         <v>2.93</v>
       </c>
-      <c r="L38" s="475">
+      <c r="L38" s="480">
         <v>3.61</v>
       </c>
-      <c r="M38" s="479">
+      <c r="M38" s="470">
         <v>2.73</v>
       </c>
-      <c r="N38" s="480">
+      <c r="N38" s="478">
         <v>9.9</v>
       </c>
-      <c r="O38" s="471">
+      <c r="O38" s="474">
         <v>3.76</v>
       </c>
       <c r="P38" s="481">
         <v>14.15</v>
       </c>
-      <c r="Q38" s="472">
+      <c r="Q38" s="475">
         <v>25.56</v>
       </c>
-      <c r="R38" s="476">
+      <c r="R38" s="469">
         <v>25.51</v>
       </c>
-      <c r="S38" s="473">
+      <c r="S38" s="471">
         <v>26.83</v>
       </c>
-      <c r="T38" s="474">
-        <v>13.61</v>
+      <c r="T38" s="479">
+        <v>19.22</v>
       </c>
     </row>
     <row r="39">
@@ -10817,41 +10817,41 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="484">
+      <c r="I40" s="487">
         <v>78.38</v>
       </c>
-      <c r="J40" s="490">
+      <c r="J40" s="483">
         <v>62.16</v>
       </c>
-      <c r="K40" s="493">
+      <c r="K40" s="489">
         <v>56.76</v>
       </c>
-      <c r="L40" s="488">
+      <c r="L40" s="490">
         <v>59.46</v>
       </c>
-      <c r="M40" s="485">
+      <c r="M40" s="484">
         <v>51.35</v>
       </c>
       <c r="N40" s="491">
         <v>40.54</v>
       </c>
-      <c r="O40" s="486">
+      <c r="O40" s="485">
         <v>37.84</v>
       </c>
       <c r="P40" s="492">
         <v>43.24</v>
       </c>
-      <c r="Q40" s="482">
+      <c r="Q40" s="486">
         <v>40.54</v>
       </c>
-      <c r="R40" s="489">
+      <c r="R40" s="493">
         <v>37.84</v>
       </c>
-      <c r="S40" s="487">
+      <c r="S40" s="488">
         <v>40.54</v>
       </c>
-      <c r="T40" s="483">
-        <v>27.03</v>
+      <c r="T40" s="482">
+        <v>24.32</v>
       </c>
     </row>
     <row r="41">
@@ -10865,41 +10865,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="494">
+      <c r="I41" s="505">
         <v>5.97</v>
       </c>
-      <c r="J41" s="504">
+      <c r="J41" s="494">
         <v>4.69</v>
       </c>
-      <c r="K41" s="498">
+      <c r="K41" s="500">
         <v>2.99</v>
       </c>
       <c r="L41" s="495">
         <v>2.46</v>
       </c>
-      <c r="M41" s="499">
+      <c r="M41" s="501">
         <v>0.83</v>
       </c>
-      <c r="N41" s="505">
+      <c r="N41" s="497">
         <v>-0.52</v>
       </c>
-      <c r="O41" s="500">
+      <c r="O41" s="496">
         <v>-0.81</v>
       </c>
-      <c r="P41" s="501">
+      <c r="P41" s="502">
         <v>-2.1</v>
       </c>
-      <c r="Q41" s="496">
+      <c r="Q41" s="498">
         <v>-1.57</v>
       </c>
-      <c r="R41" s="502">
+      <c r="R41" s="503">
         <v>-1.44</v>
       </c>
-      <c r="S41" s="503">
+      <c r="S41" s="499">
         <v>-0.29</v>
       </c>
-      <c r="T41" s="497">
-        <v>-2</v>
+      <c r="T41" s="504">
+        <v>-3.72</v>
       </c>
     </row>
   </sheetData>
